--- a/pa-temp-fix-system.com/php/shell/sp/common/excel/PA-amazon广告自动化配置-20260416.xlsx
+++ b/pa-temp-fix-system.com/php/shell/sp/common/excel/PA-amazon广告自动化配置-20260416.xlsx
@@ -1912,7 +1912,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L1081"/>
@@ -1971,7 +1971,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:12">
+    <row r="2" hidden="1" customHeight="1" spans="1:12">
       <c r="A2" s="7" t="s">
         <v>12</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:12">
+    <row r="3" hidden="1" customHeight="1" spans="1:12">
       <c r="A3" s="7" t="s">
         <v>12</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:12">
+    <row r="4" hidden="1" customHeight="1" spans="1:12">
       <c r="A4" s="7" t="s">
         <v>12</v>
       </c>
@@ -2058,7 +2058,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:12">
+    <row r="5" hidden="1" customHeight="1" spans="1:12">
       <c r="A5" s="7" t="s">
         <v>12</v>
       </c>
@@ -2087,7 +2087,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:12">
+    <row r="6" hidden="1" customHeight="1" spans="1:12">
       <c r="A6" s="7" t="s">
         <v>12</v>
       </c>
@@ -2116,7 +2116,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:12">
+    <row r="7" hidden="1" customHeight="1" spans="1:12">
       <c r="A7" s="7" t="s">
         <v>12</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:12">
+    <row r="8" hidden="1" customHeight="1" spans="1:12">
       <c r="A8" s="7" t="s">
         <v>12</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:12">
+    <row r="9" hidden="1" customHeight="1" spans="1:12">
       <c r="A9" s="7" t="s">
         <v>12</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:12">
+    <row r="10" hidden="1" customHeight="1" spans="1:12">
       <c r="A10" s="7" t="s">
         <v>12</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:12">
+    <row r="11" hidden="1" customHeight="1" spans="1:12">
       <c r="A11" s="7" t="s">
         <v>12</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:12">
+    <row r="12" hidden="1" customHeight="1" spans="1:12">
       <c r="A12" s="7" t="s">
         <v>12</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:12">
+    <row r="13" hidden="1" customHeight="1" spans="1:12">
       <c r="A13" s="7" t="s">
         <v>12</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:12">
+    <row r="14" hidden="1" customHeight="1" spans="1:12">
       <c r="A14" s="7" t="s">
         <v>12</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:12">
+    <row r="15" hidden="1" customHeight="1" spans="1:12">
       <c r="A15" s="7" t="s">
         <v>12</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:12">
+    <row r="16" hidden="1" customHeight="1" spans="1:12">
       <c r="A16" s="7" t="s">
         <v>12</v>
       </c>
@@ -2406,7 +2406,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:11">
+    <row r="17" hidden="1" customHeight="1" spans="1:11">
       <c r="A17" s="7" t="s">
         <v>12</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:11">
+    <row r="18" hidden="1" customHeight="1" spans="1:11">
       <c r="A18" s="7" t="s">
         <v>12</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:11">
+    <row r="19" hidden="1" customHeight="1" spans="1:11">
       <c r="A19" s="7" t="s">
         <v>12</v>
       </c>
@@ -2493,7 +2493,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:11">
+    <row r="20" hidden="1" customHeight="1" spans="1:11">
       <c r="A20" s="7" t="s">
         <v>12</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:11">
+    <row r="21" hidden="1" customHeight="1" spans="1:11">
       <c r="A21" s="7" t="s">
         <v>12</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:11">
+    <row r="22" hidden="1" customHeight="1" spans="1:11">
       <c r="A22" s="7" t="s">
         <v>12</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:11">
+    <row r="23" hidden="1" customHeight="1" spans="1:11">
       <c r="A23" s="7" t="s">
         <v>12</v>
       </c>
@@ -2606,7 +2606,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:11">
+    <row r="24" hidden="1" customHeight="1" spans="1:11">
       <c r="A24" s="7" t="s">
         <v>12</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:11">
+    <row r="25" hidden="1" customHeight="1" spans="1:11">
       <c r="A25" s="7" t="s">
         <v>12</v>
       </c>
@@ -2661,7 +2661,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:11">
+    <row r="26" hidden="1" customHeight="1" spans="1:11">
       <c r="A26" s="7" t="s">
         <v>50</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="1:11">
+    <row r="27" hidden="1" customHeight="1" spans="1:11">
       <c r="A27" s="7" t="s">
         <v>50</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="1:11">
+    <row r="28" hidden="1" customHeight="1" spans="1:11">
       <c r="A28" s="7" t="s">
         <v>50</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="1:11">
+    <row r="29" hidden="1" customHeight="1" spans="1:11">
       <c r="A29" s="7" t="s">
         <v>50</v>
       </c>
@@ -2777,7 +2777,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="1:11">
+    <row r="30" hidden="1" customHeight="1" spans="1:11">
       <c r="A30" s="7" t="s">
         <v>50</v>
       </c>
@@ -2806,7 +2806,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="1:11">
+    <row r="31" hidden="1" customHeight="1" spans="1:11">
       <c r="A31" s="7" t="s">
         <v>50</v>
       </c>
@@ -2835,7 +2835,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="1:11">
+    <row r="32" hidden="1" customHeight="1" spans="1:11">
       <c r="A32" s="7" t="s">
         <v>50</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="1:11">
+    <row r="33" hidden="1" customHeight="1" spans="1:11">
       <c r="A33" s="7" t="s">
         <v>50</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="1:11">
+    <row r="34" hidden="1" customHeight="1" spans="1:11">
       <c r="A34" s="7" t="s">
         <v>50</v>
       </c>
@@ -2922,7 +2922,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="1:11">
+    <row r="35" hidden="1" customHeight="1" spans="1:11">
       <c r="A35" s="7" t="s">
         <v>50</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="1:11">
+    <row r="36" hidden="1" customHeight="1" spans="1:11">
       <c r="A36" s="7" t="s">
         <v>50</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="1:11">
+    <row r="37" hidden="1" customHeight="1" spans="1:11">
       <c r="A37" s="7" t="s">
         <v>50</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="1:11">
+    <row r="38" hidden="1" customHeight="1" spans="1:11">
       <c r="A38" s="7" t="s">
         <v>50</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="1:11">
+    <row r="39" hidden="1" customHeight="1" spans="1:11">
       <c r="A39" s="7" t="s">
         <v>50</v>
       </c>
@@ -3067,7 +3067,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="1:11">
+    <row r="40" hidden="1" customHeight="1" spans="1:11">
       <c r="A40" s="7" t="s">
         <v>50</v>
       </c>
@@ -3096,7 +3096,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="1:11">
+    <row r="41" hidden="1" customHeight="1" spans="1:11">
       <c r="A41" s="7" t="s">
         <v>50</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="1:11">
+    <row r="42" hidden="1" customHeight="1" spans="1:11">
       <c r="A42" s="7" t="s">
         <v>50</v>
       </c>
@@ -3154,7 +3154,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="43" customHeight="1" spans="1:11">
+    <row r="43" hidden="1" customHeight="1" spans="1:11">
       <c r="A43" s="7" t="s">
         <v>50</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="1:11">
+    <row r="44" hidden="1" customHeight="1" spans="1:11">
       <c r="A44" s="7" t="s">
         <v>50</v>
       </c>
@@ -3209,7 +3209,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="1:11">
+    <row r="45" hidden="1" customHeight="1" spans="1:11">
       <c r="A45" s="7" t="s">
         <v>50</v>
       </c>
@@ -3238,7 +3238,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="46" customHeight="1" spans="1:11">
+    <row r="46" hidden="1" customHeight="1" spans="1:11">
       <c r="A46" s="7" t="s">
         <v>50</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="1:11">
+    <row r="47" hidden="1" customHeight="1" spans="1:11">
       <c r="A47" s="7" t="s">
         <v>50</v>
       </c>
@@ -3296,7 +3296,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="48" customHeight="1" spans="1:11">
+    <row r="48" hidden="1" customHeight="1" spans="1:11">
       <c r="A48" s="7" t="s">
         <v>50</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="49" customHeight="1" spans="1:11">
+    <row r="49" hidden="1" customHeight="1" spans="1:11">
       <c r="A49" s="7" t="s">
         <v>50</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" customHeight="1" spans="1:11">
+    <row r="50" hidden="1" customHeight="1" spans="1:11">
       <c r="A50" s="7" t="s">
         <v>53</v>
       </c>
@@ -3380,7 +3380,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="51" customHeight="1" spans="1:11">
+    <row r="51" hidden="1" customHeight="1" spans="1:11">
       <c r="A51" s="7" t="s">
         <v>53</v>
       </c>
@@ -3409,7 +3409,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="52" customHeight="1" spans="1:11">
+    <row r="52" hidden="1" customHeight="1" spans="1:11">
       <c r="A52" s="7" t="s">
         <v>53</v>
       </c>
@@ -3438,7 +3438,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="1:11">
+    <row r="53" hidden="1" customHeight="1" spans="1:11">
       <c r="A53" s="7" t="s">
         <v>53</v>
       </c>
@@ -3467,7 +3467,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="54" customHeight="1" spans="1:11">
+    <row r="54" hidden="1" customHeight="1" spans="1:11">
       <c r="A54" s="7" t="s">
         <v>53</v>
       </c>
@@ -3496,7 +3496,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="55" customHeight="1" spans="1:11">
+    <row r="55" hidden="1" customHeight="1" spans="1:11">
       <c r="A55" s="7" t="s">
         <v>53</v>
       </c>
@@ -3525,7 +3525,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="56" customHeight="1" spans="1:11">
+    <row r="56" hidden="1" customHeight="1" spans="1:11">
       <c r="A56" s="7" t="s">
         <v>53</v>
       </c>
@@ -3554,7 +3554,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="57" customHeight="1" spans="1:11">
+    <row r="57" hidden="1" customHeight="1" spans="1:11">
       <c r="A57" s="7" t="s">
         <v>53</v>
       </c>
@@ -3580,7 +3580,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" customHeight="1" spans="1:11">
+    <row r="58" hidden="1" customHeight="1" spans="1:11">
       <c r="A58" s="7" t="s">
         <v>53</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="59" customHeight="1" spans="1:11">
+    <row r="59" hidden="1" customHeight="1" spans="1:11">
       <c r="A59" s="7" t="s">
         <v>53</v>
       </c>
@@ -3638,7 +3638,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="60" customHeight="1" spans="1:11">
+    <row r="60" hidden="1" customHeight="1" spans="1:11">
       <c r="A60" s="7" t="s">
         <v>53</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="61" customHeight="1" spans="1:11">
+    <row r="61" hidden="1" customHeight="1" spans="1:11">
       <c r="A61" s="7" t="s">
         <v>53</v>
       </c>
@@ -3693,7 +3693,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="62" customHeight="1" spans="1:11">
+    <row r="62" hidden="1" customHeight="1" spans="1:11">
       <c r="A62" s="7" t="s">
         <v>53</v>
       </c>
@@ -3722,7 +3722,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="63" customHeight="1" spans="1:11">
+    <row r="63" hidden="1" customHeight="1" spans="1:11">
       <c r="A63" s="7" t="s">
         <v>53</v>
       </c>
@@ -3748,7 +3748,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="64" customHeight="1" spans="1:11">
+    <row r="64" hidden="1" customHeight="1" spans="1:11">
       <c r="A64" s="7" t="s">
         <v>53</v>
       </c>
@@ -3774,7 +3774,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="65" customHeight="1" spans="1:11">
+    <row r="65" hidden="1" customHeight="1" spans="1:11">
       <c r="A65" s="7" t="s">
         <v>53</v>
       </c>
@@ -3803,7 +3803,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="1:11">
+    <row r="66" hidden="1" customHeight="1" spans="1:11">
       <c r="A66" s="7" t="s">
         <v>53</v>
       </c>
@@ -3832,7 +3832,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="1:11">
+    <row r="67" hidden="1" customHeight="1" spans="1:11">
       <c r="A67" s="7" t="s">
         <v>53</v>
       </c>
@@ -3858,7 +3858,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="68" customHeight="1" spans="1:11">
+    <row r="68" hidden="1" customHeight="1" spans="1:11">
       <c r="A68" s="7" t="s">
         <v>53</v>
       </c>
@@ -3884,7 +3884,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" customHeight="1" spans="1:11">
+    <row r="69" hidden="1" customHeight="1" spans="1:11">
       <c r="A69" s="7" t="s">
         <v>53</v>
       </c>
@@ -3913,7 +3913,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="70" customHeight="1" spans="1:11">
+    <row r="70" hidden="1" customHeight="1" spans="1:11">
       <c r="A70" s="7" t="s">
         <v>53</v>
       </c>
@@ -3942,7 +3942,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="71" customHeight="1" spans="1:11">
+    <row r="71" hidden="1" customHeight="1" spans="1:11">
       <c r="A71" s="7" t="s">
         <v>53</v>
       </c>
@@ -3968,7 +3968,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="72" customHeight="1" spans="1:11">
+    <row r="72" hidden="1" customHeight="1" spans="1:11">
       <c r="A72" s="7" t="s">
         <v>53</v>
       </c>
@@ -3994,7 +3994,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="73" customHeight="1" spans="1:11">
+    <row r="73" hidden="1" customHeight="1" spans="1:11">
       <c r="A73" s="7" t="s">
         <v>53</v>
       </c>
@@ -4023,7 +4023,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="74" s="1" customFormat="1" customHeight="1" spans="1:11">
+    <row r="74" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:11">
       <c r="A74" s="8" t="s">
         <v>12</v>
       </c>
@@ -4052,7 +4052,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="75" customHeight="1" spans="1:11">
+    <row r="75" hidden="1" customHeight="1" spans="1:11">
       <c r="A75" s="7" t="s">
         <v>12</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="76" customHeight="1" spans="1:11">
+    <row r="76" hidden="1" customHeight="1" spans="1:11">
       <c r="A76" s="7" t="s">
         <v>12</v>
       </c>
@@ -4110,7 +4110,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="77" customHeight="1" spans="1:11">
+    <row r="77" hidden="1" customHeight="1" spans="1:11">
       <c r="A77" s="7" t="s">
         <v>12</v>
       </c>
@@ -4139,7 +4139,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="78" customHeight="1" spans="1:11">
+    <row r="78" hidden="1" customHeight="1" spans="1:11">
       <c r="A78" s="7" t="s">
         <v>12</v>
       </c>
@@ -4168,7 +4168,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="79" customHeight="1" spans="1:11">
+    <row r="79" hidden="1" customHeight="1" spans="1:11">
       <c r="A79" s="7" t="s">
         <v>12</v>
       </c>
@@ -4197,7 +4197,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="80" customHeight="1" spans="1:11">
+    <row r="80" hidden="1" customHeight="1" spans="1:11">
       <c r="A80" s="7" t="s">
         <v>12</v>
       </c>
@@ -4226,7 +4226,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="81" customHeight="1" spans="1:11">
+    <row r="81" hidden="1" customHeight="1" spans="1:11">
       <c r="A81" s="7" t="s">
         <v>12</v>
       </c>
@@ -4255,7 +4255,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="82" customHeight="1" spans="1:11">
+    <row r="82" hidden="1" customHeight="1" spans="1:11">
       <c r="A82" s="7" t="s">
         <v>12</v>
       </c>
@@ -4284,7 +4284,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="83" customHeight="1" spans="1:11">
+    <row r="83" hidden="1" customHeight="1" spans="1:11">
       <c r="A83" s="7" t="s">
         <v>12</v>
       </c>
@@ -4313,7 +4313,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="84" customHeight="1" spans="1:11">
+    <row r="84" hidden="1" customHeight="1" spans="1:11">
       <c r="A84" s="7" t="s">
         <v>12</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="85" customHeight="1" spans="1:11">
+    <row r="85" hidden="1" customHeight="1" spans="1:11">
       <c r="A85" s="7" t="s">
         <v>12</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="86" customHeight="1" spans="1:11">
+    <row r="86" hidden="1" customHeight="1" spans="1:11">
       <c r="A86" s="7" t="s">
         <v>12</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" customHeight="1" spans="1:11">
+    <row r="87" hidden="1" customHeight="1" spans="1:11">
       <c r="A87" s="7" t="s">
         <v>12</v>
       </c>
@@ -4429,7 +4429,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="88" customHeight="1" spans="1:11">
+    <row r="88" hidden="1" customHeight="1" spans="1:11">
       <c r="A88" s="7" t="s">
         <v>12</v>
       </c>
@@ -4458,7 +4458,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="89" customHeight="1" spans="1:11">
+    <row r="89" hidden="1" customHeight="1" spans="1:11">
       <c r="A89" s="7" t="s">
         <v>12</v>
       </c>
@@ -4487,7 +4487,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="90" customHeight="1" spans="1:11">
+    <row r="90" hidden="1" customHeight="1" spans="1:11">
       <c r="A90" s="7" t="s">
         <v>12</v>
       </c>
@@ -4516,7 +4516,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="91" customHeight="1" spans="1:11">
+    <row r="91" hidden="1" customHeight="1" spans="1:11">
       <c r="A91" s="7" t="s">
         <v>12</v>
       </c>
@@ -4545,7 +4545,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="92" customHeight="1" spans="1:11">
+    <row r="92" hidden="1" customHeight="1" spans="1:11">
       <c r="A92" s="7" t="s">
         <v>12</v>
       </c>
@@ -4571,7 +4571,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="93" customHeight="1" spans="1:11">
+    <row r="93" hidden="1" customHeight="1" spans="1:11">
       <c r="A93" s="7" t="s">
         <v>12</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="94" customHeight="1" spans="1:11">
+    <row r="94" hidden="1" customHeight="1" spans="1:11">
       <c r="A94" s="7" t="s">
         <v>12</v>
       </c>
@@ -4629,7 +4629,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="95" customHeight="1" spans="1:11">
+    <row r="95" hidden="1" customHeight="1" spans="1:11">
       <c r="A95" s="7" t="s">
         <v>12</v>
       </c>
@@ -4658,7 +4658,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="96" customHeight="1" spans="1:11">
+    <row r="96" hidden="1" customHeight="1" spans="1:11">
       <c r="A96" s="7" t="s">
         <v>12</v>
       </c>
@@ -4684,7 +4684,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="97" customHeight="1" spans="1:11">
+    <row r="97" hidden="1" customHeight="1" spans="1:11">
       <c r="A97" s="7" t="s">
         <v>12</v>
       </c>
@@ -4713,7 +4713,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="98" customHeight="1" spans="1:11">
+    <row r="98" hidden="1" customHeight="1" spans="1:11">
       <c r="A98" s="7" t="s">
         <v>50</v>
       </c>
@@ -4742,7 +4742,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="99" customHeight="1" spans="1:11">
+    <row r="99" hidden="1" customHeight="1" spans="1:11">
       <c r="A99" s="7" t="s">
         <v>50</v>
       </c>
@@ -4771,7 +4771,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="100" customHeight="1" spans="1:11">
+    <row r="100" hidden="1" customHeight="1" spans="1:11">
       <c r="A100" s="7" t="s">
         <v>50</v>
       </c>
@@ -4800,7 +4800,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="101" customHeight="1" spans="1:11">
+    <row r="101" hidden="1" customHeight="1" spans="1:11">
       <c r="A101" s="7" t="s">
         <v>50</v>
       </c>
@@ -4829,7 +4829,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="102" customHeight="1" spans="1:11">
+    <row r="102" hidden="1" customHeight="1" spans="1:11">
       <c r="A102" s="7" t="s">
         <v>50</v>
       </c>
@@ -4858,7 +4858,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="103" customHeight="1" spans="1:11">
+    <row r="103" hidden="1" customHeight="1" spans="1:11">
       <c r="A103" s="7" t="s">
         <v>50</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="104" customHeight="1" spans="1:11">
+    <row r="104" hidden="1" customHeight="1" spans="1:11">
       <c r="A104" s="7" t="s">
         <v>50</v>
       </c>
@@ -4916,7 +4916,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="105" customHeight="1" spans="1:11">
+    <row r="105" hidden="1" customHeight="1" spans="1:11">
       <c r="A105" s="7" t="s">
         <v>50</v>
       </c>
@@ -4945,7 +4945,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="106" customHeight="1" spans="1:11">
+    <row r="106" hidden="1" customHeight="1" spans="1:11">
       <c r="A106" s="7" t="s">
         <v>50</v>
       </c>
@@ -4974,7 +4974,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="107" customHeight="1" spans="1:11">
+    <row r="107" hidden="1" customHeight="1" spans="1:11">
       <c r="A107" s="7" t="s">
         <v>50</v>
       </c>
@@ -5003,7 +5003,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="108" customHeight="1" spans="1:11">
+    <row r="108" hidden="1" customHeight="1" spans="1:11">
       <c r="A108" s="7" t="s">
         <v>50</v>
       </c>
@@ -5032,7 +5032,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="109" customHeight="1" spans="1:11">
+    <row r="109" hidden="1" customHeight="1" spans="1:11">
       <c r="A109" s="7" t="s">
         <v>50</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="110" customHeight="1" spans="1:11">
+    <row r="110" hidden="1" customHeight="1" spans="1:11">
       <c r="A110" s="7" t="s">
         <v>50</v>
       </c>
@@ -5090,7 +5090,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="111" customHeight="1" spans="1:11">
+    <row r="111" hidden="1" customHeight="1" spans="1:11">
       <c r="A111" s="7" t="s">
         <v>50</v>
       </c>
@@ -5119,7 +5119,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="112" customHeight="1" spans="1:11">
+    <row r="112" hidden="1" customHeight="1" spans="1:11">
       <c r="A112" s="7" t="s">
         <v>50</v>
       </c>
@@ -5148,7 +5148,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="113" customHeight="1" spans="1:11">
+    <row r="113" hidden="1" customHeight="1" spans="1:11">
       <c r="A113" s="7" t="s">
         <v>50</v>
       </c>
@@ -5177,7 +5177,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="114" customHeight="1" spans="1:11">
+    <row r="114" hidden="1" customHeight="1" spans="1:11">
       <c r="A114" s="7" t="s">
         <v>50</v>
       </c>
@@ -5206,7 +5206,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="115" customHeight="1" spans="1:11">
+    <row r="115" hidden="1" customHeight="1" spans="1:11">
       <c r="A115" s="7" t="s">
         <v>50</v>
       </c>
@@ -5235,7 +5235,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="116" customHeight="1" spans="1:11">
+    <row r="116" hidden="1" customHeight="1" spans="1:11">
       <c r="A116" s="7" t="s">
         <v>50</v>
       </c>
@@ -5261,7 +5261,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="117" customHeight="1" spans="1:11">
+    <row r="117" hidden="1" customHeight="1" spans="1:11">
       <c r="A117" s="7" t="s">
         <v>50</v>
       </c>
@@ -5290,7 +5290,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="118" customHeight="1" spans="1:11">
+    <row r="118" hidden="1" customHeight="1" spans="1:11">
       <c r="A118" s="7" t="s">
         <v>50</v>
       </c>
@@ -5319,7 +5319,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="119" customHeight="1" spans="1:11">
+    <row r="119" hidden="1" customHeight="1" spans="1:11">
       <c r="A119" s="7" t="s">
         <v>50</v>
       </c>
@@ -5348,7 +5348,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="120" customHeight="1" spans="1:11">
+    <row r="120" hidden="1" customHeight="1" spans="1:11">
       <c r="A120" s="7" t="s">
         <v>50</v>
       </c>
@@ -5374,7 +5374,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="121" customHeight="1" spans="1:11">
+    <row r="121" hidden="1" customHeight="1" spans="1:11">
       <c r="A121" s="7" t="s">
         <v>50</v>
       </c>
@@ -5403,7 +5403,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="122" customHeight="1" spans="1:11">
+    <row r="122" hidden="1" customHeight="1" spans="1:11">
       <c r="A122" s="7" t="s">
         <v>53</v>
       </c>
@@ -5432,7 +5432,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="123" customHeight="1" spans="1:11">
+    <row r="123" hidden="1" customHeight="1" spans="1:11">
       <c r="A123" s="7" t="s">
         <v>53</v>
       </c>
@@ -5461,7 +5461,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="124" customHeight="1" spans="1:11">
+    <row r="124" hidden="1" customHeight="1" spans="1:11">
       <c r="A124" s="7" t="s">
         <v>53</v>
       </c>
@@ -5490,7 +5490,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="125" customHeight="1" spans="1:11">
+    <row r="125" hidden="1" customHeight="1" spans="1:11">
       <c r="A125" s="7" t="s">
         <v>53</v>
       </c>
@@ -5519,7 +5519,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="126" customHeight="1" spans="1:11">
+    <row r="126" hidden="1" customHeight="1" spans="1:11">
       <c r="A126" s="7" t="s">
         <v>53</v>
       </c>
@@ -5548,7 +5548,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="127" customHeight="1" spans="1:11">
+    <row r="127" hidden="1" customHeight="1" spans="1:11">
       <c r="A127" s="7" t="s">
         <v>53</v>
       </c>
@@ -5577,7 +5577,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="128" customHeight="1" spans="1:11">
+    <row r="128" hidden="1" customHeight="1" spans="1:11">
       <c r="A128" s="7" t="s">
         <v>53</v>
       </c>
@@ -5606,7 +5606,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="129" customHeight="1" spans="1:11">
+    <row r="129" hidden="1" customHeight="1" spans="1:11">
       <c r="A129" s="7" t="s">
         <v>53</v>
       </c>
@@ -5632,7 +5632,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="130" customHeight="1" spans="1:11">
+    <row r="130" hidden="1" customHeight="1" spans="1:11">
       <c r="A130" s="7" t="s">
         <v>53</v>
       </c>
@@ -5661,7 +5661,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="131" customHeight="1" spans="1:11">
+    <row r="131" hidden="1" customHeight="1" spans="1:11">
       <c r="A131" s="7" t="s">
         <v>53</v>
       </c>
@@ -5690,7 +5690,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="132" customHeight="1" spans="1:11">
+    <row r="132" hidden="1" customHeight="1" spans="1:11">
       <c r="A132" s="7" t="s">
         <v>53</v>
       </c>
@@ -5719,7 +5719,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="133" customHeight="1" spans="1:11">
+    <row r="133" hidden="1" customHeight="1" spans="1:11">
       <c r="A133" s="7" t="s">
         <v>53</v>
       </c>
@@ -5745,7 +5745,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="134" customHeight="1" spans="1:11">
+    <row r="134" hidden="1" customHeight="1" spans="1:11">
       <c r="A134" s="7" t="s">
         <v>53</v>
       </c>
@@ -5774,7 +5774,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="135" customHeight="1" spans="1:11">
+    <row r="135" hidden="1" customHeight="1" spans="1:11">
       <c r="A135" s="7" t="s">
         <v>53</v>
       </c>
@@ -5800,7 +5800,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="136" customHeight="1" spans="1:11">
+    <row r="136" hidden="1" customHeight="1" spans="1:11">
       <c r="A136" s="7" t="s">
         <v>53</v>
       </c>
@@ -5826,7 +5826,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="137" customHeight="1" spans="1:11">
+    <row r="137" hidden="1" customHeight="1" spans="1:11">
       <c r="A137" s="7" t="s">
         <v>53</v>
       </c>
@@ -5855,7 +5855,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="138" customHeight="1" spans="1:11">
+    <row r="138" hidden="1" customHeight="1" spans="1:11">
       <c r="A138" s="7" t="s">
         <v>53</v>
       </c>
@@ -5884,7 +5884,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="139" customHeight="1" spans="1:11">
+    <row r="139" hidden="1" customHeight="1" spans="1:11">
       <c r="A139" s="7" t="s">
         <v>53</v>
       </c>
@@ -5910,7 +5910,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="140" customHeight="1" spans="1:11">
+    <row r="140" hidden="1" customHeight="1" spans="1:11">
       <c r="A140" s="7" t="s">
         <v>53</v>
       </c>
@@ -5936,7 +5936,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="141" customHeight="1" spans="1:11">
+    <row r="141" hidden="1" customHeight="1" spans="1:11">
       <c r="A141" s="7" t="s">
         <v>53</v>
       </c>
@@ -5965,7 +5965,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="142" customHeight="1" spans="1:11">
+    <row r="142" hidden="1" customHeight="1" spans="1:11">
       <c r="A142" s="7" t="s">
         <v>53</v>
       </c>
@@ -5994,7 +5994,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="143" customHeight="1" spans="1:11">
+    <row r="143" hidden="1" customHeight="1" spans="1:11">
       <c r="A143" s="7" t="s">
         <v>53</v>
       </c>
@@ -6020,7 +6020,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="144" customHeight="1" spans="1:11">
+    <row r="144" hidden="1" customHeight="1" spans="1:11">
       <c r="A144" s="7" t="s">
         <v>53</v>
       </c>
@@ -6046,7 +6046,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="145" customHeight="1" spans="1:11">
+    <row r="145" hidden="1" customHeight="1" spans="1:11">
       <c r="A145" s="7" t="s">
         <v>53</v>
       </c>
@@ -6075,7 +6075,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="146" customHeight="1" spans="1:11">
+    <row r="146" hidden="1" customHeight="1" spans="1:11">
       <c r="A146" s="8" t="s">
         <v>12</v>
       </c>
@@ -6106,7 +6106,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="147" customHeight="1" spans="1:11">
+    <row r="147" hidden="1" customHeight="1" spans="1:11">
       <c r="A147" s="7" t="s">
         <v>12</v>
       </c>
@@ -6135,7 +6135,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="148" customHeight="1" spans="1:11">
+    <row r="148" hidden="1" customHeight="1" spans="1:11">
       <c r="A148" s="7" t="s">
         <v>12</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="149" customHeight="1" spans="1:11">
+    <row r="149" hidden="1" customHeight="1" spans="1:11">
       <c r="A149" s="7" t="s">
         <v>12</v>
       </c>
@@ -6193,7 +6193,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="150" customHeight="1" spans="1:11">
+    <row r="150" hidden="1" customHeight="1" spans="1:11">
       <c r="A150" s="7" t="s">
         <v>12</v>
       </c>
@@ -6222,7 +6222,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="151" customHeight="1" spans="1:11">
+    <row r="151" hidden="1" customHeight="1" spans="1:11">
       <c r="A151" s="7" t="s">
         <v>12</v>
       </c>
@@ -6251,7 +6251,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="152" customHeight="1" spans="1:11">
+    <row r="152" hidden="1" customHeight="1" spans="1:11">
       <c r="A152" s="7" t="s">
         <v>12</v>
       </c>
@@ -6280,7 +6280,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="153" customHeight="1" spans="1:11">
+    <row r="153" hidden="1" customHeight="1" spans="1:11">
       <c r="A153" s="7" t="s">
         <v>12</v>
       </c>
@@ -6309,7 +6309,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="154" customHeight="1" spans="1:11">
+    <row r="154" hidden="1" customHeight="1" spans="1:11">
       <c r="A154" s="7" t="s">
         <v>12</v>
       </c>
@@ -6338,7 +6338,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="155" customHeight="1" spans="1:11">
+    <row r="155" hidden="1" customHeight="1" spans="1:11">
       <c r="A155" s="7" t="s">
         <v>12</v>
       </c>
@@ -6367,7 +6367,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="156" customHeight="1" spans="1:11">
+    <row r="156" hidden="1" customHeight="1" spans="1:11">
       <c r="A156" s="7" t="s">
         <v>12</v>
       </c>
@@ -6396,7 +6396,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="157" customHeight="1" spans="1:11">
+    <row r="157" hidden="1" customHeight="1" spans="1:11">
       <c r="A157" s="7" t="s">
         <v>12</v>
       </c>
@@ -6425,7 +6425,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="158" customHeight="1" spans="1:11">
+    <row r="158" hidden="1" customHeight="1" spans="1:11">
       <c r="A158" s="7" t="s">
         <v>12</v>
       </c>
@@ -6454,7 +6454,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="159" customHeight="1" spans="1:11">
+    <row r="159" hidden="1" customHeight="1" spans="1:11">
       <c r="A159" s="7" t="s">
         <v>12</v>
       </c>
@@ -6483,7 +6483,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="160" customHeight="1" spans="1:11">
+    <row r="160" hidden="1" customHeight="1" spans="1:11">
       <c r="A160" s="7" t="s">
         <v>12</v>
       </c>
@@ -6512,7 +6512,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="161" customHeight="1" spans="1:11">
+    <row r="161" hidden="1" customHeight="1" spans="1:11">
       <c r="A161" s="7" t="s">
         <v>12</v>
       </c>
@@ -6541,7 +6541,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="162" customHeight="1" spans="1:11">
+    <row r="162" hidden="1" customHeight="1" spans="1:11">
       <c r="A162" s="7" t="s">
         <v>12</v>
       </c>
@@ -6570,7 +6570,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="163" customHeight="1" spans="1:11">
+    <row r="163" hidden="1" customHeight="1" spans="1:11">
       <c r="A163" s="7" t="s">
         <v>12</v>
       </c>
@@ -6599,7 +6599,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="164" customHeight="1" spans="1:11">
+    <row r="164" hidden="1" customHeight="1" spans="1:11">
       <c r="A164" s="7" t="s">
         <v>12</v>
       </c>
@@ -6625,7 +6625,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="165" customHeight="1" spans="1:11">
+    <row r="165" hidden="1" customHeight="1" spans="1:11">
       <c r="A165" s="7" t="s">
         <v>12</v>
       </c>
@@ -6654,7 +6654,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="166" customHeight="1" spans="1:11">
+    <row r="166" hidden="1" customHeight="1" spans="1:11">
       <c r="A166" s="7" t="s">
         <v>12</v>
       </c>
@@ -6683,7 +6683,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="167" customHeight="1" spans="1:11">
+    <row r="167" hidden="1" customHeight="1" spans="1:11">
       <c r="A167" s="7" t="s">
         <v>12</v>
       </c>
@@ -6712,7 +6712,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="168" customHeight="1" spans="1:11">
+    <row r="168" hidden="1" customHeight="1" spans="1:11">
       <c r="A168" s="7" t="s">
         <v>12</v>
       </c>
@@ -6738,7 +6738,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="169" customHeight="1" spans="1:11">
+    <row r="169" hidden="1" customHeight="1" spans="1:11">
       <c r="A169" s="7" t="s">
         <v>12</v>
       </c>
@@ -6767,7 +6767,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="170" customHeight="1" spans="1:11">
+    <row r="170" hidden="1" customHeight="1" spans="1:11">
       <c r="A170" s="7" t="s">
         <v>50</v>
       </c>
@@ -6796,7 +6796,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="171" customHeight="1" spans="1:11">
+    <row r="171" hidden="1" customHeight="1" spans="1:11">
       <c r="A171" s="7" t="s">
         <v>50</v>
       </c>
@@ -6825,7 +6825,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="172" customHeight="1" spans="1:11">
+    <row r="172" hidden="1" customHeight="1" spans="1:11">
       <c r="A172" s="7" t="s">
         <v>50</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="173" customHeight="1" spans="1:11">
+    <row r="173" hidden="1" customHeight="1" spans="1:11">
       <c r="A173" s="7" t="s">
         <v>50</v>
       </c>
@@ -6883,7 +6883,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="174" customHeight="1" spans="1:11">
+    <row r="174" hidden="1" customHeight="1" spans="1:11">
       <c r="A174" s="7" t="s">
         <v>50</v>
       </c>
@@ -6912,7 +6912,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="175" customHeight="1" spans="1:11">
+    <row r="175" hidden="1" customHeight="1" spans="1:11">
       <c r="A175" s="7" t="s">
         <v>50</v>
       </c>
@@ -6941,7 +6941,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="176" customHeight="1" spans="1:11">
+    <row r="176" hidden="1" customHeight="1" spans="1:11">
       <c r="A176" s="7" t="s">
         <v>50</v>
       </c>
@@ -6970,7 +6970,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="177" customHeight="1" spans="1:11">
+    <row r="177" hidden="1" customHeight="1" spans="1:11">
       <c r="A177" s="7" t="s">
         <v>50</v>
       </c>
@@ -6999,7 +6999,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="178" customHeight="1" spans="1:11">
+    <row r="178" hidden="1" customHeight="1" spans="1:11">
       <c r="A178" s="7" t="s">
         <v>50</v>
       </c>
@@ -7028,7 +7028,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="179" customHeight="1" spans="1:11">
+    <row r="179" hidden="1" customHeight="1" spans="1:11">
       <c r="A179" s="7" t="s">
         <v>50</v>
       </c>
@@ -7057,7 +7057,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="180" customHeight="1" spans="1:11">
+    <row r="180" hidden="1" customHeight="1" spans="1:11">
       <c r="A180" s="7" t="s">
         <v>50</v>
       </c>
@@ -7086,7 +7086,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="181" customHeight="1" spans="1:11">
+    <row r="181" hidden="1" customHeight="1" spans="1:11">
       <c r="A181" s="7" t="s">
         <v>50</v>
       </c>
@@ -7115,7 +7115,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="182" customHeight="1" spans="1:11">
+    <row r="182" hidden="1" customHeight="1" spans="1:11">
       <c r="A182" s="7" t="s">
         <v>50</v>
       </c>
@@ -7144,7 +7144,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="183" customHeight="1" spans="1:11">
+    <row r="183" hidden="1" customHeight="1" spans="1:11">
       <c r="A183" s="7" t="s">
         <v>50</v>
       </c>
@@ -7173,7 +7173,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="184" customHeight="1" spans="1:11">
+    <row r="184" hidden="1" customHeight="1" spans="1:11">
       <c r="A184" s="7" t="s">
         <v>50</v>
       </c>
@@ -7202,7 +7202,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="185" customHeight="1" spans="1:11">
+    <row r="185" hidden="1" customHeight="1" spans="1:11">
       <c r="A185" s="7" t="s">
         <v>50</v>
       </c>
@@ -7231,7 +7231,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="186" customHeight="1" spans="1:11">
+    <row r="186" hidden="1" customHeight="1" spans="1:11">
       <c r="A186" s="7" t="s">
         <v>50</v>
       </c>
@@ -7260,7 +7260,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="187" customHeight="1" spans="1:11">
+    <row r="187" hidden="1" customHeight="1" spans="1:11">
       <c r="A187" s="7" t="s">
         <v>50</v>
       </c>
@@ -7289,7 +7289,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="188" customHeight="1" spans="1:11">
+    <row r="188" hidden="1" customHeight="1" spans="1:11">
       <c r="A188" s="7" t="s">
         <v>50</v>
       </c>
@@ -7315,7 +7315,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="189" customHeight="1" spans="1:11">
+    <row r="189" hidden="1" customHeight="1" spans="1:11">
       <c r="A189" s="7" t="s">
         <v>50</v>
       </c>
@@ -7344,7 +7344,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="190" customHeight="1" spans="1:11">
+    <row r="190" hidden="1" customHeight="1" spans="1:11">
       <c r="A190" s="7" t="s">
         <v>50</v>
       </c>
@@ -7373,7 +7373,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="191" customHeight="1" spans="1:11">
+    <row r="191" hidden="1" customHeight="1" spans="1:11">
       <c r="A191" s="7" t="s">
         <v>50</v>
       </c>
@@ -7402,7 +7402,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="192" customHeight="1" spans="1:11">
+    <row r="192" hidden="1" customHeight="1" spans="1:11">
       <c r="A192" s="7" t="s">
         <v>50</v>
       </c>
@@ -7428,7 +7428,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="193" customHeight="1" spans="1:11">
+    <row r="193" hidden="1" customHeight="1" spans="1:11">
       <c r="A193" s="7" t="s">
         <v>50</v>
       </c>
@@ -7457,7 +7457,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="194" customHeight="1" spans="1:11">
+    <row r="194" hidden="1" customHeight="1" spans="1:11">
       <c r="A194" s="7" t="s">
         <v>53</v>
       </c>
@@ -7486,7 +7486,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="195" customHeight="1" spans="1:11">
+    <row r="195" hidden="1" customHeight="1" spans="1:11">
       <c r="A195" s="7" t="s">
         <v>53</v>
       </c>
@@ -7515,7 +7515,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="196" customHeight="1" spans="1:11">
+    <row r="196" hidden="1" customHeight="1" spans="1:11">
       <c r="A196" s="7" t="s">
         <v>53</v>
       </c>
@@ -7544,7 +7544,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="197" customHeight="1" spans="1:11">
+    <row r="197" hidden="1" customHeight="1" spans="1:11">
       <c r="A197" s="7" t="s">
         <v>53</v>
       </c>
@@ -7573,7 +7573,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="198" customHeight="1" spans="1:11">
+    <row r="198" hidden="1" customHeight="1" spans="1:11">
       <c r="A198" s="7" t="s">
         <v>53</v>
       </c>
@@ -7602,7 +7602,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="199" customHeight="1" spans="1:11">
+    <row r="199" hidden="1" customHeight="1" spans="1:11">
       <c r="A199" s="7" t="s">
         <v>53</v>
       </c>
@@ -7631,7 +7631,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="200" customHeight="1" spans="1:11">
+    <row r="200" hidden="1" customHeight="1" spans="1:11">
       <c r="A200" s="7" t="s">
         <v>53</v>
       </c>
@@ -7660,7 +7660,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="201" customHeight="1" spans="1:11">
+    <row r="201" hidden="1" customHeight="1" spans="1:11">
       <c r="A201" s="7" t="s">
         <v>53</v>
       </c>
@@ -7686,7 +7686,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="202" customHeight="1" spans="1:11">
+    <row r="202" hidden="1" customHeight="1" spans="1:11">
       <c r="A202" s="7" t="s">
         <v>53</v>
       </c>
@@ -7715,7 +7715,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="203" customHeight="1" spans="1:11">
+    <row r="203" hidden="1" customHeight="1" spans="1:11">
       <c r="A203" s="7" t="s">
         <v>53</v>
       </c>
@@ -7744,7 +7744,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="204" customHeight="1" spans="1:11">
+    <row r="204" hidden="1" customHeight="1" spans="1:11">
       <c r="A204" s="7" t="s">
         <v>53</v>
       </c>
@@ -7773,7 +7773,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="205" customHeight="1" spans="1:11">
+    <row r="205" hidden="1" customHeight="1" spans="1:11">
       <c r="A205" s="7" t="s">
         <v>53</v>
       </c>
@@ -7799,7 +7799,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="206" customHeight="1" spans="1:11">
+    <row r="206" hidden="1" customHeight="1" spans="1:11">
       <c r="A206" s="7" t="s">
         <v>53</v>
       </c>
@@ -7828,7 +7828,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="207" customHeight="1" spans="1:11">
+    <row r="207" hidden="1" customHeight="1" spans="1:11">
       <c r="A207" s="7" t="s">
         <v>53</v>
       </c>
@@ -7854,7 +7854,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="208" customHeight="1" spans="1:11">
+    <row r="208" hidden="1" customHeight="1" spans="1:11">
       <c r="A208" s="7" t="s">
         <v>53</v>
       </c>
@@ -7880,7 +7880,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="209" customHeight="1" spans="1:11">
+    <row r="209" hidden="1" customHeight="1" spans="1:11">
       <c r="A209" s="7" t="s">
         <v>53</v>
       </c>
@@ -7909,7 +7909,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="210" customHeight="1" spans="1:11">
+    <row r="210" hidden="1" customHeight="1" spans="1:11">
       <c r="A210" s="7" t="s">
         <v>53</v>
       </c>
@@ -7938,7 +7938,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="211" customHeight="1" spans="1:11">
+    <row r="211" hidden="1" customHeight="1" spans="1:11">
       <c r="A211" s="7" t="s">
         <v>53</v>
       </c>
@@ -7964,7 +7964,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="212" customHeight="1" spans="1:11">
+    <row r="212" hidden="1" customHeight="1" spans="1:11">
       <c r="A212" s="7" t="s">
         <v>53</v>
       </c>
@@ -7990,7 +7990,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="213" customHeight="1" spans="1:11">
+    <row r="213" hidden="1" customHeight="1" spans="1:11">
       <c r="A213" s="7" t="s">
         <v>53</v>
       </c>
@@ -8019,7 +8019,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="214" customHeight="1" spans="1:11">
+    <row r="214" hidden="1" customHeight="1" spans="1:11">
       <c r="A214" s="7" t="s">
         <v>53</v>
       </c>
@@ -8048,7 +8048,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="215" customHeight="1" spans="1:11">
+    <row r="215" hidden="1" customHeight="1" spans="1:11">
       <c r="A215" s="7" t="s">
         <v>53</v>
       </c>
@@ -8074,7 +8074,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="216" customHeight="1" spans="1:11">
+    <row r="216" hidden="1" customHeight="1" spans="1:11">
       <c r="A216" s="7" t="s">
         <v>53</v>
       </c>
@@ -8100,7 +8100,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="217" customHeight="1" spans="1:11">
+    <row r="217" hidden="1" customHeight="1" spans="1:11">
       <c r="A217" s="7" t="s">
         <v>53</v>
       </c>
@@ -8129,7 +8129,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="218" customHeight="1" spans="1:11">
+    <row r="218" hidden="1" customHeight="1" spans="1:11">
       <c r="A218" s="8" t="s">
         <v>12</v>
       </c>
@@ -8160,7 +8160,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="219" customHeight="1" spans="1:11">
+    <row r="219" hidden="1" customHeight="1" spans="1:11">
       <c r="A219" s="7" t="s">
         <v>12</v>
       </c>
@@ -8189,7 +8189,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="220" customHeight="1" spans="1:11">
+    <row r="220" hidden="1" customHeight="1" spans="1:11">
       <c r="A220" s="7" t="s">
         <v>12</v>
       </c>
@@ -8218,7 +8218,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="221" customHeight="1" spans="1:11">
+    <row r="221" hidden="1" customHeight="1" spans="1:11">
       <c r="A221" s="7" t="s">
         <v>12</v>
       </c>
@@ -8247,7 +8247,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="222" customHeight="1" spans="1:11">
+    <row r="222" hidden="1" customHeight="1" spans="1:11">
       <c r="A222" s="7" t="s">
         <v>12</v>
       </c>
@@ -8276,7 +8276,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="223" customHeight="1" spans="1:11">
+    <row r="223" hidden="1" customHeight="1" spans="1:11">
       <c r="A223" s="7" t="s">
         <v>12</v>
       </c>
@@ -8305,7 +8305,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="224" customHeight="1" spans="1:11">
+    <row r="224" hidden="1" customHeight="1" spans="1:11">
       <c r="A224" s="7" t="s">
         <v>12</v>
       </c>
@@ -8334,7 +8334,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="225" customHeight="1" spans="1:11">
+    <row r="225" hidden="1" customHeight="1" spans="1:11">
       <c r="A225" s="7" t="s">
         <v>12</v>
       </c>
@@ -8363,7 +8363,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="226" customHeight="1" spans="1:11">
+    <row r="226" hidden="1" customHeight="1" spans="1:11">
       <c r="A226" s="7" t="s">
         <v>12</v>
       </c>
@@ -8392,7 +8392,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="227" customHeight="1" spans="1:11">
+    <row r="227" hidden="1" customHeight="1" spans="1:11">
       <c r="A227" s="7" t="s">
         <v>12</v>
       </c>
@@ -8421,7 +8421,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="228" customHeight="1" spans="1:11">
+    <row r="228" hidden="1" customHeight="1" spans="1:11">
       <c r="A228" s="7" t="s">
         <v>12</v>
       </c>
@@ -8450,7 +8450,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="229" customHeight="1" spans="1:11">
+    <row r="229" hidden="1" customHeight="1" spans="1:11">
       <c r="A229" s="7" t="s">
         <v>12</v>
       </c>
@@ -8479,7 +8479,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="230" customHeight="1" spans="1:11">
+    <row r="230" hidden="1" customHeight="1" spans="1:11">
       <c r="A230" s="7" t="s">
         <v>12</v>
       </c>
@@ -8508,7 +8508,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="231" customHeight="1" spans="1:11">
+    <row r="231" hidden="1" customHeight="1" spans="1:11">
       <c r="A231" s="7" t="s">
         <v>12</v>
       </c>
@@ -8537,7 +8537,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="232" customHeight="1" spans="1:11">
+    <row r="232" hidden="1" customHeight="1" spans="1:11">
       <c r="A232" s="7" t="s">
         <v>12</v>
       </c>
@@ -8566,7 +8566,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="233" customHeight="1" spans="1:11">
+    <row r="233" hidden="1" customHeight="1" spans="1:11">
       <c r="A233" s="7" t="s">
         <v>12</v>
       </c>
@@ -8595,7 +8595,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="234" customHeight="1" spans="1:11">
+    <row r="234" hidden="1" customHeight="1" spans="1:11">
       <c r="A234" s="7" t="s">
         <v>12</v>
       </c>
@@ -8624,7 +8624,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="235" customHeight="1" spans="1:11">
+    <row r="235" hidden="1" customHeight="1" spans="1:11">
       <c r="A235" s="7" t="s">
         <v>12</v>
       </c>
@@ -8653,7 +8653,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="236" customHeight="1" spans="1:11">
+    <row r="236" hidden="1" customHeight="1" spans="1:11">
       <c r="A236" s="7" t="s">
         <v>12</v>
       </c>
@@ -8679,7 +8679,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="237" customHeight="1" spans="1:11">
+    <row r="237" hidden="1" customHeight="1" spans="1:11">
       <c r="A237" s="7" t="s">
         <v>12</v>
       </c>
@@ -8708,7 +8708,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="238" customHeight="1" spans="1:11">
+    <row r="238" hidden="1" customHeight="1" spans="1:11">
       <c r="A238" s="7" t="s">
         <v>12</v>
       </c>
@@ -8737,7 +8737,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="239" customHeight="1" spans="1:11">
+    <row r="239" hidden="1" customHeight="1" spans="1:11">
       <c r="A239" s="7" t="s">
         <v>12</v>
       </c>
@@ -8766,7 +8766,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="240" customHeight="1" spans="1:11">
+    <row r="240" hidden="1" customHeight="1" spans="1:11">
       <c r="A240" s="7" t="s">
         <v>12</v>
       </c>
@@ -8792,7 +8792,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="241" customHeight="1" spans="1:11">
+    <row r="241" hidden="1" customHeight="1" spans="1:11">
       <c r="A241" s="7" t="s">
         <v>12</v>
       </c>
@@ -8821,7 +8821,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="242" customHeight="1" spans="1:11">
+    <row r="242" hidden="1" customHeight="1" spans="1:11">
       <c r="A242" s="7" t="s">
         <v>50</v>
       </c>
@@ -8850,7 +8850,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="243" customHeight="1" spans="1:11">
+    <row r="243" hidden="1" customHeight="1" spans="1:11">
       <c r="A243" s="7" t="s">
         <v>50</v>
       </c>
@@ -8879,7 +8879,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="244" customHeight="1" spans="1:11">
+    <row r="244" hidden="1" customHeight="1" spans="1:11">
       <c r="A244" s="7" t="s">
         <v>50</v>
       </c>
@@ -8908,7 +8908,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="245" customHeight="1" spans="1:11">
+    <row r="245" hidden="1" customHeight="1" spans="1:11">
       <c r="A245" s="7" t="s">
         <v>50</v>
       </c>
@@ -8937,7 +8937,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="246" customHeight="1" spans="1:11">
+    <row r="246" hidden="1" customHeight="1" spans="1:11">
       <c r="A246" s="7" t="s">
         <v>50</v>
       </c>
@@ -8966,7 +8966,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="247" customHeight="1" spans="1:11">
+    <row r="247" hidden="1" customHeight="1" spans="1:11">
       <c r="A247" s="7" t="s">
         <v>50</v>
       </c>
@@ -8995,7 +8995,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="248" customHeight="1" spans="1:11">
+    <row r="248" hidden="1" customHeight="1" spans="1:11">
       <c r="A248" s="7" t="s">
         <v>50</v>
       </c>
@@ -9024,7 +9024,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="249" customHeight="1" spans="1:11">
+    <row r="249" hidden="1" customHeight="1" spans="1:11">
       <c r="A249" s="7" t="s">
         <v>50</v>
       </c>
@@ -9053,7 +9053,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="250" customHeight="1" spans="1:11">
+    <row r="250" hidden="1" customHeight="1" spans="1:11">
       <c r="A250" s="7" t="s">
         <v>50</v>
       </c>
@@ -9082,7 +9082,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="251" customHeight="1" spans="1:11">
+    <row r="251" hidden="1" customHeight="1" spans="1:11">
       <c r="A251" s="7" t="s">
         <v>50</v>
       </c>
@@ -9111,7 +9111,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="252" customHeight="1" spans="1:11">
+    <row r="252" hidden="1" customHeight="1" spans="1:11">
       <c r="A252" s="7" t="s">
         <v>50</v>
       </c>
@@ -9140,7 +9140,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="253" customHeight="1" spans="1:11">
+    <row r="253" hidden="1" customHeight="1" spans="1:11">
       <c r="A253" s="7" t="s">
         <v>50</v>
       </c>
@@ -9169,7 +9169,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="254" customHeight="1" spans="1:11">
+    <row r="254" hidden="1" customHeight="1" spans="1:11">
       <c r="A254" s="7" t="s">
         <v>50</v>
       </c>
@@ -9198,7 +9198,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="255" customHeight="1" spans="1:11">
+    <row r="255" hidden="1" customHeight="1" spans="1:11">
       <c r="A255" s="7" t="s">
         <v>50</v>
       </c>
@@ -9227,7 +9227,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="256" customHeight="1" spans="1:11">
+    <row r="256" hidden="1" customHeight="1" spans="1:11">
       <c r="A256" s="7" t="s">
         <v>50</v>
       </c>
@@ -9256,7 +9256,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="257" customHeight="1" spans="1:11">
+    <row r="257" hidden="1" customHeight="1" spans="1:11">
       <c r="A257" s="7" t="s">
         <v>50</v>
       </c>
@@ -9285,7 +9285,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="258" customHeight="1" spans="1:11">
+    <row r="258" hidden="1" customHeight="1" spans="1:11">
       <c r="A258" s="7" t="s">
         <v>50</v>
       </c>
@@ -9314,7 +9314,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="259" customHeight="1" spans="1:11">
+    <row r="259" hidden="1" customHeight="1" spans="1:11">
       <c r="A259" s="7" t="s">
         <v>50</v>
       </c>
@@ -9343,7 +9343,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="260" customHeight="1" spans="1:11">
+    <row r="260" hidden="1" customHeight="1" spans="1:11">
       <c r="A260" s="7" t="s">
         <v>50</v>
       </c>
@@ -9369,7 +9369,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="261" customHeight="1" spans="1:11">
+    <row r="261" hidden="1" customHeight="1" spans="1:11">
       <c r="A261" s="7" t="s">
         <v>50</v>
       </c>
@@ -9398,7 +9398,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="262" customHeight="1" spans="1:11">
+    <row r="262" hidden="1" customHeight="1" spans="1:11">
       <c r="A262" s="7" t="s">
         <v>50</v>
       </c>
@@ -9427,7 +9427,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="263" customHeight="1" spans="1:11">
+    <row r="263" hidden="1" customHeight="1" spans="1:11">
       <c r="A263" s="7" t="s">
         <v>50</v>
       </c>
@@ -9456,7 +9456,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="264" customHeight="1" spans="1:11">
+    <row r="264" hidden="1" customHeight="1" spans="1:11">
       <c r="A264" s="7" t="s">
         <v>50</v>
       </c>
@@ -9482,7 +9482,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="265" customHeight="1" spans="1:11">
+    <row r="265" hidden="1" customHeight="1" spans="1:11">
       <c r="A265" s="7" t="s">
         <v>50</v>
       </c>
@@ -9511,7 +9511,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="266" customHeight="1" spans="1:11">
+    <row r="266" hidden="1" customHeight="1" spans="1:11">
       <c r="A266" s="7" t="s">
         <v>53</v>
       </c>
@@ -9540,7 +9540,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="267" customHeight="1" spans="1:11">
+    <row r="267" hidden="1" customHeight="1" spans="1:11">
       <c r="A267" s="7" t="s">
         <v>53</v>
       </c>
@@ -9569,7 +9569,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="268" customHeight="1" spans="1:11">
+    <row r="268" hidden="1" customHeight="1" spans="1:11">
       <c r="A268" s="7" t="s">
         <v>53</v>
       </c>
@@ -9598,7 +9598,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="269" customHeight="1" spans="1:11">
+    <row r="269" hidden="1" customHeight="1" spans="1:11">
       <c r="A269" s="7" t="s">
         <v>53</v>
       </c>
@@ -9627,7 +9627,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="270" customHeight="1" spans="1:11">
+    <row r="270" hidden="1" customHeight="1" spans="1:11">
       <c r="A270" s="7" t="s">
         <v>53</v>
       </c>
@@ -9656,7 +9656,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="271" customHeight="1" spans="1:11">
+    <row r="271" hidden="1" customHeight="1" spans="1:11">
       <c r="A271" s="7" t="s">
         <v>53</v>
       </c>
@@ -9685,7 +9685,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="272" customHeight="1" spans="1:11">
+    <row r="272" hidden="1" customHeight="1" spans="1:11">
       <c r="A272" s="7" t="s">
         <v>53</v>
       </c>
@@ -9714,7 +9714,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="273" customHeight="1" spans="1:11">
+    <row r="273" hidden="1" customHeight="1" spans="1:11">
       <c r="A273" s="7" t="s">
         <v>53</v>
       </c>
@@ -9740,7 +9740,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="274" customHeight="1" spans="1:11">
+    <row r="274" hidden="1" customHeight="1" spans="1:11">
       <c r="A274" s="7" t="s">
         <v>53</v>
       </c>
@@ -9769,7 +9769,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="275" customHeight="1" spans="1:11">
+    <row r="275" hidden="1" customHeight="1" spans="1:11">
       <c r="A275" s="7" t="s">
         <v>53</v>
       </c>
@@ -9798,7 +9798,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="276" customHeight="1" spans="1:11">
+    <row r="276" hidden="1" customHeight="1" spans="1:11">
       <c r="A276" s="7" t="s">
         <v>53</v>
       </c>
@@ -9827,7 +9827,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="277" customHeight="1" spans="1:11">
+    <row r="277" hidden="1" customHeight="1" spans="1:11">
       <c r="A277" s="7" t="s">
         <v>53</v>
       </c>
@@ -9853,7 +9853,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="278" customHeight="1" spans="1:11">
+    <row r="278" hidden="1" customHeight="1" spans="1:11">
       <c r="A278" s="7" t="s">
         <v>53</v>
       </c>
@@ -9882,7 +9882,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="279" customHeight="1" spans="1:11">
+    <row r="279" hidden="1" customHeight="1" spans="1:11">
       <c r="A279" s="7" t="s">
         <v>53</v>
       </c>
@@ -9908,7 +9908,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="280" customHeight="1" spans="1:11">
+    <row r="280" hidden="1" customHeight="1" spans="1:11">
       <c r="A280" s="7" t="s">
         <v>53</v>
       </c>
@@ -9934,7 +9934,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="281" customHeight="1" spans="1:11">
+    <row r="281" hidden="1" customHeight="1" spans="1:11">
       <c r="A281" s="7" t="s">
         <v>53</v>
       </c>
@@ -9963,7 +9963,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="282" customHeight="1" spans="1:11">
+    <row r="282" hidden="1" customHeight="1" spans="1:11">
       <c r="A282" s="7" t="s">
         <v>53</v>
       </c>
@@ -9992,7 +9992,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="283" customHeight="1" spans="1:11">
+    <row r="283" hidden="1" customHeight="1" spans="1:11">
       <c r="A283" s="7" t="s">
         <v>53</v>
       </c>
@@ -10018,7 +10018,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="284" customHeight="1" spans="1:11">
+    <row r="284" hidden="1" customHeight="1" spans="1:11">
       <c r="A284" s="7" t="s">
         <v>53</v>
       </c>
@@ -10044,7 +10044,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="285" customHeight="1" spans="1:11">
+    <row r="285" hidden="1" customHeight="1" spans="1:11">
       <c r="A285" s="7" t="s">
         <v>53</v>
       </c>
@@ -10073,7 +10073,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="286" customHeight="1" spans="1:11">
+    <row r="286" hidden="1" customHeight="1" spans="1:11">
       <c r="A286" s="7" t="s">
         <v>53</v>
       </c>
@@ -10102,7 +10102,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="287" customHeight="1" spans="1:11">
+    <row r="287" hidden="1" customHeight="1" spans="1:11">
       <c r="A287" s="7" t="s">
         <v>53</v>
       </c>
@@ -10128,7 +10128,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="288" customHeight="1" spans="1:11">
+    <row r="288" hidden="1" customHeight="1" spans="1:11">
       <c r="A288" s="7" t="s">
         <v>53</v>
       </c>
@@ -10154,7 +10154,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="289" customHeight="1" spans="1:11">
+    <row r="289" hidden="1" customHeight="1" spans="1:11">
       <c r="A289" s="7" t="s">
         <v>53</v>
       </c>
@@ -10183,7 +10183,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="290" customHeight="1" spans="1:11">
+    <row r="290" hidden="1" customHeight="1" spans="1:11">
       <c r="A290" s="8" t="s">
         <v>12</v>
       </c>
@@ -10214,7 +10214,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="291" customHeight="1" spans="1:11">
+    <row r="291" hidden="1" customHeight="1" spans="1:11">
       <c r="A291" s="7" t="s">
         <v>12</v>
       </c>
@@ -10243,7 +10243,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="292" customHeight="1" spans="1:11">
+    <row r="292" hidden="1" customHeight="1" spans="1:11">
       <c r="A292" s="7" t="s">
         <v>12</v>
       </c>
@@ -10272,7 +10272,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="293" customHeight="1" spans="1:11">
+    <row r="293" hidden="1" customHeight="1" spans="1:11">
       <c r="A293" s="7" t="s">
         <v>12</v>
       </c>
@@ -10301,7 +10301,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="294" customHeight="1" spans="1:11">
+    <row r="294" hidden="1" customHeight="1" spans="1:11">
       <c r="A294" s="7" t="s">
         <v>12</v>
       </c>
@@ -10330,7 +10330,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="295" customHeight="1" spans="1:11">
+    <row r="295" hidden="1" customHeight="1" spans="1:11">
       <c r="A295" s="7" t="s">
         <v>12</v>
       </c>
@@ -10359,7 +10359,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="296" customHeight="1" spans="1:11">
+    <row r="296" hidden="1" customHeight="1" spans="1:11">
       <c r="A296" s="7" t="s">
         <v>12</v>
       </c>
@@ -10388,7 +10388,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="297" customHeight="1" spans="1:11">
+    <row r="297" hidden="1" customHeight="1" spans="1:11">
       <c r="A297" s="7" t="s">
         <v>12</v>
       </c>
@@ -10417,7 +10417,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="298" customHeight="1" spans="1:11">
+    <row r="298" hidden="1" customHeight="1" spans="1:11">
       <c r="A298" s="7" t="s">
         <v>12</v>
       </c>
@@ -10446,7 +10446,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="299" customHeight="1" spans="1:11">
+    <row r="299" hidden="1" customHeight="1" spans="1:11">
       <c r="A299" s="7" t="s">
         <v>12</v>
       </c>
@@ -10475,7 +10475,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="300" customHeight="1" spans="1:11">
+    <row r="300" hidden="1" customHeight="1" spans="1:11">
       <c r="A300" s="7" t="s">
         <v>12</v>
       </c>
@@ -10504,7 +10504,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="301" customHeight="1" spans="1:11">
+    <row r="301" hidden="1" customHeight="1" spans="1:11">
       <c r="A301" s="7" t="s">
         <v>12</v>
       </c>
@@ -10533,7 +10533,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="302" customHeight="1" spans="1:11">
+    <row r="302" hidden="1" customHeight="1" spans="1:11">
       <c r="A302" s="7" t="s">
         <v>12</v>
       </c>
@@ -10562,7 +10562,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="303" customHeight="1" spans="1:11">
+    <row r="303" hidden="1" customHeight="1" spans="1:11">
       <c r="A303" s="7" t="s">
         <v>12</v>
       </c>
@@ -10591,7 +10591,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="304" customHeight="1" spans="1:11">
+    <row r="304" hidden="1" customHeight="1" spans="1:11">
       <c r="A304" s="7" t="s">
         <v>12</v>
       </c>
@@ -10620,7 +10620,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="305" customHeight="1" spans="1:11">
+    <row r="305" hidden="1" customHeight="1" spans="1:11">
       <c r="A305" s="7" t="s">
         <v>12</v>
       </c>
@@ -10649,7 +10649,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="306" customHeight="1" spans="1:11">
+    <row r="306" hidden="1" customHeight="1" spans="1:11">
       <c r="A306" s="7" t="s">
         <v>12</v>
       </c>
@@ -10678,7 +10678,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="307" customHeight="1" spans="1:11">
+    <row r="307" hidden="1" customHeight="1" spans="1:11">
       <c r="A307" s="7" t="s">
         <v>12</v>
       </c>
@@ -10707,7 +10707,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="308" customHeight="1" spans="1:11">
+    <row r="308" hidden="1" customHeight="1" spans="1:11">
       <c r="A308" s="7" t="s">
         <v>12</v>
       </c>
@@ -10733,7 +10733,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="309" customHeight="1" spans="1:11">
+    <row r="309" hidden="1" customHeight="1" spans="1:11">
       <c r="A309" s="7" t="s">
         <v>12</v>
       </c>
@@ -10762,7 +10762,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="310" customHeight="1" spans="1:11">
+    <row r="310" hidden="1" customHeight="1" spans="1:11">
       <c r="A310" s="7" t="s">
         <v>12</v>
       </c>
@@ -10791,7 +10791,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="311" customHeight="1" spans="1:11">
+    <row r="311" hidden="1" customHeight="1" spans="1:11">
       <c r="A311" s="7" t="s">
         <v>12</v>
       </c>
@@ -10820,7 +10820,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="312" customHeight="1" spans="1:11">
+    <row r="312" hidden="1" customHeight="1" spans="1:11">
       <c r="A312" s="7" t="s">
         <v>12</v>
       </c>
@@ -10846,7 +10846,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="313" customHeight="1" spans="1:11">
+    <row r="313" hidden="1" customHeight="1" spans="1:11">
       <c r="A313" s="7" t="s">
         <v>12</v>
       </c>
@@ -10875,7 +10875,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="314" customHeight="1" spans="1:11">
+    <row r="314" hidden="1" customHeight="1" spans="1:11">
       <c r="A314" s="7" t="s">
         <v>50</v>
       </c>
@@ -10904,7 +10904,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="315" customHeight="1" spans="1:11">
+    <row r="315" hidden="1" customHeight="1" spans="1:11">
       <c r="A315" s="7" t="s">
         <v>50</v>
       </c>
@@ -10933,7 +10933,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="316" customHeight="1" spans="1:11">
+    <row r="316" hidden="1" customHeight="1" spans="1:11">
       <c r="A316" s="7" t="s">
         <v>50</v>
       </c>
@@ -10962,7 +10962,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="317" customHeight="1" spans="1:11">
+    <row r="317" hidden="1" customHeight="1" spans="1:11">
       <c r="A317" s="7" t="s">
         <v>50</v>
       </c>
@@ -10991,7 +10991,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="318" customHeight="1" spans="1:11">
+    <row r="318" hidden="1" customHeight="1" spans="1:11">
       <c r="A318" s="7" t="s">
         <v>50</v>
       </c>
@@ -11020,7 +11020,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="319" customHeight="1" spans="1:11">
+    <row r="319" hidden="1" customHeight="1" spans="1:11">
       <c r="A319" s="7" t="s">
         <v>50</v>
       </c>
@@ -11049,7 +11049,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="320" customHeight="1" spans="1:11">
+    <row r="320" hidden="1" customHeight="1" spans="1:11">
       <c r="A320" s="7" t="s">
         <v>50</v>
       </c>
@@ -11078,7 +11078,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="321" customHeight="1" spans="1:11">
+    <row r="321" hidden="1" customHeight="1" spans="1:11">
       <c r="A321" s="7" t="s">
         <v>50</v>
       </c>
@@ -11107,7 +11107,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="322" customHeight="1" spans="1:11">
+    <row r="322" hidden="1" customHeight="1" spans="1:11">
       <c r="A322" s="7" t="s">
         <v>50</v>
       </c>
@@ -11136,7 +11136,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="323" customHeight="1" spans="1:11">
+    <row r="323" hidden="1" customHeight="1" spans="1:11">
       <c r="A323" s="7" t="s">
         <v>50</v>
       </c>
@@ -11165,7 +11165,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="324" customHeight="1" spans="1:11">
+    <row r="324" hidden="1" customHeight="1" spans="1:11">
       <c r="A324" s="7" t="s">
         <v>50</v>
       </c>
@@ -11194,7 +11194,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="325" customHeight="1" spans="1:11">
+    <row r="325" hidden="1" customHeight="1" spans="1:11">
       <c r="A325" s="7" t="s">
         <v>50</v>
       </c>
@@ -11223,7 +11223,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="326" customHeight="1" spans="1:11">
+    <row r="326" hidden="1" customHeight="1" spans="1:11">
       <c r="A326" s="7" t="s">
         <v>50</v>
       </c>
@@ -11252,7 +11252,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="327" customHeight="1" spans="1:11">
+    <row r="327" hidden="1" customHeight="1" spans="1:11">
       <c r="A327" s="7" t="s">
         <v>50</v>
       </c>
@@ -11281,7 +11281,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="328" customHeight="1" spans="1:11">
+    <row r="328" hidden="1" customHeight="1" spans="1:11">
       <c r="A328" s="7" t="s">
         <v>50</v>
       </c>
@@ -11310,7 +11310,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="329" customHeight="1" spans="1:11">
+    <row r="329" hidden="1" customHeight="1" spans="1:11">
       <c r="A329" s="7" t="s">
         <v>50</v>
       </c>
@@ -11339,7 +11339,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="330" customHeight="1" spans="1:11">
+    <row r="330" hidden="1" customHeight="1" spans="1:11">
       <c r="A330" s="7" t="s">
         <v>50</v>
       </c>
@@ -11368,7 +11368,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="331" customHeight="1" spans="1:11">
+    <row r="331" hidden="1" customHeight="1" spans="1:11">
       <c r="A331" s="7" t="s">
         <v>50</v>
       </c>
@@ -11397,7 +11397,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="332" customHeight="1" spans="1:11">
+    <row r="332" hidden="1" customHeight="1" spans="1:11">
       <c r="A332" s="7" t="s">
         <v>50</v>
       </c>
@@ -11423,7 +11423,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="333" customHeight="1" spans="1:11">
+    <row r="333" hidden="1" customHeight="1" spans="1:11">
       <c r="A333" s="7" t="s">
         <v>50</v>
       </c>
@@ -11452,7 +11452,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="334" customHeight="1" spans="1:11">
+    <row r="334" hidden="1" customHeight="1" spans="1:11">
       <c r="A334" s="7" t="s">
         <v>50</v>
       </c>
@@ -11481,7 +11481,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="335" customHeight="1" spans="1:11">
+    <row r="335" hidden="1" customHeight="1" spans="1:11">
       <c r="A335" s="7" t="s">
         <v>50</v>
       </c>
@@ -11510,7 +11510,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="336" customHeight="1" spans="1:11">
+    <row r="336" hidden="1" customHeight="1" spans="1:11">
       <c r="A336" s="7" t="s">
         <v>50</v>
       </c>
@@ -11536,7 +11536,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="337" customHeight="1" spans="1:11">
+    <row r="337" hidden="1" customHeight="1" spans="1:11">
       <c r="A337" s="7" t="s">
         <v>50</v>
       </c>
@@ -11565,7 +11565,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="338" customHeight="1" spans="1:11">
+    <row r="338" hidden="1" customHeight="1" spans="1:11">
       <c r="A338" s="7" t="s">
         <v>53</v>
       </c>
@@ -11594,7 +11594,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="339" customHeight="1" spans="1:11">
+    <row r="339" hidden="1" customHeight="1" spans="1:11">
       <c r="A339" s="7" t="s">
         <v>53</v>
       </c>
@@ -11623,7 +11623,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="340" customHeight="1" spans="1:11">
+    <row r="340" hidden="1" customHeight="1" spans="1:11">
       <c r="A340" s="7" t="s">
         <v>53</v>
       </c>
@@ -11652,7 +11652,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="341" customHeight="1" spans="1:11">
+    <row r="341" hidden="1" customHeight="1" spans="1:11">
       <c r="A341" s="7" t="s">
         <v>53</v>
       </c>
@@ -11681,7 +11681,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="342" customHeight="1" spans="1:11">
+    <row r="342" hidden="1" customHeight="1" spans="1:11">
       <c r="A342" s="7" t="s">
         <v>53</v>
       </c>
@@ -11710,7 +11710,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="343" customHeight="1" spans="1:11">
+    <row r="343" hidden="1" customHeight="1" spans="1:11">
       <c r="A343" s="7" t="s">
         <v>53</v>
       </c>
@@ -11739,7 +11739,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="344" customHeight="1" spans="1:11">
+    <row r="344" hidden="1" customHeight="1" spans="1:11">
       <c r="A344" s="7" t="s">
         <v>53</v>
       </c>
@@ -11768,7 +11768,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="345" customHeight="1" spans="1:11">
+    <row r="345" hidden="1" customHeight="1" spans="1:11">
       <c r="A345" s="7" t="s">
         <v>53</v>
       </c>
@@ -11794,7 +11794,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="346" customHeight="1" spans="1:11">
+    <row r="346" hidden="1" customHeight="1" spans="1:11">
       <c r="A346" s="7" t="s">
         <v>53</v>
       </c>
@@ -11823,7 +11823,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="347" customHeight="1" spans="1:11">
+    <row r="347" hidden="1" customHeight="1" spans="1:11">
       <c r="A347" s="7" t="s">
         <v>53</v>
       </c>
@@ -11852,7 +11852,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="348" customHeight="1" spans="1:11">
+    <row r="348" hidden="1" customHeight="1" spans="1:11">
       <c r="A348" s="7" t="s">
         <v>53</v>
       </c>
@@ -11881,7 +11881,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="349" customHeight="1" spans="1:11">
+    <row r="349" hidden="1" customHeight="1" spans="1:11">
       <c r="A349" s="7" t="s">
         <v>53</v>
       </c>
@@ -11907,7 +11907,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="350" customHeight="1" spans="1:11">
+    <row r="350" hidden="1" customHeight="1" spans="1:11">
       <c r="A350" s="7" t="s">
         <v>53</v>
       </c>
@@ -11936,7 +11936,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="351" customHeight="1" spans="1:11">
+    <row r="351" hidden="1" customHeight="1" spans="1:11">
       <c r="A351" s="7" t="s">
         <v>53</v>
       </c>
@@ -11962,7 +11962,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="352" customHeight="1" spans="1:11">
+    <row r="352" hidden="1" customHeight="1" spans="1:11">
       <c r="A352" s="7" t="s">
         <v>53</v>
       </c>
@@ -11988,7 +11988,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="353" customHeight="1" spans="1:11">
+    <row r="353" hidden="1" customHeight="1" spans="1:11">
       <c r="A353" s="7" t="s">
         <v>53</v>
       </c>
@@ -12017,7 +12017,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="354" customHeight="1" spans="1:11">
+    <row r="354" hidden="1" customHeight="1" spans="1:11">
       <c r="A354" s="7" t="s">
         <v>53</v>
       </c>
@@ -12046,7 +12046,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="355" customHeight="1" spans="1:11">
+    <row r="355" hidden="1" customHeight="1" spans="1:11">
       <c r="A355" s="7" t="s">
         <v>53</v>
       </c>
@@ -12072,7 +12072,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="356" customHeight="1" spans="1:11">
+    <row r="356" hidden="1" customHeight="1" spans="1:11">
       <c r="A356" s="7" t="s">
         <v>53</v>
       </c>
@@ -12098,7 +12098,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="357" customHeight="1" spans="1:11">
+    <row r="357" hidden="1" customHeight="1" spans="1:11">
       <c r="A357" s="7" t="s">
         <v>53</v>
       </c>
@@ -12127,7 +12127,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="358" customHeight="1" spans="1:11">
+    <row r="358" hidden="1" customHeight="1" spans="1:11">
       <c r="A358" s="7" t="s">
         <v>53</v>
       </c>
@@ -12156,7 +12156,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="359" customHeight="1" spans="1:11">
+    <row r="359" hidden="1" customHeight="1" spans="1:11">
       <c r="A359" s="7" t="s">
         <v>53</v>
       </c>
@@ -12182,7 +12182,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="360" customHeight="1" spans="1:11">
+    <row r="360" hidden="1" customHeight="1" spans="1:11">
       <c r="A360" s="7" t="s">
         <v>53</v>
       </c>
@@ -12208,7 +12208,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="361" customHeight="1" spans="1:11">
+    <row r="361" hidden="1" customHeight="1" spans="1:11">
       <c r="A361" s="7" t="s">
         <v>53</v>
       </c>
@@ -12237,7 +12237,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="362" customHeight="1" spans="1:11">
+    <row r="362" hidden="1" customHeight="1" spans="1:11">
       <c r="A362" s="8" t="s">
         <v>12</v>
       </c>
@@ -12268,7 +12268,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="363" customHeight="1" spans="1:11">
+    <row r="363" hidden="1" customHeight="1" spans="1:11">
       <c r="A363" s="7" t="s">
         <v>12</v>
       </c>
@@ -12297,7 +12297,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="364" customHeight="1" spans="1:11">
+    <row r="364" hidden="1" customHeight="1" spans="1:11">
       <c r="A364" s="7" t="s">
         <v>12</v>
       </c>
@@ -12326,7 +12326,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="365" customHeight="1" spans="1:11">
+    <row r="365" hidden="1" customHeight="1" spans="1:11">
       <c r="A365" s="7" t="s">
         <v>12</v>
       </c>
@@ -12355,7 +12355,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="366" customHeight="1" spans="1:11">
+    <row r="366" hidden="1" customHeight="1" spans="1:11">
       <c r="A366" s="7" t="s">
         <v>12</v>
       </c>
@@ -12384,7 +12384,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="367" customHeight="1" spans="1:11">
+    <row r="367" hidden="1" customHeight="1" spans="1:11">
       <c r="A367" s="7" t="s">
         <v>12</v>
       </c>
@@ -12413,7 +12413,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="368" customHeight="1" spans="1:11">
+    <row r="368" hidden="1" customHeight="1" spans="1:11">
       <c r="A368" s="7" t="s">
         <v>12</v>
       </c>
@@ -12442,7 +12442,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="369" customHeight="1" spans="1:11">
+    <row r="369" hidden="1" customHeight="1" spans="1:11">
       <c r="A369" s="7" t="s">
         <v>12</v>
       </c>
@@ -12471,7 +12471,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="370" customHeight="1" spans="1:11">
+    <row r="370" hidden="1" customHeight="1" spans="1:11">
       <c r="A370" s="7" t="s">
         <v>12</v>
       </c>
@@ -12500,7 +12500,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="371" customHeight="1" spans="1:11">
+    <row r="371" hidden="1" customHeight="1" spans="1:11">
       <c r="A371" s="7" t="s">
         <v>12</v>
       </c>
@@ -12529,7 +12529,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="372" customHeight="1" spans="1:11">
+    <row r="372" hidden="1" customHeight="1" spans="1:11">
       <c r="A372" s="7" t="s">
         <v>12</v>
       </c>
@@ -12558,7 +12558,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="373" customHeight="1" spans="1:11">
+    <row r="373" hidden="1" customHeight="1" spans="1:11">
       <c r="A373" s="7" t="s">
         <v>12</v>
       </c>
@@ -12587,7 +12587,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="374" customHeight="1" spans="1:11">
+    <row r="374" hidden="1" customHeight="1" spans="1:11">
       <c r="A374" s="7" t="s">
         <v>12</v>
       </c>
@@ -12616,7 +12616,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="375" customHeight="1" spans="1:11">
+    <row r="375" hidden="1" customHeight="1" spans="1:11">
       <c r="A375" s="7" t="s">
         <v>12</v>
       </c>
@@ -12645,7 +12645,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="376" customHeight="1" spans="1:11">
+    <row r="376" hidden="1" customHeight="1" spans="1:11">
       <c r="A376" s="7" t="s">
         <v>12</v>
       </c>
@@ -12674,7 +12674,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="377" customHeight="1" spans="1:11">
+    <row r="377" hidden="1" customHeight="1" spans="1:11">
       <c r="A377" s="7" t="s">
         <v>12</v>
       </c>
@@ -12703,7 +12703,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="378" customHeight="1" spans="1:11">
+    <row r="378" hidden="1" customHeight="1" spans="1:11">
       <c r="A378" s="7" t="s">
         <v>12</v>
       </c>
@@ -12732,7 +12732,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="379" customHeight="1" spans="1:11">
+    <row r="379" hidden="1" customHeight="1" spans="1:11">
       <c r="A379" s="7" t="s">
         <v>12</v>
       </c>
@@ -12761,7 +12761,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="380" customHeight="1" spans="1:11">
+    <row r="380" hidden="1" customHeight="1" spans="1:11">
       <c r="A380" s="7" t="s">
         <v>12</v>
       </c>
@@ -12787,7 +12787,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="381" customHeight="1" spans="1:11">
+    <row r="381" hidden="1" customHeight="1" spans="1:11">
       <c r="A381" s="7" t="s">
         <v>12</v>
       </c>
@@ -12816,7 +12816,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="382" customHeight="1" spans="1:11">
+    <row r="382" hidden="1" customHeight="1" spans="1:11">
       <c r="A382" s="7" t="s">
         <v>12</v>
       </c>
@@ -12845,7 +12845,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="383" customHeight="1" spans="1:11">
+    <row r="383" hidden="1" customHeight="1" spans="1:11">
       <c r="A383" s="7" t="s">
         <v>12</v>
       </c>
@@ -12874,7 +12874,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="384" customHeight="1" spans="1:11">
+    <row r="384" hidden="1" customHeight="1" spans="1:11">
       <c r="A384" s="7" t="s">
         <v>12</v>
       </c>
@@ -12900,7 +12900,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="385" customHeight="1" spans="1:11">
+    <row r="385" hidden="1" customHeight="1" spans="1:11">
       <c r="A385" s="7" t="s">
         <v>12</v>
       </c>
@@ -12929,7 +12929,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="386" customHeight="1" spans="1:11">
+    <row r="386" hidden="1" customHeight="1" spans="1:11">
       <c r="A386" s="7" t="s">
         <v>50</v>
       </c>
@@ -12958,7 +12958,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="387" customHeight="1" spans="1:11">
+    <row r="387" hidden="1" customHeight="1" spans="1:11">
       <c r="A387" s="7" t="s">
         <v>50</v>
       </c>
@@ -12987,7 +12987,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="388" customHeight="1" spans="1:11">
+    <row r="388" hidden="1" customHeight="1" spans="1:11">
       <c r="A388" s="7" t="s">
         <v>50</v>
       </c>
@@ -13016,7 +13016,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="389" customHeight="1" spans="1:11">
+    <row r="389" hidden="1" customHeight="1" spans="1:11">
       <c r="A389" s="7" t="s">
         <v>50</v>
       </c>
@@ -13045,7 +13045,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="390" customHeight="1" spans="1:11">
+    <row r="390" hidden="1" customHeight="1" spans="1:11">
       <c r="A390" s="7" t="s">
         <v>50</v>
       </c>
@@ -13074,7 +13074,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="391" customHeight="1" spans="1:11">
+    <row r="391" hidden="1" customHeight="1" spans="1:11">
       <c r="A391" s="7" t="s">
         <v>50</v>
       </c>
@@ -13103,7 +13103,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="392" customHeight="1" spans="1:11">
+    <row r="392" hidden="1" customHeight="1" spans="1:11">
       <c r="A392" s="7" t="s">
         <v>50</v>
       </c>
@@ -13132,7 +13132,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="393" customHeight="1" spans="1:11">
+    <row r="393" hidden="1" customHeight="1" spans="1:11">
       <c r="A393" s="7" t="s">
         <v>50</v>
       </c>
@@ -13161,7 +13161,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="394" customHeight="1" spans="1:11">
+    <row r="394" hidden="1" customHeight="1" spans="1:11">
       <c r="A394" s="7" t="s">
         <v>50</v>
       </c>
@@ -13190,7 +13190,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="395" customHeight="1" spans="1:11">
+    <row r="395" hidden="1" customHeight="1" spans="1:11">
       <c r="A395" s="7" t="s">
         <v>50</v>
       </c>
@@ -13219,7 +13219,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="396" customHeight="1" spans="1:11">
+    <row r="396" hidden="1" customHeight="1" spans="1:11">
       <c r="A396" s="7" t="s">
         <v>50</v>
       </c>
@@ -13248,7 +13248,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="397" customHeight="1" spans="1:11">
+    <row r="397" hidden="1" customHeight="1" spans="1:11">
       <c r="A397" s="7" t="s">
         <v>50</v>
       </c>
@@ -13277,7 +13277,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="398" customHeight="1" spans="1:11">
+    <row r="398" hidden="1" customHeight="1" spans="1:11">
       <c r="A398" s="7" t="s">
         <v>50</v>
       </c>
@@ -13306,7 +13306,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="399" customHeight="1" spans="1:11">
+    <row r="399" hidden="1" customHeight="1" spans="1:11">
       <c r="A399" s="7" t="s">
         <v>50</v>
       </c>
@@ -13335,7 +13335,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="400" customHeight="1" spans="1:11">
+    <row r="400" hidden="1" customHeight="1" spans="1:11">
       <c r="A400" s="7" t="s">
         <v>50</v>
       </c>
@@ -13364,7 +13364,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="401" customHeight="1" spans="1:11">
+    <row r="401" hidden="1" customHeight="1" spans="1:11">
       <c r="A401" s="7" t="s">
         <v>50</v>
       </c>
@@ -13393,7 +13393,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="402" customHeight="1" spans="1:11">
+    <row r="402" hidden="1" customHeight="1" spans="1:11">
       <c r="A402" s="7" t="s">
         <v>50</v>
       </c>
@@ -13422,7 +13422,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="403" customHeight="1" spans="1:11">
+    <row r="403" hidden="1" customHeight="1" spans="1:11">
       <c r="A403" s="7" t="s">
         <v>50</v>
       </c>
@@ -13451,7 +13451,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="404" customHeight="1" spans="1:11">
+    <row r="404" hidden="1" customHeight="1" spans="1:11">
       <c r="A404" s="7" t="s">
         <v>50</v>
       </c>
@@ -13477,7 +13477,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="405" customHeight="1" spans="1:11">
+    <row r="405" hidden="1" customHeight="1" spans="1:11">
       <c r="A405" s="7" t="s">
         <v>50</v>
       </c>
@@ -13506,7 +13506,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="406" customHeight="1" spans="1:11">
+    <row r="406" hidden="1" customHeight="1" spans="1:11">
       <c r="A406" s="7" t="s">
         <v>50</v>
       </c>
@@ -13535,7 +13535,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="407" customHeight="1" spans="1:11">
+    <row r="407" hidden="1" customHeight="1" spans="1:11">
       <c r="A407" s="7" t="s">
         <v>50</v>
       </c>
@@ -13564,7 +13564,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="408" customHeight="1" spans="1:11">
+    <row r="408" hidden="1" customHeight="1" spans="1:11">
       <c r="A408" s="7" t="s">
         <v>50</v>
       </c>
@@ -13590,7 +13590,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="409" customHeight="1" spans="1:11">
+    <row r="409" hidden="1" customHeight="1" spans="1:11">
       <c r="A409" s="7" t="s">
         <v>50</v>
       </c>
@@ -13619,7 +13619,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="410" customHeight="1" spans="1:11">
+    <row r="410" hidden="1" customHeight="1" spans="1:11">
       <c r="A410" s="7" t="s">
         <v>53</v>
       </c>
@@ -13648,7 +13648,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="411" customHeight="1" spans="1:11">
+    <row r="411" hidden="1" customHeight="1" spans="1:11">
       <c r="A411" s="7" t="s">
         <v>53</v>
       </c>
@@ -13677,7 +13677,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="412" customHeight="1" spans="1:11">
+    <row r="412" hidden="1" customHeight="1" spans="1:11">
       <c r="A412" s="7" t="s">
         <v>53</v>
       </c>
@@ -13706,7 +13706,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="413" customHeight="1" spans="1:11">
+    <row r="413" hidden="1" customHeight="1" spans="1:11">
       <c r="A413" s="7" t="s">
         <v>53</v>
       </c>
@@ -13735,7 +13735,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="414" customHeight="1" spans="1:11">
+    <row r="414" hidden="1" customHeight="1" spans="1:11">
       <c r="A414" s="7" t="s">
         <v>53</v>
       </c>
@@ -13764,7 +13764,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="415" customHeight="1" spans="1:11">
+    <row r="415" hidden="1" customHeight="1" spans="1:11">
       <c r="A415" s="7" t="s">
         <v>53</v>
       </c>
@@ -13793,7 +13793,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="416" customHeight="1" spans="1:11">
+    <row r="416" hidden="1" customHeight="1" spans="1:11">
       <c r="A416" s="7" t="s">
         <v>53</v>
       </c>
@@ -13822,7 +13822,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="417" customHeight="1" spans="1:11">
+    <row r="417" hidden="1" customHeight="1" spans="1:11">
       <c r="A417" s="7" t="s">
         <v>53</v>
       </c>
@@ -13848,7 +13848,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="418" customHeight="1" spans="1:11">
+    <row r="418" hidden="1" customHeight="1" spans="1:11">
       <c r="A418" s="7" t="s">
         <v>53</v>
       </c>
@@ -13877,7 +13877,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="419" customHeight="1" spans="1:11">
+    <row r="419" hidden="1" customHeight="1" spans="1:11">
       <c r="A419" s="7" t="s">
         <v>53</v>
       </c>
@@ -13906,7 +13906,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="420" customHeight="1" spans="1:11">
+    <row r="420" hidden="1" customHeight="1" spans="1:11">
       <c r="A420" s="7" t="s">
         <v>53</v>
       </c>
@@ -13935,7 +13935,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="421" customHeight="1" spans="1:11">
+    <row r="421" hidden="1" customHeight="1" spans="1:11">
       <c r="A421" s="7" t="s">
         <v>53</v>
       </c>
@@ -13961,7 +13961,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="422" customHeight="1" spans="1:11">
+    <row r="422" hidden="1" customHeight="1" spans="1:11">
       <c r="A422" s="7" t="s">
         <v>53</v>
       </c>
@@ -13990,7 +13990,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="423" customHeight="1" spans="1:11">
+    <row r="423" hidden="1" customHeight="1" spans="1:11">
       <c r="A423" s="7" t="s">
         <v>53</v>
       </c>
@@ -14016,7 +14016,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="424" customHeight="1" spans="1:11">
+    <row r="424" hidden="1" customHeight="1" spans="1:11">
       <c r="A424" s="7" t="s">
         <v>53</v>
       </c>
@@ -14042,7 +14042,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="425" customHeight="1" spans="1:11">
+    <row r="425" hidden="1" customHeight="1" spans="1:11">
       <c r="A425" s="7" t="s">
         <v>53</v>
       </c>
@@ -14071,7 +14071,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="426" customHeight="1" spans="1:11">
+    <row r="426" hidden="1" customHeight="1" spans="1:11">
       <c r="A426" s="7" t="s">
         <v>53</v>
       </c>
@@ -14100,7 +14100,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="427" customHeight="1" spans="1:11">
+    <row r="427" hidden="1" customHeight="1" spans="1:11">
       <c r="A427" s="7" t="s">
         <v>53</v>
       </c>
@@ -14126,7 +14126,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="428" customHeight="1" spans="1:11">
+    <row r="428" hidden="1" customHeight="1" spans="1:11">
       <c r="A428" s="7" t="s">
         <v>53</v>
       </c>
@@ -14152,7 +14152,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="429" customHeight="1" spans="1:11">
+    <row r="429" hidden="1" customHeight="1" spans="1:11">
       <c r="A429" s="7" t="s">
         <v>53</v>
       </c>
@@ -14181,7 +14181,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="430" customHeight="1" spans="1:11">
+    <row r="430" hidden="1" customHeight="1" spans="1:11">
       <c r="A430" s="7" t="s">
         <v>53</v>
       </c>
@@ -14210,7 +14210,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="431" customHeight="1" spans="1:11">
+    <row r="431" hidden="1" customHeight="1" spans="1:11">
       <c r="A431" s="7" t="s">
         <v>53</v>
       </c>
@@ -14236,7 +14236,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="432" customHeight="1" spans="1:11">
+    <row r="432" hidden="1" customHeight="1" spans="1:11">
       <c r="A432" s="7" t="s">
         <v>53</v>
       </c>
@@ -14262,7 +14262,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="433" customHeight="1" spans="1:11">
+    <row r="433" hidden="1" customHeight="1" spans="1:11">
       <c r="A433" s="7" t="s">
         <v>53</v>
       </c>
@@ -14291,7 +14291,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="434" customHeight="1" spans="1:11">
+    <row r="434" hidden="1" customHeight="1" spans="1:11">
       <c r="A434" s="8" t="s">
         <v>12</v>
       </c>
@@ -14322,7 +14322,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="435" customHeight="1" spans="1:11">
+    <row r="435" hidden="1" customHeight="1" spans="1:11">
       <c r="A435" s="7" t="s">
         <v>12</v>
       </c>
@@ -14351,7 +14351,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="436" customHeight="1" spans="1:11">
+    <row r="436" hidden="1" customHeight="1" spans="1:11">
       <c r="A436" s="7" t="s">
         <v>12</v>
       </c>
@@ -14380,7 +14380,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="437" customHeight="1" spans="1:11">
+    <row r="437" hidden="1" customHeight="1" spans="1:11">
       <c r="A437" s="7" t="s">
         <v>12</v>
       </c>
@@ -14409,7 +14409,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="438" customHeight="1" spans="1:11">
+    <row r="438" hidden="1" customHeight="1" spans="1:11">
       <c r="A438" s="7" t="s">
         <v>12</v>
       </c>
@@ -14438,7 +14438,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="439" customHeight="1" spans="1:11">
+    <row r="439" hidden="1" customHeight="1" spans="1:11">
       <c r="A439" s="7" t="s">
         <v>12</v>
       </c>
@@ -14467,7 +14467,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="440" customHeight="1" spans="1:11">
+    <row r="440" hidden="1" customHeight="1" spans="1:11">
       <c r="A440" s="7" t="s">
         <v>12</v>
       </c>
@@ -14496,7 +14496,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="441" customHeight="1" spans="1:11">
+    <row r="441" hidden="1" customHeight="1" spans="1:11">
       <c r="A441" s="7" t="s">
         <v>12</v>
       </c>
@@ -14525,7 +14525,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="442" customHeight="1" spans="1:11">
+    <row r="442" hidden="1" customHeight="1" spans="1:11">
       <c r="A442" s="7" t="s">
         <v>12</v>
       </c>
@@ -14554,7 +14554,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="443" customHeight="1" spans="1:11">
+    <row r="443" hidden="1" customHeight="1" spans="1:11">
       <c r="A443" s="7" t="s">
         <v>12</v>
       </c>
@@ -14583,7 +14583,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="444" customHeight="1" spans="1:11">
+    <row r="444" hidden="1" customHeight="1" spans="1:11">
       <c r="A444" s="7" t="s">
         <v>12</v>
       </c>
@@ -14612,7 +14612,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="445" customHeight="1" spans="1:11">
+    <row r="445" hidden="1" customHeight="1" spans="1:11">
       <c r="A445" s="7" t="s">
         <v>12</v>
       </c>
@@ -14641,7 +14641,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="446" customHeight="1" spans="1:11">
+    <row r="446" hidden="1" customHeight="1" spans="1:11">
       <c r="A446" s="7" t="s">
         <v>12</v>
       </c>
@@ -14670,7 +14670,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="447" customHeight="1" spans="1:11">
+    <row r="447" hidden="1" customHeight="1" spans="1:11">
       <c r="A447" s="7" t="s">
         <v>12</v>
       </c>
@@ -14699,7 +14699,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="448" customHeight="1" spans="1:11">
+    <row r="448" hidden="1" customHeight="1" spans="1:11">
       <c r="A448" s="7" t="s">
         <v>12</v>
       </c>
@@ -14728,7 +14728,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="449" customHeight="1" spans="1:11">
+    <row r="449" hidden="1" customHeight="1" spans="1:11">
       <c r="A449" s="7" t="s">
         <v>12</v>
       </c>
@@ -14757,7 +14757,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="450" customHeight="1" spans="1:11">
+    <row r="450" hidden="1" customHeight="1" spans="1:11">
       <c r="A450" s="7" t="s">
         <v>12</v>
       </c>
@@ -14786,7 +14786,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="451" customHeight="1" spans="1:11">
+    <row r="451" hidden="1" customHeight="1" spans="1:11">
       <c r="A451" s="7" t="s">
         <v>12</v>
       </c>
@@ -14815,7 +14815,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="452" customHeight="1" spans="1:11">
+    <row r="452" hidden="1" customHeight="1" spans="1:11">
       <c r="A452" s="7" t="s">
         <v>12</v>
       </c>
@@ -14841,7 +14841,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="453" customHeight="1" spans="1:11">
+    <row r="453" hidden="1" customHeight="1" spans="1:11">
       <c r="A453" s="7" t="s">
         <v>12</v>
       </c>
@@ -14870,7 +14870,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="454" customHeight="1" spans="1:11">
+    <row r="454" hidden="1" customHeight="1" spans="1:11">
       <c r="A454" s="7" t="s">
         <v>12</v>
       </c>
@@ -14899,7 +14899,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="455" customHeight="1" spans="1:11">
+    <row r="455" hidden="1" customHeight="1" spans="1:11">
       <c r="A455" s="7" t="s">
         <v>12</v>
       </c>
@@ -14928,7 +14928,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="456" customHeight="1" spans="1:11">
+    <row r="456" hidden="1" customHeight="1" spans="1:11">
       <c r="A456" s="7" t="s">
         <v>12</v>
       </c>
@@ -14954,7 +14954,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="457" customHeight="1" spans="1:11">
+    <row r="457" hidden="1" customHeight="1" spans="1:11">
       <c r="A457" s="7" t="s">
         <v>12</v>
       </c>
@@ -14983,7 +14983,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="458" customHeight="1" spans="1:11">
+    <row r="458" hidden="1" customHeight="1" spans="1:11">
       <c r="A458" s="7" t="s">
         <v>50</v>
       </c>
@@ -15012,7 +15012,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="459" customHeight="1" spans="1:11">
+    <row r="459" hidden="1" customHeight="1" spans="1:11">
       <c r="A459" s="7" t="s">
         <v>50</v>
       </c>
@@ -15041,7 +15041,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="460" customHeight="1" spans="1:11">
+    <row r="460" hidden="1" customHeight="1" spans="1:11">
       <c r="A460" s="7" t="s">
         <v>50</v>
       </c>
@@ -15070,7 +15070,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="461" customHeight="1" spans="1:11">
+    <row r="461" hidden="1" customHeight="1" spans="1:11">
       <c r="A461" s="7" t="s">
         <v>50</v>
       </c>
@@ -15099,7 +15099,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="462" customHeight="1" spans="1:11">
+    <row r="462" hidden="1" customHeight="1" spans="1:11">
       <c r="A462" s="7" t="s">
         <v>50</v>
       </c>
@@ -15128,7 +15128,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="463" customHeight="1" spans="1:11">
+    <row r="463" hidden="1" customHeight="1" spans="1:11">
       <c r="A463" s="7" t="s">
         <v>50</v>
       </c>
@@ -15157,7 +15157,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="464" customHeight="1" spans="1:11">
+    <row r="464" hidden="1" customHeight="1" spans="1:11">
       <c r="A464" s="7" t="s">
         <v>50</v>
       </c>
@@ -15186,7 +15186,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="465" customHeight="1" spans="1:11">
+    <row r="465" hidden="1" customHeight="1" spans="1:11">
       <c r="A465" s="7" t="s">
         <v>50</v>
       </c>
@@ -15215,7 +15215,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="466" customHeight="1" spans="1:11">
+    <row r="466" hidden="1" customHeight="1" spans="1:11">
       <c r="A466" s="7" t="s">
         <v>50</v>
       </c>
@@ -15244,7 +15244,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="467" customHeight="1" spans="1:11">
+    <row r="467" hidden="1" customHeight="1" spans="1:11">
       <c r="A467" s="7" t="s">
         <v>50</v>
       </c>
@@ -15273,7 +15273,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="468" customHeight="1" spans="1:11">
+    <row r="468" hidden="1" customHeight="1" spans="1:11">
       <c r="A468" s="7" t="s">
         <v>50</v>
       </c>
@@ -15302,7 +15302,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="469" customHeight="1" spans="1:11">
+    <row r="469" hidden="1" customHeight="1" spans="1:11">
       <c r="A469" s="7" t="s">
         <v>50</v>
       </c>
@@ -15331,7 +15331,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="470" customHeight="1" spans="1:11">
+    <row r="470" hidden="1" customHeight="1" spans="1:11">
       <c r="A470" s="7" t="s">
         <v>50</v>
       </c>
@@ -15360,7 +15360,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="471" customHeight="1" spans="1:11">
+    <row r="471" hidden="1" customHeight="1" spans="1:11">
       <c r="A471" s="7" t="s">
         <v>50</v>
       </c>
@@ -15389,7 +15389,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="472" customHeight="1" spans="1:11">
+    <row r="472" hidden="1" customHeight="1" spans="1:11">
       <c r="A472" s="7" t="s">
         <v>50</v>
       </c>
@@ -15418,7 +15418,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="473" customHeight="1" spans="1:11">
+    <row r="473" hidden="1" customHeight="1" spans="1:11">
       <c r="A473" s="7" t="s">
         <v>50</v>
       </c>
@@ -15447,7 +15447,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="474" customHeight="1" spans="1:11">
+    <row r="474" hidden="1" customHeight="1" spans="1:11">
       <c r="A474" s="7" t="s">
         <v>50</v>
       </c>
@@ -15476,7 +15476,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="475" customHeight="1" spans="1:11">
+    <row r="475" hidden="1" customHeight="1" spans="1:11">
       <c r="A475" s="7" t="s">
         <v>50</v>
       </c>
@@ -15505,7 +15505,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="476" customHeight="1" spans="1:11">
+    <row r="476" hidden="1" customHeight="1" spans="1:11">
       <c r="A476" s="7" t="s">
         <v>50</v>
       </c>
@@ -15531,7 +15531,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="477" customHeight="1" spans="1:11">
+    <row r="477" hidden="1" customHeight="1" spans="1:11">
       <c r="A477" s="7" t="s">
         <v>50</v>
       </c>
@@ -15560,7 +15560,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="478" customHeight="1" spans="1:11">
+    <row r="478" hidden="1" customHeight="1" spans="1:11">
       <c r="A478" s="7" t="s">
         <v>50</v>
       </c>
@@ -15589,7 +15589,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="479" customHeight="1" spans="1:11">
+    <row r="479" hidden="1" customHeight="1" spans="1:11">
       <c r="A479" s="7" t="s">
         <v>50</v>
       </c>
@@ -15618,7 +15618,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="480" customHeight="1" spans="1:11">
+    <row r="480" hidden="1" customHeight="1" spans="1:11">
       <c r="A480" s="7" t="s">
         <v>50</v>
       </c>
@@ -15644,7 +15644,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="481" customHeight="1" spans="1:11">
+    <row r="481" hidden="1" customHeight="1" spans="1:11">
       <c r="A481" s="7" t="s">
         <v>50</v>
       </c>
@@ -15673,7 +15673,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="482" customHeight="1" spans="1:11">
+    <row r="482" hidden="1" customHeight="1" spans="1:11">
       <c r="A482" s="7" t="s">
         <v>53</v>
       </c>
@@ -15702,7 +15702,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="483" customHeight="1" spans="1:11">
+    <row r="483" hidden="1" customHeight="1" spans="1:11">
       <c r="A483" s="7" t="s">
         <v>53</v>
       </c>
@@ -15731,7 +15731,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="484" customHeight="1" spans="1:11">
+    <row r="484" hidden="1" customHeight="1" spans="1:11">
       <c r="A484" s="7" t="s">
         <v>53</v>
       </c>
@@ -15760,7 +15760,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="485" customHeight="1" spans="1:11">
+    <row r="485" hidden="1" customHeight="1" spans="1:11">
       <c r="A485" s="7" t="s">
         <v>53</v>
       </c>
@@ -15789,7 +15789,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="486" customHeight="1" spans="1:11">
+    <row r="486" hidden="1" customHeight="1" spans="1:11">
       <c r="A486" s="7" t="s">
         <v>53</v>
       </c>
@@ -15818,7 +15818,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="487" customHeight="1" spans="1:11">
+    <row r="487" hidden="1" customHeight="1" spans="1:11">
       <c r="A487" s="7" t="s">
         <v>53</v>
       </c>
@@ -15847,7 +15847,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="488" customHeight="1" spans="1:11">
+    <row r="488" hidden="1" customHeight="1" spans="1:11">
       <c r="A488" s="7" t="s">
         <v>53</v>
       </c>
@@ -15876,7 +15876,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="489" customHeight="1" spans="1:11">
+    <row r="489" hidden="1" customHeight="1" spans="1:11">
       <c r="A489" s="7" t="s">
         <v>53</v>
       </c>
@@ -15902,7 +15902,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="490" customHeight="1" spans="1:11">
+    <row r="490" hidden="1" customHeight="1" spans="1:11">
       <c r="A490" s="7" t="s">
         <v>53</v>
       </c>
@@ -15931,7 +15931,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="491" customHeight="1" spans="1:11">
+    <row r="491" hidden="1" customHeight="1" spans="1:11">
       <c r="A491" s="7" t="s">
         <v>53</v>
       </c>
@@ -15960,7 +15960,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="492" customHeight="1" spans="1:11">
+    <row r="492" hidden="1" customHeight="1" spans="1:11">
       <c r="A492" s="7" t="s">
         <v>53</v>
       </c>
@@ -15989,7 +15989,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="493" customHeight="1" spans="1:11">
+    <row r="493" hidden="1" customHeight="1" spans="1:11">
       <c r="A493" s="7" t="s">
         <v>53</v>
       </c>
@@ -16015,7 +16015,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="494" customHeight="1" spans="1:11">
+    <row r="494" hidden="1" customHeight="1" spans="1:11">
       <c r="A494" s="7" t="s">
         <v>53</v>
       </c>
@@ -16044,7 +16044,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="495" customHeight="1" spans="1:11">
+    <row r="495" hidden="1" customHeight="1" spans="1:11">
       <c r="A495" s="7" t="s">
         <v>53</v>
       </c>
@@ -16070,7 +16070,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="496" customHeight="1" spans="1:11">
+    <row r="496" hidden="1" customHeight="1" spans="1:11">
       <c r="A496" s="7" t="s">
         <v>53</v>
       </c>
@@ -16096,7 +16096,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="497" customHeight="1" spans="1:11">
+    <row r="497" hidden="1" customHeight="1" spans="1:11">
       <c r="A497" s="7" t="s">
         <v>53</v>
       </c>
@@ -16125,7 +16125,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="498" customHeight="1" spans="1:11">
+    <row r="498" hidden="1" customHeight="1" spans="1:11">
       <c r="A498" s="7" t="s">
         <v>53</v>
       </c>
@@ -16154,7 +16154,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="499" customHeight="1" spans="1:11">
+    <row r="499" hidden="1" customHeight="1" spans="1:11">
       <c r="A499" s="7" t="s">
         <v>53</v>
       </c>
@@ -16180,7 +16180,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="500" customHeight="1" spans="1:11">
+    <row r="500" hidden="1" customHeight="1" spans="1:11">
       <c r="A500" s="7" t="s">
         <v>53</v>
       </c>
@@ -16206,7 +16206,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="501" customHeight="1" spans="1:11">
+    <row r="501" hidden="1" customHeight="1" spans="1:11">
       <c r="A501" s="7" t="s">
         <v>53</v>
       </c>
@@ -16235,7 +16235,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="502" customHeight="1" spans="1:11">
+    <row r="502" hidden="1" customHeight="1" spans="1:11">
       <c r="A502" s="7" t="s">
         <v>53</v>
       </c>
@@ -16264,7 +16264,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="503" customHeight="1" spans="1:11">
+    <row r="503" hidden="1" customHeight="1" spans="1:11">
       <c r="A503" s="7" t="s">
         <v>53</v>
       </c>
@@ -16290,7 +16290,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="504" customHeight="1" spans="1:11">
+    <row r="504" hidden="1" customHeight="1" spans="1:11">
       <c r="A504" s="7" t="s">
         <v>53</v>
       </c>
@@ -16316,7 +16316,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="505" customHeight="1" spans="1:11">
+    <row r="505" hidden="1" customHeight="1" spans="1:11">
       <c r="A505" s="7" t="s">
         <v>53</v>
       </c>
@@ -16345,7 +16345,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="506" customHeight="1" spans="1:11">
+    <row r="506" hidden="1" customHeight="1" spans="1:11">
       <c r="A506" s="8" t="s">
         <v>12</v>
       </c>
@@ -16376,7 +16376,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="507" customHeight="1" spans="1:11">
+    <row r="507" hidden="1" customHeight="1" spans="1:11">
       <c r="A507" s="7" t="s">
         <v>12</v>
       </c>
@@ -16405,7 +16405,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="508" customHeight="1" spans="1:11">
+    <row r="508" hidden="1" customHeight="1" spans="1:11">
       <c r="A508" s="7" t="s">
         <v>12</v>
       </c>
@@ -16434,7 +16434,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="509" customHeight="1" spans="1:11">
+    <row r="509" hidden="1" customHeight="1" spans="1:11">
       <c r="A509" s="7" t="s">
         <v>12</v>
       </c>
@@ -16463,7 +16463,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="510" customHeight="1" spans="1:11">
+    <row r="510" hidden="1" customHeight="1" spans="1:11">
       <c r="A510" s="7" t="s">
         <v>12</v>
       </c>
@@ -16492,7 +16492,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="511" customHeight="1" spans="1:11">
+    <row r="511" hidden="1" customHeight="1" spans="1:11">
       <c r="A511" s="7" t="s">
         <v>12</v>
       </c>
@@ -16521,7 +16521,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="512" customHeight="1" spans="1:11">
+    <row r="512" hidden="1" customHeight="1" spans="1:11">
       <c r="A512" s="7" t="s">
         <v>12</v>
       </c>
@@ -16550,7 +16550,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="513" customHeight="1" spans="1:11">
+    <row r="513" hidden="1" customHeight="1" spans="1:11">
       <c r="A513" s="7" t="s">
         <v>12</v>
       </c>
@@ -16579,7 +16579,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="514" customHeight="1" spans="1:11">
+    <row r="514" hidden="1" customHeight="1" spans="1:11">
       <c r="A514" s="7" t="s">
         <v>12</v>
       </c>
@@ -16608,7 +16608,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="515" customHeight="1" spans="1:11">
+    <row r="515" hidden="1" customHeight="1" spans="1:11">
       <c r="A515" s="7" t="s">
         <v>12</v>
       </c>
@@ -16637,7 +16637,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="516" customHeight="1" spans="1:11">
+    <row r="516" hidden="1" customHeight="1" spans="1:11">
       <c r="A516" s="7" t="s">
         <v>12</v>
       </c>
@@ -16666,7 +16666,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="517" customHeight="1" spans="1:11">
+    <row r="517" hidden="1" customHeight="1" spans="1:11">
       <c r="A517" s="7" t="s">
         <v>12</v>
       </c>
@@ -16695,7 +16695,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="518" customHeight="1" spans="1:11">
+    <row r="518" hidden="1" customHeight="1" spans="1:11">
       <c r="A518" s="7" t="s">
         <v>12</v>
       </c>
@@ -16724,7 +16724,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="519" customHeight="1" spans="1:11">
+    <row r="519" hidden="1" customHeight="1" spans="1:11">
       <c r="A519" s="7" t="s">
         <v>12</v>
       </c>
@@ -16753,7 +16753,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="520" customHeight="1" spans="1:11">
+    <row r="520" hidden="1" customHeight="1" spans="1:11">
       <c r="A520" s="7" t="s">
         <v>12</v>
       </c>
@@ -16782,7 +16782,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="521" customHeight="1" spans="1:11">
+    <row r="521" hidden="1" customHeight="1" spans="1:11">
       <c r="A521" s="7" t="s">
         <v>12</v>
       </c>
@@ -16811,7 +16811,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="522" customHeight="1" spans="1:11">
+    <row r="522" hidden="1" customHeight="1" spans="1:11">
       <c r="A522" s="7" t="s">
         <v>12</v>
       </c>
@@ -16840,7 +16840,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="523" customHeight="1" spans="1:11">
+    <row r="523" hidden="1" customHeight="1" spans="1:11">
       <c r="A523" s="7" t="s">
         <v>12</v>
       </c>
@@ -16869,7 +16869,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="524" customHeight="1" spans="1:11">
+    <row r="524" hidden="1" customHeight="1" spans="1:11">
       <c r="A524" s="7" t="s">
         <v>12</v>
       </c>
@@ -16895,7 +16895,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="525" customHeight="1" spans="1:11">
+    <row r="525" hidden="1" customHeight="1" spans="1:11">
       <c r="A525" s="7" t="s">
         <v>12</v>
       </c>
@@ -16924,7 +16924,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="526" customHeight="1" spans="1:11">
+    <row r="526" hidden="1" customHeight="1" spans="1:11">
       <c r="A526" s="7" t="s">
         <v>12</v>
       </c>
@@ -16953,7 +16953,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="527" customHeight="1" spans="1:11">
+    <row r="527" hidden="1" customHeight="1" spans="1:11">
       <c r="A527" s="7" t="s">
         <v>12</v>
       </c>
@@ -16982,7 +16982,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="528" customHeight="1" spans="1:11">
+    <row r="528" hidden="1" customHeight="1" spans="1:11">
       <c r="A528" s="7" t="s">
         <v>12</v>
       </c>
@@ -17008,7 +17008,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="529" customHeight="1" spans="1:11">
+    <row r="529" hidden="1" customHeight="1" spans="1:11">
       <c r="A529" s="7" t="s">
         <v>12</v>
       </c>
@@ -17037,7 +17037,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="530" customHeight="1" spans="1:11">
+    <row r="530" hidden="1" customHeight="1" spans="1:11">
       <c r="A530" s="7" t="s">
         <v>50</v>
       </c>
@@ -17066,7 +17066,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="531" customHeight="1" spans="1:11">
+    <row r="531" hidden="1" customHeight="1" spans="1:11">
       <c r="A531" s="7" t="s">
         <v>50</v>
       </c>
@@ -17095,7 +17095,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="532" customHeight="1" spans="1:11">
+    <row r="532" hidden="1" customHeight="1" spans="1:11">
       <c r="A532" s="7" t="s">
         <v>50</v>
       </c>
@@ -17124,7 +17124,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="533" customHeight="1" spans="1:11">
+    <row r="533" hidden="1" customHeight="1" spans="1:11">
       <c r="A533" s="7" t="s">
         <v>50</v>
       </c>
@@ -17153,7 +17153,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="534" customHeight="1" spans="1:11">
+    <row r="534" hidden="1" customHeight="1" spans="1:11">
       <c r="A534" s="7" t="s">
         <v>50</v>
       </c>
@@ -17182,7 +17182,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="535" customHeight="1" spans="1:11">
+    <row r="535" hidden="1" customHeight="1" spans="1:11">
       <c r="A535" s="7" t="s">
         <v>50</v>
       </c>
@@ -17211,7 +17211,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="536" customHeight="1" spans="1:11">
+    <row r="536" hidden="1" customHeight="1" spans="1:11">
       <c r="A536" s="7" t="s">
         <v>50</v>
       </c>
@@ -17240,7 +17240,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="537" customHeight="1" spans="1:11">
+    <row r="537" hidden="1" customHeight="1" spans="1:11">
       <c r="A537" s="7" t="s">
         <v>50</v>
       </c>
@@ -17269,7 +17269,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="538" customHeight="1" spans="1:11">
+    <row r="538" hidden="1" customHeight="1" spans="1:11">
       <c r="A538" s="7" t="s">
         <v>50</v>
       </c>
@@ -17298,7 +17298,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="539" customHeight="1" spans="1:11">
+    <row r="539" hidden="1" customHeight="1" spans="1:11">
       <c r="A539" s="7" t="s">
         <v>50</v>
       </c>
@@ -17327,7 +17327,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="540" customHeight="1" spans="1:11">
+    <row r="540" hidden="1" customHeight="1" spans="1:11">
       <c r="A540" s="7" t="s">
         <v>50</v>
       </c>
@@ -17356,7 +17356,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="541" customHeight="1" spans="1:11">
+    <row r="541" hidden="1" customHeight="1" spans="1:11">
       <c r="A541" s="7" t="s">
         <v>50</v>
       </c>
@@ -17385,7 +17385,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="542" customHeight="1" spans="1:11">
+    <row r="542" hidden="1" customHeight="1" spans="1:11">
       <c r="A542" s="7" t="s">
         <v>50</v>
       </c>
@@ -17414,7 +17414,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="543" customHeight="1" spans="1:11">
+    <row r="543" hidden="1" customHeight="1" spans="1:11">
       <c r="A543" s="7" t="s">
         <v>50</v>
       </c>
@@ -17443,7 +17443,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="544" customHeight="1" spans="1:11">
+    <row r="544" hidden="1" customHeight="1" spans="1:11">
       <c r="A544" s="7" t="s">
         <v>50</v>
       </c>
@@ -17472,7 +17472,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="545" customHeight="1" spans="1:11">
+    <row r="545" hidden="1" customHeight="1" spans="1:11">
       <c r="A545" s="7" t="s">
         <v>50</v>
       </c>
@@ -17501,7 +17501,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="546" customHeight="1" spans="1:11">
+    <row r="546" hidden="1" customHeight="1" spans="1:11">
       <c r="A546" s="7" t="s">
         <v>50</v>
       </c>
@@ -17530,7 +17530,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="547" customHeight="1" spans="1:11">
+    <row r="547" hidden="1" customHeight="1" spans="1:11">
       <c r="A547" s="7" t="s">
         <v>50</v>
       </c>
@@ -17559,7 +17559,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="548" customHeight="1" spans="1:11">
+    <row r="548" hidden="1" customHeight="1" spans="1:11">
       <c r="A548" s="7" t="s">
         <v>50</v>
       </c>
@@ -17585,7 +17585,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="549" customHeight="1" spans="1:11">
+    <row r="549" hidden="1" customHeight="1" spans="1:11">
       <c r="A549" s="7" t="s">
         <v>50</v>
       </c>
@@ -17614,7 +17614,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="550" customHeight="1" spans="1:11">
+    <row r="550" hidden="1" customHeight="1" spans="1:11">
       <c r="A550" s="7" t="s">
         <v>50</v>
       </c>
@@ -17643,7 +17643,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="551" customHeight="1" spans="1:11">
+    <row r="551" hidden="1" customHeight="1" spans="1:11">
       <c r="A551" s="7" t="s">
         <v>50</v>
       </c>
@@ -17672,7 +17672,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="552" customHeight="1" spans="1:11">
+    <row r="552" hidden="1" customHeight="1" spans="1:11">
       <c r="A552" s="7" t="s">
         <v>50</v>
       </c>
@@ -17698,7 +17698,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="553" customHeight="1" spans="1:11">
+    <row r="553" hidden="1" customHeight="1" spans="1:11">
       <c r="A553" s="7" t="s">
         <v>50</v>
       </c>
@@ -17727,7 +17727,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="554" customHeight="1" spans="1:11">
+    <row r="554" hidden="1" customHeight="1" spans="1:11">
       <c r="A554" s="7" t="s">
         <v>53</v>
       </c>
@@ -17756,7 +17756,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="555" customHeight="1" spans="1:11">
+    <row r="555" hidden="1" customHeight="1" spans="1:11">
       <c r="A555" s="7" t="s">
         <v>53</v>
       </c>
@@ -17785,7 +17785,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="556" customHeight="1" spans="1:11">
+    <row r="556" hidden="1" customHeight="1" spans="1:11">
       <c r="A556" s="7" t="s">
         <v>53</v>
       </c>
@@ -17814,7 +17814,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="557" customHeight="1" spans="1:11">
+    <row r="557" hidden="1" customHeight="1" spans="1:11">
       <c r="A557" s="7" t="s">
         <v>53</v>
       </c>
@@ -17843,7 +17843,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="558" customHeight="1" spans="1:11">
+    <row r="558" hidden="1" customHeight="1" spans="1:11">
       <c r="A558" s="7" t="s">
         <v>53</v>
       </c>
@@ -17872,7 +17872,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="559" customHeight="1" spans="1:11">
+    <row r="559" hidden="1" customHeight="1" spans="1:11">
       <c r="A559" s="7" t="s">
         <v>53</v>
       </c>
@@ -17901,7 +17901,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="560" customHeight="1" spans="1:11">
+    <row r="560" hidden="1" customHeight="1" spans="1:11">
       <c r="A560" s="7" t="s">
         <v>53</v>
       </c>
@@ -17930,7 +17930,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="561" customHeight="1" spans="1:11">
+    <row r="561" hidden="1" customHeight="1" spans="1:11">
       <c r="A561" s="7" t="s">
         <v>53</v>
       </c>
@@ -17956,7 +17956,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="562" customHeight="1" spans="1:11">
+    <row r="562" hidden="1" customHeight="1" spans="1:11">
       <c r="A562" s="7" t="s">
         <v>53</v>
       </c>
@@ -17985,7 +17985,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="563" customHeight="1" spans="1:11">
+    <row r="563" hidden="1" customHeight="1" spans="1:11">
       <c r="A563" s="7" t="s">
         <v>53</v>
       </c>
@@ -18014,7 +18014,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="564" customHeight="1" spans="1:11">
+    <row r="564" hidden="1" customHeight="1" spans="1:11">
       <c r="A564" s="7" t="s">
         <v>53</v>
       </c>
@@ -18043,7 +18043,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="565" customHeight="1" spans="1:11">
+    <row r="565" hidden="1" customHeight="1" spans="1:11">
       <c r="A565" s="7" t="s">
         <v>53</v>
       </c>
@@ -18069,7 +18069,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="566" customHeight="1" spans="1:11">
+    <row r="566" hidden="1" customHeight="1" spans="1:11">
       <c r="A566" s="7" t="s">
         <v>53</v>
       </c>
@@ -18098,7 +18098,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="567" customHeight="1" spans="1:11">
+    <row r="567" hidden="1" customHeight="1" spans="1:11">
       <c r="A567" s="7" t="s">
         <v>53</v>
       </c>
@@ -18124,7 +18124,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="568" customHeight="1" spans="1:11">
+    <row r="568" hidden="1" customHeight="1" spans="1:11">
       <c r="A568" s="7" t="s">
         <v>53</v>
       </c>
@@ -18150,7 +18150,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="569" customHeight="1" spans="1:11">
+    <row r="569" hidden="1" customHeight="1" spans="1:11">
       <c r="A569" s="7" t="s">
         <v>53</v>
       </c>
@@ -18179,7 +18179,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="570" customHeight="1" spans="1:11">
+    <row r="570" hidden="1" customHeight="1" spans="1:11">
       <c r="A570" s="7" t="s">
         <v>53</v>
       </c>
@@ -18208,7 +18208,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="571" customHeight="1" spans="1:11">
+    <row r="571" hidden="1" customHeight="1" spans="1:11">
       <c r="A571" s="7" t="s">
         <v>53</v>
       </c>
@@ -18234,7 +18234,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="572" customHeight="1" spans="1:11">
+    <row r="572" hidden="1" customHeight="1" spans="1:11">
       <c r="A572" s="7" t="s">
         <v>53</v>
       </c>
@@ -18260,7 +18260,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="573" customHeight="1" spans="1:11">
+    <row r="573" hidden="1" customHeight="1" spans="1:11">
       <c r="A573" s="7" t="s">
         <v>53</v>
       </c>
@@ -18289,7 +18289,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="574" customHeight="1" spans="1:11">
+    <row r="574" hidden="1" customHeight="1" spans="1:11">
       <c r="A574" s="7" t="s">
         <v>53</v>
       </c>
@@ -18318,7 +18318,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="575" customHeight="1" spans="1:11">
+    <row r="575" hidden="1" customHeight="1" spans="1:11">
       <c r="A575" s="7" t="s">
         <v>53</v>
       </c>
@@ -18344,7 +18344,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="576" customHeight="1" spans="1:11">
+    <row r="576" hidden="1" customHeight="1" spans="1:11">
       <c r="A576" s="7" t="s">
         <v>53</v>
       </c>
@@ -18370,7 +18370,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="577" customHeight="1" spans="1:11">
+    <row r="577" hidden="1" customHeight="1" spans="1:11">
       <c r="A577" s="7" t="s">
         <v>53</v>
       </c>
@@ -18399,7 +18399,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="578" s="1" customFormat="1" customHeight="1" spans="1:11">
+    <row r="578" s="1" customFormat="1" hidden="1" customHeight="1" spans="1:11">
       <c r="A578" s="8" t="s">
         <v>12</v>
       </c>
@@ -18428,7 +18428,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="579" customHeight="1" spans="1:11">
+    <row r="579" hidden="1" customHeight="1" spans="1:11">
       <c r="A579" s="7" t="s">
         <v>12</v>
       </c>
@@ -18457,7 +18457,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="580" customHeight="1" spans="1:11">
+    <row r="580" hidden="1" customHeight="1" spans="1:11">
       <c r="A580" s="7" t="s">
         <v>12</v>
       </c>
@@ -18486,7 +18486,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="581" customHeight="1" spans="1:11">
+    <row r="581" hidden="1" customHeight="1" spans="1:11">
       <c r="A581" s="7" t="s">
         <v>12</v>
       </c>
@@ -18515,7 +18515,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="582" customHeight="1" spans="1:11">
+    <row r="582" hidden="1" customHeight="1" spans="1:11">
       <c r="A582" s="7" t="s">
         <v>12</v>
       </c>
@@ -18544,7 +18544,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="583" customHeight="1" spans="1:11">
+    <row r="583" hidden="1" customHeight="1" spans="1:11">
       <c r="A583" s="7" t="s">
         <v>12</v>
       </c>
@@ -18573,7 +18573,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="584" customHeight="1" spans="1:11">
+    <row r="584" hidden="1" customHeight="1" spans="1:11">
       <c r="A584" s="7" t="s">
         <v>12</v>
       </c>
@@ -18602,7 +18602,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="585" customHeight="1" spans="1:11">
+    <row r="585" hidden="1" customHeight="1" spans="1:11">
       <c r="A585" s="7" t="s">
         <v>12</v>
       </c>
@@ -18631,7 +18631,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="586" customHeight="1" spans="1:11">
+    <row r="586" hidden="1" customHeight="1" spans="1:11">
       <c r="A586" s="7" t="s">
         <v>12</v>
       </c>
@@ -18660,7 +18660,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="587" customHeight="1" spans="1:11">
+    <row r="587" hidden="1" customHeight="1" spans="1:11">
       <c r="A587" s="7" t="s">
         <v>12</v>
       </c>
@@ -18689,7 +18689,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="588" customHeight="1" spans="1:11">
+    <row r="588" hidden="1" customHeight="1" spans="1:11">
       <c r="A588" s="7" t="s">
         <v>12</v>
       </c>
@@ -18718,7 +18718,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="589" customHeight="1" spans="1:11">
+    <row r="589" hidden="1" customHeight="1" spans="1:11">
       <c r="A589" s="7" t="s">
         <v>12</v>
       </c>
@@ -18747,7 +18747,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="590" customHeight="1" spans="1:11">
+    <row r="590" hidden="1" customHeight="1" spans="1:11">
       <c r="A590" s="7" t="s">
         <v>12</v>
       </c>
@@ -18776,7 +18776,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="591" customHeight="1" spans="1:11">
+    <row r="591" hidden="1" customHeight="1" spans="1:11">
       <c r="A591" s="7" t="s">
         <v>12</v>
       </c>
@@ -18805,7 +18805,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="592" customHeight="1" spans="1:11">
+    <row r="592" hidden="1" customHeight="1" spans="1:11">
       <c r="A592" s="7" t="s">
         <v>12</v>
       </c>
@@ -18834,7 +18834,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="593" customHeight="1" spans="1:11">
+    <row r="593" hidden="1" customHeight="1" spans="1:11">
       <c r="A593" s="7" t="s">
         <v>12</v>
       </c>
@@ -18863,7 +18863,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="594" customHeight="1" spans="1:11">
+    <row r="594" hidden="1" customHeight="1" spans="1:11">
       <c r="A594" s="7" t="s">
         <v>12</v>
       </c>
@@ -18892,7 +18892,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="595" customHeight="1" spans="1:11">
+    <row r="595" hidden="1" customHeight="1" spans="1:11">
       <c r="A595" s="7" t="s">
         <v>12</v>
       </c>
@@ -18921,7 +18921,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="596" customHeight="1" spans="1:11">
+    <row r="596" hidden="1" customHeight="1" spans="1:11">
       <c r="A596" s="7" t="s">
         <v>12</v>
       </c>
@@ -18947,7 +18947,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="597" customHeight="1" spans="1:11">
+    <row r="597" hidden="1" customHeight="1" spans="1:11">
       <c r="A597" s="7" t="s">
         <v>12</v>
       </c>
@@ -18976,7 +18976,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="598" customHeight="1" spans="1:11">
+    <row r="598" hidden="1" customHeight="1" spans="1:11">
       <c r="A598" s="7" t="s">
         <v>12</v>
       </c>
@@ -19005,7 +19005,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="599" customHeight="1" spans="1:11">
+    <row r="599" hidden="1" customHeight="1" spans="1:11">
       <c r="A599" s="7" t="s">
         <v>12</v>
       </c>
@@ -19034,7 +19034,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="600" customHeight="1" spans="1:11">
+    <row r="600" hidden="1" customHeight="1" spans="1:11">
       <c r="A600" s="7" t="s">
         <v>12</v>
       </c>
@@ -19060,7 +19060,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="601" customHeight="1" spans="1:11">
+    <row r="601" hidden="1" customHeight="1" spans="1:11">
       <c r="A601" s="7" t="s">
         <v>12</v>
       </c>
@@ -19089,7 +19089,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="602" customHeight="1" spans="1:11">
+    <row r="602" hidden="1" customHeight="1" spans="1:11">
       <c r="A602" s="7" t="s">
         <v>50</v>
       </c>
@@ -19118,7 +19118,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="603" customHeight="1" spans="1:11">
+    <row r="603" hidden="1" customHeight="1" spans="1:11">
       <c r="A603" s="7" t="s">
         <v>50</v>
       </c>
@@ -19147,7 +19147,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="604" customHeight="1" spans="1:11">
+    <row r="604" hidden="1" customHeight="1" spans="1:11">
       <c r="A604" s="7" t="s">
         <v>50</v>
       </c>
@@ -19176,7 +19176,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="605" customHeight="1" spans="1:11">
+    <row r="605" hidden="1" customHeight="1" spans="1:11">
       <c r="A605" s="7" t="s">
         <v>50</v>
       </c>
@@ -19205,7 +19205,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="606" customHeight="1" spans="1:11">
+    <row r="606" hidden="1" customHeight="1" spans="1:11">
       <c r="A606" s="7" t="s">
         <v>50</v>
       </c>
@@ -19234,7 +19234,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="607" customHeight="1" spans="1:11">
+    <row r="607" hidden="1" customHeight="1" spans="1:11">
       <c r="A607" s="7" t="s">
         <v>50</v>
       </c>
@@ -19263,7 +19263,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="608" customHeight="1" spans="1:11">
+    <row r="608" hidden="1" customHeight="1" spans="1:11">
       <c r="A608" s="7" t="s">
         <v>50</v>
       </c>
@@ -19292,7 +19292,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="609" customHeight="1" spans="1:11">
+    <row r="609" hidden="1" customHeight="1" spans="1:11">
       <c r="A609" s="7" t="s">
         <v>50</v>
       </c>
@@ -19321,7 +19321,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="610" customHeight="1" spans="1:11">
+    <row r="610" hidden="1" customHeight="1" spans="1:11">
       <c r="A610" s="7" t="s">
         <v>50</v>
       </c>
@@ -19350,7 +19350,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="611" customHeight="1" spans="1:11">
+    <row r="611" hidden="1" customHeight="1" spans="1:11">
       <c r="A611" s="7" t="s">
         <v>50</v>
       </c>
@@ -19379,7 +19379,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="612" customHeight="1" spans="1:11">
+    <row r="612" hidden="1" customHeight="1" spans="1:11">
       <c r="A612" s="7" t="s">
         <v>50</v>
       </c>
@@ -19408,7 +19408,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="613" customHeight="1" spans="1:11">
+    <row r="613" hidden="1" customHeight="1" spans="1:11">
       <c r="A613" s="7" t="s">
         <v>50</v>
       </c>
@@ -19437,7 +19437,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="614" customHeight="1" spans="1:11">
+    <row r="614" hidden="1" customHeight="1" spans="1:11">
       <c r="A614" s="7" t="s">
         <v>50</v>
       </c>
@@ -19466,7 +19466,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="615" customHeight="1" spans="1:11">
+    <row r="615" hidden="1" customHeight="1" spans="1:11">
       <c r="A615" s="7" t="s">
         <v>50</v>
       </c>
@@ -19495,7 +19495,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="616" customHeight="1" spans="1:11">
+    <row r="616" hidden="1" customHeight="1" spans="1:11">
       <c r="A616" s="7" t="s">
         <v>50</v>
       </c>
@@ -19524,7 +19524,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="617" customHeight="1" spans="1:11">
+    <row r="617" hidden="1" customHeight="1" spans="1:11">
       <c r="A617" s="7" t="s">
         <v>50</v>
       </c>
@@ -19553,7 +19553,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="618" customHeight="1" spans="1:11">
+    <row r="618" hidden="1" customHeight="1" spans="1:11">
       <c r="A618" s="7" t="s">
         <v>50</v>
       </c>
@@ -19582,7 +19582,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="619" customHeight="1" spans="1:11">
+    <row r="619" hidden="1" customHeight="1" spans="1:11">
       <c r="A619" s="7" t="s">
         <v>50</v>
       </c>
@@ -19611,7 +19611,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="620" customHeight="1" spans="1:11">
+    <row r="620" hidden="1" customHeight="1" spans="1:11">
       <c r="A620" s="7" t="s">
         <v>50</v>
       </c>
@@ -19637,7 +19637,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="621" customHeight="1" spans="1:11">
+    <row r="621" hidden="1" customHeight="1" spans="1:11">
       <c r="A621" s="7" t="s">
         <v>50</v>
       </c>
@@ -19666,7 +19666,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="622" customHeight="1" spans="1:11">
+    <row r="622" hidden="1" customHeight="1" spans="1:11">
       <c r="A622" s="7" t="s">
         <v>50</v>
       </c>
@@ -19695,7 +19695,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="623" customHeight="1" spans="1:11">
+    <row r="623" hidden="1" customHeight="1" spans="1:11">
       <c r="A623" s="7" t="s">
         <v>50</v>
       </c>
@@ -19724,7 +19724,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="624" customHeight="1" spans="1:11">
+    <row r="624" hidden="1" customHeight="1" spans="1:11">
       <c r="A624" s="7" t="s">
         <v>50</v>
       </c>
@@ -19750,7 +19750,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="625" customHeight="1" spans="1:11">
+    <row r="625" hidden="1" customHeight="1" spans="1:11">
       <c r="A625" s="7" t="s">
         <v>50</v>
       </c>
@@ -19779,7 +19779,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="626" customHeight="1" spans="1:11">
+    <row r="626" hidden="1" customHeight="1" spans="1:11">
       <c r="A626" s="7" t="s">
         <v>53</v>
       </c>
@@ -19808,7 +19808,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="627" customHeight="1" spans="1:11">
+    <row r="627" hidden="1" customHeight="1" spans="1:11">
       <c r="A627" s="7" t="s">
         <v>53</v>
       </c>
@@ -19837,7 +19837,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="628" customHeight="1" spans="1:11">
+    <row r="628" hidden="1" customHeight="1" spans="1:11">
       <c r="A628" s="7" t="s">
         <v>53</v>
       </c>
@@ -19866,7 +19866,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="629" customHeight="1" spans="1:11">
+    <row r="629" hidden="1" customHeight="1" spans="1:11">
       <c r="A629" s="7" t="s">
         <v>53</v>
       </c>
@@ -19895,7 +19895,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="630" customHeight="1" spans="1:11">
+    <row r="630" hidden="1" customHeight="1" spans="1:11">
       <c r="A630" s="7" t="s">
         <v>53</v>
       </c>
@@ -19924,7 +19924,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="631" customHeight="1" spans="1:11">
+    <row r="631" hidden="1" customHeight="1" spans="1:11">
       <c r="A631" s="7" t="s">
         <v>53</v>
       </c>
@@ -19953,7 +19953,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="632" customHeight="1" spans="1:11">
+    <row r="632" hidden="1" customHeight="1" spans="1:11">
       <c r="A632" s="7" t="s">
         <v>53</v>
       </c>
@@ -19982,7 +19982,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="633" customHeight="1" spans="1:11">
+    <row r="633" hidden="1" customHeight="1" spans="1:11">
       <c r="A633" s="7" t="s">
         <v>53</v>
       </c>
@@ -20008,7 +20008,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="634" customHeight="1" spans="1:11">
+    <row r="634" hidden="1" customHeight="1" spans="1:11">
       <c r="A634" s="7" t="s">
         <v>53</v>
       </c>
@@ -20037,7 +20037,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="635" customHeight="1" spans="1:11">
+    <row r="635" hidden="1" customHeight="1" spans="1:11">
       <c r="A635" s="7" t="s">
         <v>53</v>
       </c>
@@ -20066,7 +20066,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="636" customHeight="1" spans="1:11">
+    <row r="636" hidden="1" customHeight="1" spans="1:11">
       <c r="A636" s="7" t="s">
         <v>53</v>
       </c>
@@ -20095,7 +20095,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="637" customHeight="1" spans="1:11">
+    <row r="637" hidden="1" customHeight="1" spans="1:11">
       <c r="A637" s="7" t="s">
         <v>53</v>
       </c>
@@ -20121,7 +20121,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="638" customHeight="1" spans="1:11">
+    <row r="638" hidden="1" customHeight="1" spans="1:11">
       <c r="A638" s="7" t="s">
         <v>53</v>
       </c>
@@ -20150,7 +20150,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="639" customHeight="1" spans="1:11">
+    <row r="639" hidden="1" customHeight="1" spans="1:11">
       <c r="A639" s="7" t="s">
         <v>53</v>
       </c>
@@ -20176,7 +20176,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="640" customHeight="1" spans="1:11">
+    <row r="640" hidden="1" customHeight="1" spans="1:11">
       <c r="A640" s="7" t="s">
         <v>53</v>
       </c>
@@ -20202,7 +20202,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="641" customHeight="1" spans="1:11">
+    <row r="641" hidden="1" customHeight="1" spans="1:11">
       <c r="A641" s="7" t="s">
         <v>53</v>
       </c>
@@ -20231,7 +20231,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="642" customHeight="1" spans="1:11">
+    <row r="642" hidden="1" customHeight="1" spans="1:11">
       <c r="A642" s="7" t="s">
         <v>53</v>
       </c>
@@ -20260,7 +20260,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="643" customHeight="1" spans="1:11">
+    <row r="643" hidden="1" customHeight="1" spans="1:11">
       <c r="A643" s="7" t="s">
         <v>53</v>
       </c>
@@ -20286,7 +20286,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="644" customHeight="1" spans="1:11">
+    <row r="644" hidden="1" customHeight="1" spans="1:11">
       <c r="A644" s="7" t="s">
         <v>53</v>
       </c>
@@ -20312,7 +20312,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="645" customHeight="1" spans="1:11">
+    <row r="645" hidden="1" customHeight="1" spans="1:11">
       <c r="A645" s="7" t="s">
         <v>53</v>
       </c>
@@ -20341,7 +20341,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="646" customHeight="1" spans="1:11">
+    <row r="646" hidden="1" customHeight="1" spans="1:11">
       <c r="A646" s="7" t="s">
         <v>53</v>
       </c>
@@ -20370,7 +20370,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="647" customHeight="1" spans="1:11">
+    <row r="647" hidden="1" customHeight="1" spans="1:11">
       <c r="A647" s="7" t="s">
         <v>53</v>
       </c>
@@ -20396,7 +20396,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="648" customHeight="1" spans="1:11">
+    <row r="648" hidden="1" customHeight="1" spans="1:11">
       <c r="A648" s="7" t="s">
         <v>53</v>
       </c>
@@ -20422,7 +20422,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="649" customHeight="1" spans="1:11">
+    <row r="649" hidden="1" customHeight="1" spans="1:11">
       <c r="A649" s="7" t="s">
         <v>53</v>
       </c>
@@ -20451,7 +20451,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="650" customHeight="1" spans="1:11">
+    <row r="650" hidden="1" customHeight="1" spans="1:11">
       <c r="A650" s="8" t="s">
         <v>12</v>
       </c>
@@ -20482,7 +20482,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="651" customHeight="1" spans="1:11">
+    <row r="651" hidden="1" customHeight="1" spans="1:11">
       <c r="A651" s="7" t="s">
         <v>12</v>
       </c>
@@ -20511,7 +20511,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="652" customHeight="1" spans="1:11">
+    <row r="652" hidden="1" customHeight="1" spans="1:11">
       <c r="A652" s="7" t="s">
         <v>12</v>
       </c>
@@ -20540,7 +20540,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="653" customHeight="1" spans="1:11">
+    <row r="653" hidden="1" customHeight="1" spans="1:11">
       <c r="A653" s="7" t="s">
         <v>12</v>
       </c>
@@ -20569,7 +20569,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="654" customHeight="1" spans="1:11">
+    <row r="654" hidden="1" customHeight="1" spans="1:11">
       <c r="A654" s="7" t="s">
         <v>12</v>
       </c>
@@ -20598,7 +20598,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="655" customHeight="1" spans="1:11">
+    <row r="655" hidden="1" customHeight="1" spans="1:11">
       <c r="A655" s="7" t="s">
         <v>12</v>
       </c>
@@ -20627,7 +20627,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="656" customHeight="1" spans="1:11">
+    <row r="656" hidden="1" customHeight="1" spans="1:11">
       <c r="A656" s="7" t="s">
         <v>12</v>
       </c>
@@ -20656,7 +20656,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="657" customHeight="1" spans="1:11">
+    <row r="657" hidden="1" customHeight="1" spans="1:11">
       <c r="A657" s="7" t="s">
         <v>12</v>
       </c>
@@ -20685,7 +20685,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="658" customHeight="1" spans="1:11">
+    <row r="658" hidden="1" customHeight="1" spans="1:11">
       <c r="A658" s="7" t="s">
         <v>12</v>
       </c>
@@ -20714,7 +20714,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="659" customHeight="1" spans="1:11">
+    <row r="659" hidden="1" customHeight="1" spans="1:11">
       <c r="A659" s="7" t="s">
         <v>12</v>
       </c>
@@ -20743,7 +20743,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="660" customHeight="1" spans="1:11">
+    <row r="660" hidden="1" customHeight="1" spans="1:11">
       <c r="A660" s="7" t="s">
         <v>12</v>
       </c>
@@ -20772,7 +20772,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="661" customHeight="1" spans="1:11">
+    <row r="661" hidden="1" customHeight="1" spans="1:11">
       <c r="A661" s="7" t="s">
         <v>12</v>
       </c>
@@ -20801,7 +20801,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="662" customHeight="1" spans="1:11">
+    <row r="662" hidden="1" customHeight="1" spans="1:11">
       <c r="A662" s="7" t="s">
         <v>12</v>
       </c>
@@ -20830,7 +20830,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="663" customHeight="1" spans="1:11">
+    <row r="663" hidden="1" customHeight="1" spans="1:11">
       <c r="A663" s="7" t="s">
         <v>12</v>
       </c>
@@ -20859,7 +20859,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="664" customHeight="1" spans="1:11">
+    <row r="664" hidden="1" customHeight="1" spans="1:11">
       <c r="A664" s="7" t="s">
         <v>12</v>
       </c>
@@ -20888,7 +20888,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="665" customHeight="1" spans="1:11">
+    <row r="665" hidden="1" customHeight="1" spans="1:11">
       <c r="A665" s="7" t="s">
         <v>12</v>
       </c>
@@ -20917,7 +20917,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="666" customHeight="1" spans="1:11">
+    <row r="666" hidden="1" customHeight="1" spans="1:11">
       <c r="A666" s="7" t="s">
         <v>12</v>
       </c>
@@ -20946,7 +20946,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="667" customHeight="1" spans="1:11">
+    <row r="667" hidden="1" customHeight="1" spans="1:11">
       <c r="A667" s="7" t="s">
         <v>12</v>
       </c>
@@ -20975,7 +20975,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="668" customHeight="1" spans="1:11">
+    <row r="668" hidden="1" customHeight="1" spans="1:11">
       <c r="A668" s="7" t="s">
         <v>12</v>
       </c>
@@ -21001,7 +21001,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="669" customHeight="1" spans="1:11">
+    <row r="669" hidden="1" customHeight="1" spans="1:11">
       <c r="A669" s="7" t="s">
         <v>12</v>
       </c>
@@ -21030,7 +21030,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="670" customHeight="1" spans="1:11">
+    <row r="670" hidden="1" customHeight="1" spans="1:11">
       <c r="A670" s="7" t="s">
         <v>12</v>
       </c>
@@ -21059,7 +21059,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="671" customHeight="1" spans="1:11">
+    <row r="671" hidden="1" customHeight="1" spans="1:11">
       <c r="A671" s="7" t="s">
         <v>12</v>
       </c>
@@ -21088,7 +21088,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="672" customHeight="1" spans="1:11">
+    <row r="672" hidden="1" customHeight="1" spans="1:11">
       <c r="A672" s="7" t="s">
         <v>12</v>
       </c>
@@ -21114,7 +21114,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="673" customHeight="1" spans="1:11">
+    <row r="673" hidden="1" customHeight="1" spans="1:11">
       <c r="A673" s="7" t="s">
         <v>12</v>
       </c>
@@ -21143,7 +21143,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="674" customHeight="1" spans="1:11">
+    <row r="674" hidden="1" customHeight="1" spans="1:11">
       <c r="A674" s="7" t="s">
         <v>50</v>
       </c>
@@ -21172,7 +21172,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="675" customHeight="1" spans="1:11">
+    <row r="675" hidden="1" customHeight="1" spans="1:11">
       <c r="A675" s="7" t="s">
         <v>50</v>
       </c>
@@ -21201,7 +21201,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="676" customHeight="1" spans="1:11">
+    <row r="676" hidden="1" customHeight="1" spans="1:11">
       <c r="A676" s="7" t="s">
         <v>50</v>
       </c>
@@ -21230,7 +21230,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="677" customHeight="1" spans="1:11">
+    <row r="677" hidden="1" customHeight="1" spans="1:11">
       <c r="A677" s="7" t="s">
         <v>50</v>
       </c>
@@ -21259,7 +21259,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="678" customHeight="1" spans="1:11">
+    <row r="678" hidden="1" customHeight="1" spans="1:11">
       <c r="A678" s="7" t="s">
         <v>50</v>
       </c>
@@ -21288,7 +21288,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="679" customHeight="1" spans="1:11">
+    <row r="679" hidden="1" customHeight="1" spans="1:11">
       <c r="A679" s="7" t="s">
         <v>50</v>
       </c>
@@ -21317,7 +21317,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="680" customHeight="1" spans="1:11">
+    <row r="680" hidden="1" customHeight="1" spans="1:11">
       <c r="A680" s="7" t="s">
         <v>50</v>
       </c>
@@ -21346,7 +21346,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="681" customHeight="1" spans="1:11">
+    <row r="681" hidden="1" customHeight="1" spans="1:11">
       <c r="A681" s="7" t="s">
         <v>50</v>
       </c>
@@ -21375,7 +21375,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="682" customHeight="1" spans="1:11">
+    <row r="682" hidden="1" customHeight="1" spans="1:11">
       <c r="A682" s="7" t="s">
         <v>50</v>
       </c>
@@ -21404,7 +21404,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="683" customHeight="1" spans="1:11">
+    <row r="683" hidden="1" customHeight="1" spans="1:11">
       <c r="A683" s="7" t="s">
         <v>50</v>
       </c>
@@ -21433,7 +21433,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="684" customHeight="1" spans="1:11">
+    <row r="684" hidden="1" customHeight="1" spans="1:11">
       <c r="A684" s="7" t="s">
         <v>50</v>
       </c>
@@ -21462,7 +21462,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="685" customHeight="1" spans="1:11">
+    <row r="685" hidden="1" customHeight="1" spans="1:11">
       <c r="A685" s="7" t="s">
         <v>50</v>
       </c>
@@ -21491,7 +21491,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="686" customHeight="1" spans="1:11">
+    <row r="686" hidden="1" customHeight="1" spans="1:11">
       <c r="A686" s="7" t="s">
         <v>50</v>
       </c>
@@ -21520,7 +21520,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="687" customHeight="1" spans="1:11">
+    <row r="687" hidden="1" customHeight="1" spans="1:11">
       <c r="A687" s="7" t="s">
         <v>50</v>
       </c>
@@ -21549,7 +21549,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="688" customHeight="1" spans="1:11">
+    <row r="688" hidden="1" customHeight="1" spans="1:11">
       <c r="A688" s="7" t="s">
         <v>50</v>
       </c>
@@ -21578,7 +21578,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="689" customHeight="1" spans="1:11">
+    <row r="689" hidden="1" customHeight="1" spans="1:11">
       <c r="A689" s="7" t="s">
         <v>50</v>
       </c>
@@ -21607,7 +21607,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="690" customHeight="1" spans="1:11">
+    <row r="690" hidden="1" customHeight="1" spans="1:11">
       <c r="A690" s="7" t="s">
         <v>50</v>
       </c>
@@ -21636,7 +21636,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="691" customHeight="1" spans="1:11">
+    <row r="691" hidden="1" customHeight="1" spans="1:11">
       <c r="A691" s="7" t="s">
         <v>50</v>
       </c>
@@ -21665,7 +21665,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="692" customHeight="1" spans="1:11">
+    <row r="692" hidden="1" customHeight="1" spans="1:11">
       <c r="A692" s="7" t="s">
         <v>50</v>
       </c>
@@ -21691,7 +21691,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="693" customHeight="1" spans="1:11">
+    <row r="693" hidden="1" customHeight="1" spans="1:11">
       <c r="A693" s="7" t="s">
         <v>50</v>
       </c>
@@ -21720,7 +21720,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="694" customHeight="1" spans="1:11">
+    <row r="694" hidden="1" customHeight="1" spans="1:11">
       <c r="A694" s="7" t="s">
         <v>50</v>
       </c>
@@ -21749,7 +21749,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="695" customHeight="1" spans="1:11">
+    <row r="695" hidden="1" customHeight="1" spans="1:11">
       <c r="A695" s="7" t="s">
         <v>50</v>
       </c>
@@ -21778,7 +21778,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="696" customHeight="1" spans="1:11">
+    <row r="696" hidden="1" customHeight="1" spans="1:11">
       <c r="A696" s="7" t="s">
         <v>50</v>
       </c>
@@ -21804,7 +21804,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="697" customHeight="1" spans="1:11">
+    <row r="697" hidden="1" customHeight="1" spans="1:11">
       <c r="A697" s="7" t="s">
         <v>50</v>
       </c>
@@ -21833,7 +21833,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="698" customHeight="1" spans="1:11">
+    <row r="698" hidden="1" customHeight="1" spans="1:11">
       <c r="A698" s="7" t="s">
         <v>53</v>
       </c>
@@ -21862,7 +21862,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="699" customHeight="1" spans="1:11">
+    <row r="699" hidden="1" customHeight="1" spans="1:11">
       <c r="A699" s="7" t="s">
         <v>53</v>
       </c>
@@ -21891,7 +21891,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="700" customHeight="1" spans="1:11">
+    <row r="700" hidden="1" customHeight="1" spans="1:11">
       <c r="A700" s="7" t="s">
         <v>53</v>
       </c>
@@ -21920,7 +21920,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="701" customHeight="1" spans="1:11">
+    <row r="701" hidden="1" customHeight="1" spans="1:11">
       <c r="A701" s="7" t="s">
         <v>53</v>
       </c>
@@ -21949,7 +21949,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="702" customHeight="1" spans="1:11">
+    <row r="702" hidden="1" customHeight="1" spans="1:11">
       <c r="A702" s="7" t="s">
         <v>53</v>
       </c>
@@ -21978,7 +21978,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="703" customHeight="1" spans="1:11">
+    <row r="703" hidden="1" customHeight="1" spans="1:11">
       <c r="A703" s="7" t="s">
         <v>53</v>
       </c>
@@ -22007,7 +22007,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="704" customHeight="1" spans="1:11">
+    <row r="704" hidden="1" customHeight="1" spans="1:11">
       <c r="A704" s="7" t="s">
         <v>53</v>
       </c>
@@ -22036,7 +22036,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="705" customHeight="1" spans="1:11">
+    <row r="705" hidden="1" customHeight="1" spans="1:11">
       <c r="A705" s="7" t="s">
         <v>53</v>
       </c>
@@ -22062,7 +22062,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="706" customHeight="1" spans="1:11">
+    <row r="706" hidden="1" customHeight="1" spans="1:11">
       <c r="A706" s="7" t="s">
         <v>53</v>
       </c>
@@ -22091,7 +22091,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="707" customHeight="1" spans="1:11">
+    <row r="707" hidden="1" customHeight="1" spans="1:11">
       <c r="A707" s="7" t="s">
         <v>53</v>
       </c>
@@ -22120,7 +22120,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="708" customHeight="1" spans="1:11">
+    <row r="708" hidden="1" customHeight="1" spans="1:11">
       <c r="A708" s="7" t="s">
         <v>53</v>
       </c>
@@ -22149,7 +22149,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="709" customHeight="1" spans="1:11">
+    <row r="709" hidden="1" customHeight="1" spans="1:11">
       <c r="A709" s="7" t="s">
         <v>53</v>
       </c>
@@ -22175,7 +22175,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="710" customHeight="1" spans="1:11">
+    <row r="710" hidden="1" customHeight="1" spans="1:11">
       <c r="A710" s="7" t="s">
         <v>53</v>
       </c>
@@ -22204,7 +22204,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="711" customHeight="1" spans="1:11">
+    <row r="711" hidden="1" customHeight="1" spans="1:11">
       <c r="A711" s="7" t="s">
         <v>53</v>
       </c>
@@ -22230,7 +22230,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="712" customHeight="1" spans="1:11">
+    <row r="712" hidden="1" customHeight="1" spans="1:11">
       <c r="A712" s="7" t="s">
         <v>53</v>
       </c>
@@ -22256,7 +22256,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="713" customHeight="1" spans="1:11">
+    <row r="713" hidden="1" customHeight="1" spans="1:11">
       <c r="A713" s="7" t="s">
         <v>53</v>
       </c>
@@ -22285,7 +22285,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="714" customHeight="1" spans="1:11">
+    <row r="714" hidden="1" customHeight="1" spans="1:11">
       <c r="A714" s="7" t="s">
         <v>53</v>
       </c>
@@ -22314,7 +22314,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="715" customHeight="1" spans="1:11">
+    <row r="715" hidden="1" customHeight="1" spans="1:11">
       <c r="A715" s="7" t="s">
         <v>53</v>
       </c>
@@ -22340,7 +22340,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="716" customHeight="1" spans="1:11">
+    <row r="716" hidden="1" customHeight="1" spans="1:11">
       <c r="A716" s="7" t="s">
         <v>53</v>
       </c>
@@ -22366,7 +22366,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="717" customHeight="1" spans="1:11">
+    <row r="717" hidden="1" customHeight="1" spans="1:11">
       <c r="A717" s="7" t="s">
         <v>53</v>
       </c>
@@ -22395,7 +22395,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="718" customHeight="1" spans="1:11">
+    <row r="718" hidden="1" customHeight="1" spans="1:11">
       <c r="A718" s="7" t="s">
         <v>53</v>
       </c>
@@ -22424,7 +22424,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="719" customHeight="1" spans="1:11">
+    <row r="719" hidden="1" customHeight="1" spans="1:11">
       <c r="A719" s="7" t="s">
         <v>53</v>
       </c>
@@ -22450,7 +22450,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="720" customHeight="1" spans="1:11">
+    <row r="720" hidden="1" customHeight="1" spans="1:11">
       <c r="A720" s="7" t="s">
         <v>53</v>
       </c>
@@ -22476,7 +22476,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="721" customHeight="1" spans="1:11">
+    <row r="721" hidden="1" customHeight="1" spans="1:11">
       <c r="A721" s="7" t="s">
         <v>53</v>
       </c>
@@ -22505,7 +22505,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="722" customHeight="1" spans="1:11">
+    <row r="722" hidden="1" customHeight="1" spans="1:11">
       <c r="A722" s="8" t="s">
         <v>12</v>
       </c>
@@ -22536,7 +22536,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="723" customHeight="1" spans="1:11">
+    <row r="723" hidden="1" customHeight="1" spans="1:11">
       <c r="A723" s="7" t="s">
         <v>12</v>
       </c>
@@ -22565,7 +22565,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="724" customHeight="1" spans="1:11">
+    <row r="724" hidden="1" customHeight="1" spans="1:11">
       <c r="A724" s="7" t="s">
         <v>12</v>
       </c>
@@ -22594,7 +22594,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="725" customHeight="1" spans="1:11">
+    <row r="725" hidden="1" customHeight="1" spans="1:11">
       <c r="A725" s="7" t="s">
         <v>12</v>
       </c>
@@ -22623,7 +22623,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="726" customHeight="1" spans="1:11">
+    <row r="726" hidden="1" customHeight="1" spans="1:11">
       <c r="A726" s="7" t="s">
         <v>12</v>
       </c>
@@ -22652,7 +22652,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="727" customHeight="1" spans="1:11">
+    <row r="727" hidden="1" customHeight="1" spans="1:11">
       <c r="A727" s="7" t="s">
         <v>12</v>
       </c>
@@ -22681,7 +22681,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="728" customHeight="1" spans="1:11">
+    <row r="728" hidden="1" customHeight="1" spans="1:11">
       <c r="A728" s="7" t="s">
         <v>12</v>
       </c>
@@ -22710,7 +22710,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="729" customHeight="1" spans="1:11">
+    <row r="729" hidden="1" customHeight="1" spans="1:11">
       <c r="A729" s="7" t="s">
         <v>12</v>
       </c>
@@ -22739,7 +22739,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="730" customHeight="1" spans="1:11">
+    <row r="730" hidden="1" customHeight="1" spans="1:11">
       <c r="A730" s="7" t="s">
         <v>12</v>
       </c>
@@ -22768,7 +22768,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="731" customHeight="1" spans="1:11">
+    <row r="731" hidden="1" customHeight="1" spans="1:11">
       <c r="A731" s="7" t="s">
         <v>12</v>
       </c>
@@ -22797,7 +22797,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="732" customHeight="1" spans="1:11">
+    <row r="732" hidden="1" customHeight="1" spans="1:11">
       <c r="A732" s="7" t="s">
         <v>12</v>
       </c>
@@ -22826,7 +22826,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="733" customHeight="1" spans="1:11">
+    <row r="733" hidden="1" customHeight="1" spans="1:11">
       <c r="A733" s="7" t="s">
         <v>12</v>
       </c>
@@ -22855,7 +22855,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="734" customHeight="1" spans="1:11">
+    <row r="734" hidden="1" customHeight="1" spans="1:11">
       <c r="A734" s="7" t="s">
         <v>12</v>
       </c>
@@ -22884,7 +22884,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="735" customHeight="1" spans="1:11">
+    <row r="735" hidden="1" customHeight="1" spans="1:11">
       <c r="A735" s="7" t="s">
         <v>12</v>
       </c>
@@ -22913,7 +22913,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="736" customHeight="1" spans="1:11">
+    <row r="736" hidden="1" customHeight="1" spans="1:11">
       <c r="A736" s="7" t="s">
         <v>12</v>
       </c>
@@ -22942,7 +22942,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="737" customHeight="1" spans="1:11">
+    <row r="737" hidden="1" customHeight="1" spans="1:11">
       <c r="A737" s="7" t="s">
         <v>12</v>
       </c>
@@ -22971,7 +22971,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="738" customHeight="1" spans="1:11">
+    <row r="738" hidden="1" customHeight="1" spans="1:11">
       <c r="A738" s="7" t="s">
         <v>12</v>
       </c>
@@ -23000,7 +23000,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="739" customHeight="1" spans="1:11">
+    <row r="739" hidden="1" customHeight="1" spans="1:11">
       <c r="A739" s="7" t="s">
         <v>12</v>
       </c>
@@ -23029,7 +23029,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="740" customHeight="1" spans="1:11">
+    <row r="740" hidden="1" customHeight="1" spans="1:11">
       <c r="A740" s="7" t="s">
         <v>12</v>
       </c>
@@ -23055,7 +23055,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="741" customHeight="1" spans="1:11">
+    <row r="741" hidden="1" customHeight="1" spans="1:11">
       <c r="A741" s="7" t="s">
         <v>12</v>
       </c>
@@ -23084,7 +23084,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="742" customHeight="1" spans="1:11">
+    <row r="742" hidden="1" customHeight="1" spans="1:11">
       <c r="A742" s="7" t="s">
         <v>12</v>
       </c>
@@ -23113,7 +23113,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="743" customHeight="1" spans="1:11">
+    <row r="743" hidden="1" customHeight="1" spans="1:11">
       <c r="A743" s="7" t="s">
         <v>12</v>
       </c>
@@ -23142,7 +23142,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="744" customHeight="1" spans="1:11">
+    <row r="744" hidden="1" customHeight="1" spans="1:11">
       <c r="A744" s="7" t="s">
         <v>12</v>
       </c>
@@ -23168,7 +23168,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="745" customHeight="1" spans="1:11">
+    <row r="745" hidden="1" customHeight="1" spans="1:11">
       <c r="A745" s="7" t="s">
         <v>12</v>
       </c>
@@ -23197,7 +23197,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="746" customHeight="1" spans="1:11">
+    <row r="746" hidden="1" customHeight="1" spans="1:11">
       <c r="A746" s="7" t="s">
         <v>50</v>
       </c>
@@ -23226,7 +23226,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="747" customHeight="1" spans="1:11">
+    <row r="747" hidden="1" customHeight="1" spans="1:11">
       <c r="A747" s="7" t="s">
         <v>50</v>
       </c>
@@ -23255,7 +23255,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="748" customHeight="1" spans="1:11">
+    <row r="748" hidden="1" customHeight="1" spans="1:11">
       <c r="A748" s="7" t="s">
         <v>50</v>
       </c>
@@ -23284,7 +23284,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="749" customHeight="1" spans="1:11">
+    <row r="749" hidden="1" customHeight="1" spans="1:11">
       <c r="A749" s="7" t="s">
         <v>50</v>
       </c>
@@ -23313,7 +23313,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="750" customHeight="1" spans="1:11">
+    <row r="750" hidden="1" customHeight="1" spans="1:11">
       <c r="A750" s="7" t="s">
         <v>50</v>
       </c>
@@ -23342,7 +23342,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="751" customHeight="1" spans="1:11">
+    <row r="751" hidden="1" customHeight="1" spans="1:11">
       <c r="A751" s="7" t="s">
         <v>50</v>
       </c>
@@ -23371,7 +23371,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="752" customHeight="1" spans="1:11">
+    <row r="752" hidden="1" customHeight="1" spans="1:11">
       <c r="A752" s="7" t="s">
         <v>50</v>
       </c>
@@ -23400,7 +23400,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="753" customHeight="1" spans="1:11">
+    <row r="753" hidden="1" customHeight="1" spans="1:11">
       <c r="A753" s="7" t="s">
         <v>50</v>
       </c>
@@ -23429,7 +23429,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="754" customHeight="1" spans="1:11">
+    <row r="754" hidden="1" customHeight="1" spans="1:11">
       <c r="A754" s="7" t="s">
         <v>50</v>
       </c>
@@ -23458,7 +23458,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="755" customHeight="1" spans="1:11">
+    <row r="755" hidden="1" customHeight="1" spans="1:11">
       <c r="A755" s="7" t="s">
         <v>50</v>
       </c>
@@ -23487,7 +23487,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="756" customHeight="1" spans="1:11">
+    <row r="756" hidden="1" customHeight="1" spans="1:11">
       <c r="A756" s="7" t="s">
         <v>50</v>
       </c>
@@ -23516,7 +23516,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="757" customHeight="1" spans="1:11">
+    <row r="757" hidden="1" customHeight="1" spans="1:11">
       <c r="A757" s="7" t="s">
         <v>50</v>
       </c>
@@ -23545,7 +23545,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="758" customHeight="1" spans="1:11">
+    <row r="758" hidden="1" customHeight="1" spans="1:11">
       <c r="A758" s="7" t="s">
         <v>50</v>
       </c>
@@ -23574,7 +23574,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="759" customHeight="1" spans="1:11">
+    <row r="759" hidden="1" customHeight="1" spans="1:11">
       <c r="A759" s="7" t="s">
         <v>50</v>
       </c>
@@ -23603,7 +23603,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="760" customHeight="1" spans="1:11">
+    <row r="760" hidden="1" customHeight="1" spans="1:11">
       <c r="A760" s="7" t="s">
         <v>50</v>
       </c>
@@ -23632,7 +23632,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="761" customHeight="1" spans="1:11">
+    <row r="761" hidden="1" customHeight="1" spans="1:11">
       <c r="A761" s="7" t="s">
         <v>50</v>
       </c>
@@ -23661,7 +23661,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="762" customHeight="1" spans="1:11">
+    <row r="762" hidden="1" customHeight="1" spans="1:11">
       <c r="A762" s="7" t="s">
         <v>50</v>
       </c>
@@ -23690,7 +23690,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="763" customHeight="1" spans="1:11">
+    <row r="763" hidden="1" customHeight="1" spans="1:11">
       <c r="A763" s="7" t="s">
         <v>50</v>
       </c>
@@ -23719,7 +23719,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="764" customHeight="1" spans="1:11">
+    <row r="764" hidden="1" customHeight="1" spans="1:11">
       <c r="A764" s="7" t="s">
         <v>50</v>
       </c>
@@ -23745,7 +23745,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="765" customHeight="1" spans="1:11">
+    <row r="765" hidden="1" customHeight="1" spans="1:11">
       <c r="A765" s="7" t="s">
         <v>50</v>
       </c>
@@ -23774,7 +23774,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="766" customHeight="1" spans="1:11">
+    <row r="766" hidden="1" customHeight="1" spans="1:11">
       <c r="A766" s="7" t="s">
         <v>50</v>
       </c>
@@ -23803,7 +23803,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="767" customHeight="1" spans="1:11">
+    <row r="767" hidden="1" customHeight="1" spans="1:11">
       <c r="A767" s="7" t="s">
         <v>50</v>
       </c>
@@ -23832,7 +23832,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="768" customHeight="1" spans="1:11">
+    <row r="768" hidden="1" customHeight="1" spans="1:11">
       <c r="A768" s="7" t="s">
         <v>50</v>
       </c>
@@ -23858,7 +23858,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="769" customHeight="1" spans="1:12">
+    <row r="769" hidden="1" customHeight="1" spans="1:12">
       <c r="A769" s="7" t="s">
         <v>50</v>
       </c>
@@ -23887,7 +23887,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="770" customHeight="1" spans="1:12">
+    <row r="770" hidden="1" customHeight="1" spans="1:12">
       <c r="A770" s="7" t="s">
         <v>53</v>
       </c>
@@ -23916,7 +23916,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="771" customHeight="1" spans="1:12">
+    <row r="771" hidden="1" customHeight="1" spans="1:12">
       <c r="A771" s="7" t="s">
         <v>53</v>
       </c>
@@ -23945,7 +23945,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="772" customHeight="1" spans="1:12">
+    <row r="772" hidden="1" customHeight="1" spans="1:12">
       <c r="A772" s="7" t="s">
         <v>53</v>
       </c>
@@ -23974,7 +23974,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="773" customHeight="1" spans="1:12">
+    <row r="773" hidden="1" customHeight="1" spans="1:12">
       <c r="A773" s="7" t="s">
         <v>53</v>
       </c>
@@ -24003,7 +24003,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="774" customHeight="1" spans="1:12">
+    <row r="774" hidden="1" customHeight="1" spans="1:12">
       <c r="A774" s="7" t="s">
         <v>53</v>
       </c>
@@ -24032,7 +24032,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="775" customHeight="1" spans="1:12">
+    <row r="775" hidden="1" customHeight="1" spans="1:12">
       <c r="A775" s="7" t="s">
         <v>53</v>
       </c>
@@ -24061,7 +24061,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="776" customHeight="1" spans="1:12">
+    <row r="776" hidden="1" customHeight="1" spans="1:12">
       <c r="A776" s="7" t="s">
         <v>53</v>
       </c>
@@ -24090,7 +24090,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="777" customHeight="1" spans="1:12">
+    <row r="777" hidden="1" customHeight="1" spans="1:12">
       <c r="A777" s="7" t="s">
         <v>53</v>
       </c>
@@ -24119,7 +24119,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="778" customHeight="1" spans="1:12">
+    <row r="778" hidden="1" customHeight="1" spans="1:12">
       <c r="A778" s="7" t="s">
         <v>53</v>
       </c>
@@ -24148,7 +24148,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="779" customHeight="1" spans="1:12">
+    <row r="779" hidden="1" customHeight="1" spans="1:12">
       <c r="A779" s="7" t="s">
         <v>53</v>
       </c>
@@ -24177,7 +24177,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="780" customHeight="1" spans="1:12">
+    <row r="780" hidden="1" customHeight="1" spans="1:12">
       <c r="A780" s="7" t="s">
         <v>53</v>
       </c>
@@ -24206,7 +24206,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="781" customHeight="1" spans="1:12">
+    <row r="781" hidden="1" customHeight="1" spans="1:12">
       <c r="A781" s="7" t="s">
         <v>53</v>
       </c>
@@ -24235,7 +24235,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="782" customHeight="1" spans="1:12">
+    <row r="782" hidden="1" customHeight="1" spans="1:12">
       <c r="A782" s="7" t="s">
         <v>53</v>
       </c>
@@ -24264,7 +24264,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="783" customHeight="1" spans="1:12">
+    <row r="783" hidden="1" customHeight="1" spans="1:12">
       <c r="A783" s="7" t="s">
         <v>53</v>
       </c>
@@ -24293,7 +24293,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="784" customHeight="1" spans="1:12">
+    <row r="784" hidden="1" customHeight="1" spans="1:12">
       <c r="A784" s="7" t="s">
         <v>53</v>
       </c>
@@ -24322,7 +24322,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="785" customHeight="1" spans="1:12">
+    <row r="785" hidden="1" customHeight="1" spans="1:12">
       <c r="A785" s="7" t="s">
         <v>53</v>
       </c>
@@ -24351,7 +24351,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="786" customHeight="1" spans="1:12">
+    <row r="786" hidden="1" customHeight="1" spans="1:12">
       <c r="A786" s="7" t="s">
         <v>53</v>
       </c>
@@ -24380,7 +24380,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="787" customHeight="1" spans="1:12">
+    <row r="787" hidden="1" customHeight="1" spans="1:12">
       <c r="A787" s="7" t="s">
         <v>53</v>
       </c>
@@ -24409,7 +24409,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="788" customHeight="1" spans="1:12">
+    <row r="788" hidden="1" customHeight="1" spans="1:12">
       <c r="A788" s="7" t="s">
         <v>53</v>
       </c>
@@ -24438,7 +24438,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="789" customHeight="1" spans="1:12">
+    <row r="789" hidden="1" customHeight="1" spans="1:12">
       <c r="A789" s="7" t="s">
         <v>53</v>
       </c>
@@ -24467,7 +24467,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="790" customHeight="1" spans="1:12">
+    <row r="790" hidden="1" customHeight="1" spans="1:12">
       <c r="A790" s="7" t="s">
         <v>53</v>
       </c>
@@ -24496,7 +24496,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="791" customHeight="1" spans="1:12">
+    <row r="791" hidden="1" customHeight="1" spans="1:12">
       <c r="A791" s="7" t="s">
         <v>53</v>
       </c>
@@ -24525,7 +24525,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="792" customHeight="1" spans="1:12">
+    <row r="792" hidden="1" customHeight="1" spans="1:12">
       <c r="A792" s="7" t="s">
         <v>53</v>
       </c>
@@ -24554,7 +24554,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="793" customHeight="1" spans="1:12">
+    <row r="793" hidden="1" customHeight="1" spans="1:12">
       <c r="A793" s="7" t="s">
         <v>53</v>
       </c>
@@ -24583,7 +24583,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="794" customHeight="1" spans="1:12">
+    <row r="794" hidden="1" customHeight="1" spans="1:12">
       <c r="A794" s="8" t="s">
         <v>12</v>
       </c>
@@ -24614,7 +24614,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="795" customHeight="1" spans="1:12">
+    <row r="795" hidden="1" customHeight="1" spans="1:12">
       <c r="A795" s="7" t="s">
         <v>12</v>
       </c>
@@ -24643,7 +24643,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="796" customHeight="1" spans="1:12">
+    <row r="796" hidden="1" customHeight="1" spans="1:12">
       <c r="A796" s="7" t="s">
         <v>12</v>
       </c>
@@ -24672,7 +24672,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="797" customHeight="1" spans="1:12">
+    <row r="797" hidden="1" customHeight="1" spans="1:12">
       <c r="A797" s="7" t="s">
         <v>12</v>
       </c>
@@ -24701,7 +24701,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="798" customHeight="1" spans="1:12">
+    <row r="798" hidden="1" customHeight="1" spans="1:12">
       <c r="A798" s="7" t="s">
         <v>12</v>
       </c>
@@ -24730,7 +24730,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="799" customHeight="1" spans="1:12">
+    <row r="799" hidden="1" customHeight="1" spans="1:12">
       <c r="A799" s="7" t="s">
         <v>12</v>
       </c>
@@ -24759,7 +24759,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="800" customHeight="1" spans="1:12">
+    <row r="800" hidden="1" customHeight="1" spans="1:12">
       <c r="A800" s="7" t="s">
         <v>12</v>
       </c>
@@ -24788,7 +24788,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="801" customHeight="1" spans="1:11">
+    <row r="801" hidden="1" customHeight="1" spans="1:11">
       <c r="A801" s="7" t="s">
         <v>12</v>
       </c>
@@ -24817,7 +24817,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="802" customHeight="1" spans="1:11">
+    <row r="802" hidden="1" customHeight="1" spans="1:11">
       <c r="A802" s="7" t="s">
         <v>12</v>
       </c>
@@ -24846,7 +24846,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="803" customHeight="1" spans="1:11">
+    <row r="803" hidden="1" customHeight="1" spans="1:11">
       <c r="A803" s="7" t="s">
         <v>12</v>
       </c>
@@ -24875,7 +24875,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="804" customHeight="1" spans="1:11">
+    <row r="804" hidden="1" customHeight="1" spans="1:11">
       <c r="A804" s="7" t="s">
         <v>12</v>
       </c>
@@ -24904,7 +24904,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="805" customHeight="1" spans="1:11">
+    <row r="805" hidden="1" customHeight="1" spans="1:11">
       <c r="A805" s="7" t="s">
         <v>12</v>
       </c>
@@ -24933,7 +24933,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="806" customHeight="1" spans="1:11">
+    <row r="806" hidden="1" customHeight="1" spans="1:11">
       <c r="A806" s="7" t="s">
         <v>12</v>
       </c>
@@ -24962,7 +24962,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="807" customHeight="1" spans="1:11">
+    <row r="807" hidden="1" customHeight="1" spans="1:11">
       <c r="A807" s="7" t="s">
         <v>12</v>
       </c>
@@ -24991,7 +24991,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="808" customHeight="1" spans="1:11">
+    <row r="808" hidden="1" customHeight="1" spans="1:11">
       <c r="A808" s="7" t="s">
         <v>12</v>
       </c>
@@ -25020,7 +25020,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="809" customHeight="1" spans="1:11">
+    <row r="809" hidden="1" customHeight="1" spans="1:11">
       <c r="A809" s="7" t="s">
         <v>12</v>
       </c>
@@ -25049,7 +25049,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="810" customHeight="1" spans="1:11">
+    <row r="810" hidden="1" customHeight="1" spans="1:11">
       <c r="A810" s="7" t="s">
         <v>12</v>
       </c>
@@ -25078,7 +25078,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="811" customHeight="1" spans="1:11">
+    <row r="811" hidden="1" customHeight="1" spans="1:11">
       <c r="A811" s="7" t="s">
         <v>12</v>
       </c>
@@ -25107,7 +25107,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="812" customHeight="1" spans="1:11">
+    <row r="812" hidden="1" customHeight="1" spans="1:11">
       <c r="A812" s="7" t="s">
         <v>12</v>
       </c>
@@ -25133,7 +25133,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="813" customHeight="1" spans="1:11">
+    <row r="813" hidden="1" customHeight="1" spans="1:11">
       <c r="A813" s="7" t="s">
         <v>12</v>
       </c>
@@ -25162,7 +25162,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="814" customHeight="1" spans="1:11">
+    <row r="814" hidden="1" customHeight="1" spans="1:11">
       <c r="A814" s="7" t="s">
         <v>12</v>
       </c>
@@ -25191,7 +25191,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="815" customHeight="1" spans="1:11">
+    <row r="815" hidden="1" customHeight="1" spans="1:11">
       <c r="A815" s="7" t="s">
         <v>12</v>
       </c>
@@ -25220,7 +25220,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="816" customHeight="1" spans="1:11">
+    <row r="816" hidden="1" customHeight="1" spans="1:11">
       <c r="A816" s="7" t="s">
         <v>12</v>
       </c>
@@ -25246,7 +25246,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="817" customHeight="1" spans="1:11">
+    <row r="817" hidden="1" customHeight="1" spans="1:11">
       <c r="A817" s="7" t="s">
         <v>12</v>
       </c>
@@ -25275,7 +25275,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="818" customHeight="1" spans="1:11">
+    <row r="818" hidden="1" customHeight="1" spans="1:11">
       <c r="A818" s="7" t="s">
         <v>50</v>
       </c>
@@ -25304,7 +25304,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="819" customHeight="1" spans="1:11">
+    <row r="819" hidden="1" customHeight="1" spans="1:11">
       <c r="A819" s="7" t="s">
         <v>50</v>
       </c>
@@ -25333,7 +25333,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="820" customHeight="1" spans="1:11">
+    <row r="820" hidden="1" customHeight="1" spans="1:11">
       <c r="A820" s="7" t="s">
         <v>50</v>
       </c>
@@ -25362,7 +25362,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="821" customHeight="1" spans="1:11">
+    <row r="821" hidden="1" customHeight="1" spans="1:11">
       <c r="A821" s="7" t="s">
         <v>50</v>
       </c>
@@ -25391,7 +25391,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="822" customHeight="1" spans="1:11">
+    <row r="822" hidden="1" customHeight="1" spans="1:11">
       <c r="A822" s="7" t="s">
         <v>50</v>
       </c>
@@ -25420,7 +25420,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="823" customHeight="1" spans="1:11">
+    <row r="823" hidden="1" customHeight="1" spans="1:11">
       <c r="A823" s="7" t="s">
         <v>50</v>
       </c>
@@ -25449,7 +25449,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="824" customHeight="1" spans="1:11">
+    <row r="824" hidden="1" customHeight="1" spans="1:11">
       <c r="A824" s="7" t="s">
         <v>50</v>
       </c>
@@ -25478,7 +25478,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="825" customHeight="1" spans="1:11">
+    <row r="825" hidden="1" customHeight="1" spans="1:11">
       <c r="A825" s="7" t="s">
         <v>50</v>
       </c>
@@ -25507,7 +25507,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="826" customHeight="1" spans="1:11">
+    <row r="826" hidden="1" customHeight="1" spans="1:11">
       <c r="A826" s="7" t="s">
         <v>50</v>
       </c>
@@ -25536,7 +25536,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="827" customHeight="1" spans="1:11">
+    <row r="827" hidden="1" customHeight="1" spans="1:11">
       <c r="A827" s="7" t="s">
         <v>50</v>
       </c>
@@ -25565,7 +25565,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="828" customHeight="1" spans="1:11">
+    <row r="828" hidden="1" customHeight="1" spans="1:11">
       <c r="A828" s="7" t="s">
         <v>50</v>
       </c>
@@ -25594,7 +25594,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="829" customHeight="1" spans="1:11">
+    <row r="829" hidden="1" customHeight="1" spans="1:11">
       <c r="A829" s="7" t="s">
         <v>50</v>
       </c>
@@ -25623,7 +25623,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="830" customHeight="1" spans="1:11">
+    <row r="830" hidden="1" customHeight="1" spans="1:11">
       <c r="A830" s="7" t="s">
         <v>50</v>
       </c>
@@ -25652,7 +25652,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="831" customHeight="1" spans="1:11">
+    <row r="831" hidden="1" customHeight="1" spans="1:11">
       <c r="A831" s="7" t="s">
         <v>50</v>
       </c>
@@ -25681,7 +25681,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="832" customHeight="1" spans="1:11">
+    <row r="832" hidden="1" customHeight="1" spans="1:11">
       <c r="A832" s="7" t="s">
         <v>50</v>
       </c>
@@ -25710,7 +25710,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="833" customHeight="1" spans="1:12">
+    <row r="833" hidden="1" customHeight="1" spans="1:12">
       <c r="A833" s="7" t="s">
         <v>50</v>
       </c>
@@ -25739,7 +25739,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="834" customHeight="1" spans="1:12">
+    <row r="834" hidden="1" customHeight="1" spans="1:12">
       <c r="A834" s="7" t="s">
         <v>50</v>
       </c>
@@ -25768,7 +25768,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="835" customHeight="1" spans="1:12">
+    <row r="835" hidden="1" customHeight="1" spans="1:12">
       <c r="A835" s="7" t="s">
         <v>50</v>
       </c>
@@ -25797,7 +25797,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="836" customHeight="1" spans="1:12">
+    <row r="836" hidden="1" customHeight="1" spans="1:12">
       <c r="A836" s="7" t="s">
         <v>50</v>
       </c>
@@ -25823,7 +25823,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="837" customHeight="1" spans="1:12">
+    <row r="837" hidden="1" customHeight="1" spans="1:12">
       <c r="A837" s="7" t="s">
         <v>50</v>
       </c>
@@ -25852,7 +25852,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="838" customHeight="1" spans="1:12">
+    <row r="838" hidden="1" customHeight="1" spans="1:12">
       <c r="A838" s="7" t="s">
         <v>50</v>
       </c>
@@ -25881,7 +25881,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="839" customHeight="1" spans="1:12">
+    <row r="839" hidden="1" customHeight="1" spans="1:12">
       <c r="A839" s="7" t="s">
         <v>50</v>
       </c>
@@ -25910,7 +25910,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="840" customHeight="1" spans="1:12">
+    <row r="840" hidden="1" customHeight="1" spans="1:12">
       <c r="A840" s="7" t="s">
         <v>50</v>
       </c>
@@ -25936,7 +25936,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="841" customHeight="1" spans="1:12">
+    <row r="841" hidden="1" customHeight="1" spans="1:12">
       <c r="A841" s="7" t="s">
         <v>50</v>
       </c>
@@ -25965,7 +25965,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="842" customHeight="1" spans="1:12">
+    <row r="842" hidden="1" customHeight="1" spans="1:12">
       <c r="A842" s="7" t="s">
         <v>53</v>
       </c>
@@ -25994,7 +25994,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="843" customHeight="1" spans="1:12">
+    <row r="843" hidden="1" customHeight="1" spans="1:12">
       <c r="A843" s="7" t="s">
         <v>53</v>
       </c>
@@ -26023,7 +26023,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="844" customHeight="1" spans="1:12">
+    <row r="844" hidden="1" customHeight="1" spans="1:12">
       <c r="A844" s="7" t="s">
         <v>53</v>
       </c>
@@ -26052,7 +26052,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="845" customHeight="1" spans="1:12">
+    <row r="845" hidden="1" customHeight="1" spans="1:12">
       <c r="A845" s="7" t="s">
         <v>53</v>
       </c>
@@ -26081,7 +26081,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="846" customHeight="1" spans="1:12">
+    <row r="846" hidden="1" customHeight="1" spans="1:12">
       <c r="A846" s="7" t="s">
         <v>53</v>
       </c>
@@ -26110,7 +26110,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="847" customHeight="1" spans="1:12">
+    <row r="847" hidden="1" customHeight="1" spans="1:12">
       <c r="A847" s="7" t="s">
         <v>53</v>
       </c>
@@ -26139,7 +26139,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="848" customHeight="1" spans="1:12">
+    <row r="848" hidden="1" customHeight="1" spans="1:12">
       <c r="A848" s="7" t="s">
         <v>53</v>
       </c>
@@ -26168,7 +26168,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="849" customHeight="1" spans="1:12">
+    <row r="849" hidden="1" customHeight="1" spans="1:12">
       <c r="A849" s="7" t="s">
         <v>53</v>
       </c>
@@ -26197,7 +26197,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="850" customHeight="1" spans="1:12">
+    <row r="850" hidden="1" customHeight="1" spans="1:12">
       <c r="A850" s="7" t="s">
         <v>53</v>
       </c>
@@ -26226,7 +26226,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="851" customHeight="1" spans="1:12">
+    <row r="851" hidden="1" customHeight="1" spans="1:12">
       <c r="A851" s="7" t="s">
         <v>53</v>
       </c>
@@ -26255,7 +26255,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="852" customHeight="1" spans="1:12">
+    <row r="852" hidden="1" customHeight="1" spans="1:12">
       <c r="A852" s="7" t="s">
         <v>53</v>
       </c>
@@ -26284,7 +26284,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="853" customHeight="1" spans="1:12">
+    <row r="853" hidden="1" customHeight="1" spans="1:12">
       <c r="A853" s="7" t="s">
         <v>53</v>
       </c>
@@ -26313,7 +26313,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="854" customHeight="1" spans="1:12">
+    <row r="854" hidden="1" customHeight="1" spans="1:12">
       <c r="A854" s="7" t="s">
         <v>53</v>
       </c>
@@ -26342,7 +26342,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="855" customHeight="1" spans="1:12">
+    <row r="855" hidden="1" customHeight="1" spans="1:12">
       <c r="A855" s="7" t="s">
         <v>53</v>
       </c>
@@ -26371,7 +26371,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="856" customHeight="1" spans="1:12">
+    <row r="856" hidden="1" customHeight="1" spans="1:12">
       <c r="A856" s="7" t="s">
         <v>53</v>
       </c>
@@ -26400,7 +26400,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="857" customHeight="1" spans="1:12">
+    <row r="857" hidden="1" customHeight="1" spans="1:12">
       <c r="A857" s="7" t="s">
         <v>53</v>
       </c>
@@ -26429,7 +26429,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="858" customHeight="1" spans="1:12">
+    <row r="858" hidden="1" customHeight="1" spans="1:12">
       <c r="A858" s="7" t="s">
         <v>53</v>
       </c>
@@ -26458,7 +26458,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="859" customHeight="1" spans="1:12">
+    <row r="859" hidden="1" customHeight="1" spans="1:12">
       <c r="A859" s="7" t="s">
         <v>53</v>
       </c>
@@ -26487,7 +26487,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="860" customHeight="1" spans="1:12">
+    <row r="860" hidden="1" customHeight="1" spans="1:12">
       <c r="A860" s="7" t="s">
         <v>53</v>
       </c>
@@ -26516,7 +26516,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="861" customHeight="1" spans="1:12">
+    <row r="861" hidden="1" customHeight="1" spans="1:12">
       <c r="A861" s="7" t="s">
         <v>53</v>
       </c>
@@ -26545,7 +26545,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="862" customHeight="1" spans="1:12">
+    <row r="862" hidden="1" customHeight="1" spans="1:12">
       <c r="A862" s="7" t="s">
         <v>53</v>
       </c>
@@ -26574,7 +26574,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="863" customHeight="1" spans="1:12">
+    <row r="863" hidden="1" customHeight="1" spans="1:12">
       <c r="A863" s="7" t="s">
         <v>53</v>
       </c>
@@ -26603,7 +26603,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="864" customHeight="1" spans="1:12">
+    <row r="864" hidden="1" customHeight="1" spans="1:12">
       <c r="A864" s="7" t="s">
         <v>53</v>
       </c>
@@ -26632,7 +26632,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="865" customHeight="1" spans="1:12">
+    <row r="865" hidden="1" customHeight="1" spans="1:12">
       <c r="A865" s="7" t="s">
         <v>53</v>
       </c>
@@ -26661,7 +26661,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="866" customHeight="1" spans="1:12">
+    <row r="866" hidden="1" customHeight="1" spans="1:12">
       <c r="A866" s="8" t="s">
         <v>12</v>
       </c>
@@ -26692,7 +26692,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="867" customHeight="1" spans="1:12">
+    <row r="867" hidden="1" customHeight="1" spans="1:12">
       <c r="A867" s="7" t="s">
         <v>12</v>
       </c>
@@ -26721,7 +26721,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="868" customHeight="1" spans="1:12">
+    <row r="868" hidden="1" customHeight="1" spans="1:12">
       <c r="A868" s="7" t="s">
         <v>12</v>
       </c>
@@ -26750,7 +26750,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="869" customHeight="1" spans="1:12">
+    <row r="869" hidden="1" customHeight="1" spans="1:12">
       <c r="A869" s="7" t="s">
         <v>12</v>
       </c>
@@ -26779,7 +26779,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="870" customHeight="1" spans="1:12">
+    <row r="870" hidden="1" customHeight="1" spans="1:12">
       <c r="A870" s="7" t="s">
         <v>12</v>
       </c>
@@ -26808,7 +26808,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="871" customHeight="1" spans="1:12">
+    <row r="871" hidden="1" customHeight="1" spans="1:12">
       <c r="A871" s="7" t="s">
         <v>12</v>
       </c>
@@ -26837,7 +26837,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="872" customHeight="1" spans="1:12">
+    <row r="872" hidden="1" customHeight="1" spans="1:12">
       <c r="A872" s="7" t="s">
         <v>12</v>
       </c>
@@ -26866,7 +26866,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="873" customHeight="1" spans="1:12">
+    <row r="873" hidden="1" customHeight="1" spans="1:12">
       <c r="A873" s="7" t="s">
         <v>12</v>
       </c>
@@ -26895,7 +26895,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="874" customHeight="1" spans="1:12">
+    <row r="874" hidden="1" customHeight="1" spans="1:12">
       <c r="A874" s="7" t="s">
         <v>12</v>
       </c>
@@ -26924,7 +26924,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="875" customHeight="1" spans="1:12">
+    <row r="875" hidden="1" customHeight="1" spans="1:12">
       <c r="A875" s="7" t="s">
         <v>12</v>
       </c>
@@ -26953,7 +26953,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="876" customHeight="1" spans="1:12">
+    <row r="876" hidden="1" customHeight="1" spans="1:12">
       <c r="A876" s="7" t="s">
         <v>12</v>
       </c>
@@ -26982,7 +26982,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="877" customHeight="1" spans="1:12">
+    <row r="877" hidden="1" customHeight="1" spans="1:12">
       <c r="A877" s="7" t="s">
         <v>12</v>
       </c>
@@ -27011,7 +27011,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="878" customHeight="1" spans="1:12">
+    <row r="878" hidden="1" customHeight="1" spans="1:12">
       <c r="A878" s="7" t="s">
         <v>12</v>
       </c>
@@ -27040,7 +27040,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="879" customHeight="1" spans="1:12">
+    <row r="879" hidden="1" customHeight="1" spans="1:12">
       <c r="A879" s="7" t="s">
         <v>12</v>
       </c>
@@ -27069,7 +27069,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="880" customHeight="1" spans="1:12">
+    <row r="880" hidden="1" customHeight="1" spans="1:12">
       <c r="A880" s="7" t="s">
         <v>12</v>
       </c>
@@ -27098,7 +27098,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="881" customHeight="1" spans="1:11">
+    <row r="881" hidden="1" customHeight="1" spans="1:11">
       <c r="A881" s="7" t="s">
         <v>12</v>
       </c>
@@ -27127,7 +27127,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="882" customHeight="1" spans="1:11">
+    <row r="882" hidden="1" customHeight="1" spans="1:11">
       <c r="A882" s="7" t="s">
         <v>12</v>
       </c>
@@ -27156,7 +27156,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="883" customHeight="1" spans="1:11">
+    <row r="883" hidden="1" customHeight="1" spans="1:11">
       <c r="A883" s="7" t="s">
         <v>12</v>
       </c>
@@ -27185,7 +27185,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="884" customHeight="1" spans="1:11">
+    <row r="884" hidden="1" customHeight="1" spans="1:11">
       <c r="A884" s="7" t="s">
         <v>12</v>
       </c>
@@ -27211,7 +27211,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="885" customHeight="1" spans="1:11">
+    <row r="885" hidden="1" customHeight="1" spans="1:11">
       <c r="A885" s="7" t="s">
         <v>12</v>
       </c>
@@ -27240,7 +27240,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="886" customHeight="1" spans="1:11">
+    <row r="886" hidden="1" customHeight="1" spans="1:11">
       <c r="A886" s="7" t="s">
         <v>12</v>
       </c>
@@ -27269,7 +27269,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="887" customHeight="1" spans="1:11">
+    <row r="887" hidden="1" customHeight="1" spans="1:11">
       <c r="A887" s="7" t="s">
         <v>12</v>
       </c>
@@ -27298,7 +27298,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="888" customHeight="1" spans="1:11">
+    <row r="888" hidden="1" customHeight="1" spans="1:11">
       <c r="A888" s="7" t="s">
         <v>12</v>
       </c>
@@ -27324,7 +27324,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="889" customHeight="1" spans="1:11">
+    <row r="889" hidden="1" customHeight="1" spans="1:11">
       <c r="A889" s="7" t="s">
         <v>12</v>
       </c>
@@ -27353,7 +27353,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="890" customHeight="1" spans="1:11">
+    <row r="890" hidden="1" customHeight="1" spans="1:11">
       <c r="A890" s="7" t="s">
         <v>50</v>
       </c>
@@ -27382,7 +27382,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="891" customHeight="1" spans="1:11">
+    <row r="891" hidden="1" customHeight="1" spans="1:11">
       <c r="A891" s="7" t="s">
         <v>50</v>
       </c>
@@ -27411,7 +27411,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="892" customHeight="1" spans="1:11">
+    <row r="892" hidden="1" customHeight="1" spans="1:11">
       <c r="A892" s="7" t="s">
         <v>50</v>
       </c>
@@ -27440,7 +27440,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="893" customHeight="1" spans="1:11">
+    <row r="893" hidden="1" customHeight="1" spans="1:11">
       <c r="A893" s="7" t="s">
         <v>50</v>
       </c>
@@ -27469,7 +27469,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="894" customHeight="1" spans="1:11">
+    <row r="894" hidden="1" customHeight="1" spans="1:11">
       <c r="A894" s="7" t="s">
         <v>50</v>
       </c>
@@ -27498,7 +27498,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="895" customHeight="1" spans="1:11">
+    <row r="895" hidden="1" customHeight="1" spans="1:11">
       <c r="A895" s="7" t="s">
         <v>50</v>
       </c>
@@ -27527,7 +27527,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="896" customHeight="1" spans="1:11">
+    <row r="896" hidden="1" customHeight="1" spans="1:11">
       <c r="A896" s="7" t="s">
         <v>50</v>
       </c>
@@ -27556,7 +27556,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="897" customHeight="1" spans="1:11">
+    <row r="897" hidden="1" customHeight="1" spans="1:11">
       <c r="A897" s="7" t="s">
         <v>50</v>
       </c>
@@ -27585,7 +27585,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="898" customHeight="1" spans="1:11">
+    <row r="898" hidden="1" customHeight="1" spans="1:11">
       <c r="A898" s="7" t="s">
         <v>50</v>
       </c>
@@ -27614,7 +27614,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="899" customHeight="1" spans="1:11">
+    <row r="899" hidden="1" customHeight="1" spans="1:11">
       <c r="A899" s="7" t="s">
         <v>50</v>
       </c>
@@ -27643,7 +27643,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="900" customHeight="1" spans="1:11">
+    <row r="900" hidden="1" customHeight="1" spans="1:11">
       <c r="A900" s="7" t="s">
         <v>50</v>
       </c>
@@ -27672,7 +27672,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="901" customHeight="1" spans="1:11">
+    <row r="901" hidden="1" customHeight="1" spans="1:11">
       <c r="A901" s="7" t="s">
         <v>50</v>
       </c>
@@ -27701,7 +27701,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="902" customHeight="1" spans="1:11">
+    <row r="902" hidden="1" customHeight="1" spans="1:11">
       <c r="A902" s="7" t="s">
         <v>50</v>
       </c>
@@ -27730,7 +27730,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="903" customHeight="1" spans="1:11">
+    <row r="903" hidden="1" customHeight="1" spans="1:11">
       <c r="A903" s="7" t="s">
         <v>50</v>
       </c>
@@ -27759,7 +27759,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="904" customHeight="1" spans="1:11">
+    <row r="904" hidden="1" customHeight="1" spans="1:11">
       <c r="A904" s="7" t="s">
         <v>50</v>
       </c>
@@ -27788,7 +27788,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="905" customHeight="1" spans="1:11">
+    <row r="905" hidden="1" customHeight="1" spans="1:11">
       <c r="A905" s="7" t="s">
         <v>50</v>
       </c>
@@ -27817,7 +27817,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="906" customHeight="1" spans="1:11">
+    <row r="906" hidden="1" customHeight="1" spans="1:11">
       <c r="A906" s="7" t="s">
         <v>50</v>
       </c>
@@ -27846,7 +27846,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="907" customHeight="1" spans="1:11">
+    <row r="907" hidden="1" customHeight="1" spans="1:11">
       <c r="A907" s="7" t="s">
         <v>50</v>
       </c>
@@ -27875,7 +27875,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="908" customHeight="1" spans="1:11">
+    <row r="908" hidden="1" customHeight="1" spans="1:11">
       <c r="A908" s="7" t="s">
         <v>50</v>
       </c>
@@ -27901,7 +27901,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="909" customHeight="1" spans="1:11">
+    <row r="909" hidden="1" customHeight="1" spans="1:11">
       <c r="A909" s="7" t="s">
         <v>50</v>
       </c>
@@ -27930,7 +27930,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="910" customHeight="1" spans="1:11">
+    <row r="910" hidden="1" customHeight="1" spans="1:11">
       <c r="A910" s="7" t="s">
         <v>50</v>
       </c>
@@ -27959,7 +27959,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="911" customHeight="1" spans="1:11">
+    <row r="911" hidden="1" customHeight="1" spans="1:11">
       <c r="A911" s="7" t="s">
         <v>50</v>
       </c>
@@ -27988,7 +27988,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="912" customHeight="1" spans="1:11">
+    <row r="912" hidden="1" customHeight="1" spans="1:11">
       <c r="A912" s="7" t="s">
         <v>50</v>
       </c>
@@ -28014,7 +28014,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="913" customHeight="1" spans="1:11">
+    <row r="913" hidden="1" customHeight="1" spans="1:11">
       <c r="A913" s="7" t="s">
         <v>50</v>
       </c>
@@ -28043,7 +28043,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="914" customHeight="1" spans="1:11">
+    <row r="914" hidden="1" customHeight="1" spans="1:11">
       <c r="A914" s="7" t="s">
         <v>53</v>
       </c>
@@ -28072,7 +28072,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="915" customHeight="1" spans="1:11">
+    <row r="915" hidden="1" customHeight="1" spans="1:11">
       <c r="A915" s="7" t="s">
         <v>53</v>
       </c>
@@ -28101,7 +28101,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="916" customHeight="1" spans="1:11">
+    <row r="916" hidden="1" customHeight="1" spans="1:11">
       <c r="A916" s="7" t="s">
         <v>53</v>
       </c>
@@ -28130,7 +28130,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="917" customHeight="1" spans="1:11">
+    <row r="917" hidden="1" customHeight="1" spans="1:11">
       <c r="A917" s="7" t="s">
         <v>53</v>
       </c>
@@ -28159,7 +28159,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="918" customHeight="1" spans="1:11">
+    <row r="918" hidden="1" customHeight="1" spans="1:11">
       <c r="A918" s="7" t="s">
         <v>53</v>
       </c>
@@ -28188,7 +28188,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="919" customHeight="1" spans="1:11">
+    <row r="919" hidden="1" customHeight="1" spans="1:11">
       <c r="A919" s="7" t="s">
         <v>53</v>
       </c>
@@ -28217,7 +28217,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="920" customHeight="1" spans="1:11">
+    <row r="920" hidden="1" customHeight="1" spans="1:11">
       <c r="A920" s="7" t="s">
         <v>53</v>
       </c>
@@ -28246,7 +28246,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="921" customHeight="1" spans="1:11">
+    <row r="921" hidden="1" customHeight="1" spans="1:11">
       <c r="A921" s="7" t="s">
         <v>53</v>
       </c>
@@ -28272,7 +28272,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="922" customHeight="1" spans="1:11">
+    <row r="922" hidden="1" customHeight="1" spans="1:11">
       <c r="A922" s="7" t="s">
         <v>53</v>
       </c>
@@ -28301,7 +28301,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="923" customHeight="1" spans="1:11">
+    <row r="923" hidden="1" customHeight="1" spans="1:11">
       <c r="A923" s="7" t="s">
         <v>53</v>
       </c>
@@ -28330,7 +28330,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="924" customHeight="1" spans="1:11">
+    <row r="924" hidden="1" customHeight="1" spans="1:11">
       <c r="A924" s="7" t="s">
         <v>53</v>
       </c>
@@ -28359,7 +28359,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="925" customHeight="1" spans="1:11">
+    <row r="925" hidden="1" customHeight="1" spans="1:11">
       <c r="A925" s="7" t="s">
         <v>53</v>
       </c>
@@ -28385,7 +28385,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="926" customHeight="1" spans="1:11">
+    <row r="926" hidden="1" customHeight="1" spans="1:11">
       <c r="A926" s="7" t="s">
         <v>53</v>
       </c>
@@ -28414,7 +28414,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="927" customHeight="1" spans="1:11">
+    <row r="927" hidden="1" customHeight="1" spans="1:11">
       <c r="A927" s="7" t="s">
         <v>53</v>
       </c>
@@ -28440,7 +28440,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="928" customHeight="1" spans="1:11">
+    <row r="928" hidden="1" customHeight="1" spans="1:11">
       <c r="A928" s="7" t="s">
         <v>53</v>
       </c>
@@ -28466,7 +28466,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="929" customHeight="1" spans="1:11">
+    <row r="929" hidden="1" customHeight="1" spans="1:11">
       <c r="A929" s="7" t="s">
         <v>53</v>
       </c>
@@ -28495,7 +28495,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="930" customHeight="1" spans="1:11">
+    <row r="930" hidden="1" customHeight="1" spans="1:11">
       <c r="A930" s="7" t="s">
         <v>53</v>
       </c>
@@ -28524,7 +28524,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="931" customHeight="1" spans="1:11">
+    <row r="931" hidden="1" customHeight="1" spans="1:11">
       <c r="A931" s="7" t="s">
         <v>53</v>
       </c>
@@ -28550,7 +28550,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="932" customHeight="1" spans="1:11">
+    <row r="932" hidden="1" customHeight="1" spans="1:11">
       <c r="A932" s="7" t="s">
         <v>53</v>
       </c>
@@ -28576,7 +28576,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="933" customHeight="1" spans="1:11">
+    <row r="933" hidden="1" customHeight="1" spans="1:11">
       <c r="A933" s="7" t="s">
         <v>53</v>
       </c>
@@ -28605,7 +28605,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="934" customHeight="1" spans="1:11">
+    <row r="934" hidden="1" customHeight="1" spans="1:11">
       <c r="A934" s="7" t="s">
         <v>53</v>
       </c>
@@ -28634,7 +28634,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="935" customHeight="1" spans="1:11">
+    <row r="935" hidden="1" customHeight="1" spans="1:11">
       <c r="A935" s="7" t="s">
         <v>53</v>
       </c>
@@ -28660,7 +28660,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="936" customHeight="1" spans="1:11">
+    <row r="936" hidden="1" customHeight="1" spans="1:11">
       <c r="A936" s="7" t="s">
         <v>53</v>
       </c>
@@ -28686,7 +28686,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="937" customHeight="1" spans="1:11">
+    <row r="937" hidden="1" customHeight="1" spans="1:11">
       <c r="A937" s="7" t="s">
         <v>53</v>
       </c>
@@ -28715,7 +28715,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="938" customHeight="1" spans="1:11">
+    <row r="938" hidden="1" customHeight="1" spans="1:11">
       <c r="A938" s="8" t="s">
         <v>12</v>
       </c>
@@ -28746,7 +28746,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="939" customHeight="1" spans="1:11">
+    <row r="939" hidden="1" customHeight="1" spans="1:11">
       <c r="A939" s="7" t="s">
         <v>12</v>
       </c>
@@ -28775,7 +28775,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="940" customHeight="1" spans="1:11">
+    <row r="940" hidden="1" customHeight="1" spans="1:11">
       <c r="A940" s="7" t="s">
         <v>12</v>
       </c>
@@ -28804,7 +28804,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="941" customHeight="1" spans="1:11">
+    <row r="941" hidden="1" customHeight="1" spans="1:11">
       <c r="A941" s="7" t="s">
         <v>12</v>
       </c>
@@ -28833,7 +28833,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="942" customHeight="1" spans="1:11">
+    <row r="942" hidden="1" customHeight="1" spans="1:11">
       <c r="A942" s="7" t="s">
         <v>12</v>
       </c>
@@ -28862,7 +28862,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="943" customHeight="1" spans="1:11">
+    <row r="943" hidden="1" customHeight="1" spans="1:11">
       <c r="A943" s="7" t="s">
         <v>12</v>
       </c>
@@ -28891,7 +28891,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="944" customHeight="1" spans="1:11">
+    <row r="944" hidden="1" customHeight="1" spans="1:11">
       <c r="A944" s="7" t="s">
         <v>12</v>
       </c>
@@ -28920,7 +28920,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="945" customHeight="1" spans="1:11">
+    <row r="945" hidden="1" customHeight="1" spans="1:11">
       <c r="A945" s="7" t="s">
         <v>12</v>
       </c>
@@ -28949,7 +28949,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="946" customHeight="1" spans="1:11">
+    <row r="946" hidden="1" customHeight="1" spans="1:11">
       <c r="A946" s="7" t="s">
         <v>12</v>
       </c>
@@ -28978,7 +28978,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="947" customHeight="1" spans="1:11">
+    <row r="947" hidden="1" customHeight="1" spans="1:11">
       <c r="A947" s="7" t="s">
         <v>12</v>
       </c>
@@ -29007,7 +29007,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="948" customHeight="1" spans="1:11">
+    <row r="948" hidden="1" customHeight="1" spans="1:11">
       <c r="A948" s="7" t="s">
         <v>12</v>
       </c>
@@ -29036,7 +29036,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="949" customHeight="1" spans="1:11">
+    <row r="949" hidden="1" customHeight="1" spans="1:11">
       <c r="A949" s="7" t="s">
         <v>12</v>
       </c>
@@ -29065,7 +29065,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="950" customHeight="1" spans="1:11">
+    <row r="950" hidden="1" customHeight="1" spans="1:11">
       <c r="A950" s="7" t="s">
         <v>12</v>
       </c>
@@ -29094,7 +29094,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="951" customHeight="1" spans="1:11">
+    <row r="951" hidden="1" customHeight="1" spans="1:11">
       <c r="A951" s="7" t="s">
         <v>12</v>
       </c>
@@ -29123,7 +29123,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="952" customHeight="1" spans="1:11">
+    <row r="952" hidden="1" customHeight="1" spans="1:11">
       <c r="A952" s="7" t="s">
         <v>12</v>
       </c>
@@ -29152,7 +29152,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="953" customHeight="1" spans="1:11">
+    <row r="953" hidden="1" customHeight="1" spans="1:11">
       <c r="A953" s="7" t="s">
         <v>12</v>
       </c>
@@ -29181,7 +29181,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="954" customHeight="1" spans="1:11">
+    <row r="954" hidden="1" customHeight="1" spans="1:11">
       <c r="A954" s="7" t="s">
         <v>12</v>
       </c>
@@ -29210,7 +29210,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="955" customHeight="1" spans="1:11">
+    <row r="955" hidden="1" customHeight="1" spans="1:11">
       <c r="A955" s="7" t="s">
         <v>12</v>
       </c>
@@ -29239,7 +29239,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="956" customHeight="1" spans="1:11">
+    <row r="956" hidden="1" customHeight="1" spans="1:11">
       <c r="A956" s="7" t="s">
         <v>12</v>
       </c>
@@ -29265,7 +29265,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="957" customHeight="1" spans="1:11">
+    <row r="957" hidden="1" customHeight="1" spans="1:11">
       <c r="A957" s="7" t="s">
         <v>12</v>
       </c>
@@ -29294,7 +29294,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="958" customHeight="1" spans="1:11">
+    <row r="958" hidden="1" customHeight="1" spans="1:11">
       <c r="A958" s="7" t="s">
         <v>12</v>
       </c>
@@ -29323,7 +29323,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="959" customHeight="1" spans="1:11">
+    <row r="959" hidden="1" customHeight="1" spans="1:11">
       <c r="A959" s="7" t="s">
         <v>12</v>
       </c>
@@ -29352,7 +29352,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="960" customHeight="1" spans="1:11">
+    <row r="960" hidden="1" customHeight="1" spans="1:11">
       <c r="A960" s="7" t="s">
         <v>12</v>
       </c>
@@ -29378,7 +29378,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="961" customHeight="1" spans="1:11">
+    <row r="961" hidden="1" customHeight="1" spans="1:11">
       <c r="A961" s="7" t="s">
         <v>12</v>
       </c>
@@ -29407,7 +29407,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="962" customHeight="1" spans="1:11">
+    <row r="962" hidden="1" customHeight="1" spans="1:11">
       <c r="A962" s="7" t="s">
         <v>50</v>
       </c>
@@ -29436,7 +29436,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="963" customHeight="1" spans="1:11">
+    <row r="963" hidden="1" customHeight="1" spans="1:11">
       <c r="A963" s="7" t="s">
         <v>50</v>
       </c>
@@ -29465,7 +29465,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="964" customHeight="1" spans="1:11">
+    <row r="964" hidden="1" customHeight="1" spans="1:11">
       <c r="A964" s="7" t="s">
         <v>50</v>
       </c>
@@ -29494,7 +29494,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="965" customHeight="1" spans="1:11">
+    <row r="965" hidden="1" customHeight="1" spans="1:11">
       <c r="A965" s="7" t="s">
         <v>50</v>
       </c>
@@ -29523,7 +29523,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="966" customHeight="1" spans="1:11">
+    <row r="966" hidden="1" customHeight="1" spans="1:11">
       <c r="A966" s="7" t="s">
         <v>50</v>
       </c>
@@ -29552,7 +29552,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="967" customHeight="1" spans="1:11">
+    <row r="967" hidden="1" customHeight="1" spans="1:11">
       <c r="A967" s="7" t="s">
         <v>50</v>
       </c>
@@ -29581,7 +29581,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="968" customHeight="1" spans="1:11">
+    <row r="968" hidden="1" customHeight="1" spans="1:11">
       <c r="A968" s="7" t="s">
         <v>50</v>
       </c>
@@ -29610,7 +29610,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="969" customHeight="1" spans="1:11">
+    <row r="969" hidden="1" customHeight="1" spans="1:11">
       <c r="A969" s="7" t="s">
         <v>50</v>
       </c>
@@ -29639,7 +29639,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="970" customHeight="1" spans="1:11">
+    <row r="970" hidden="1" customHeight="1" spans="1:11">
       <c r="A970" s="7" t="s">
         <v>50</v>
       </c>
@@ -29668,7 +29668,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="971" customHeight="1" spans="1:11">
+    <row r="971" hidden="1" customHeight="1" spans="1:11">
       <c r="A971" s="7" t="s">
         <v>50</v>
       </c>
@@ -29697,7 +29697,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="972" customHeight="1" spans="1:11">
+    <row r="972" hidden="1" customHeight="1" spans="1:11">
       <c r="A972" s="7" t="s">
         <v>50</v>
       </c>
@@ -29726,7 +29726,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="973" customHeight="1" spans="1:11">
+    <row r="973" hidden="1" customHeight="1" spans="1:11">
       <c r="A973" s="7" t="s">
         <v>50</v>
       </c>
@@ -29755,7 +29755,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="974" customHeight="1" spans="1:11">
+    <row r="974" hidden="1" customHeight="1" spans="1:11">
       <c r="A974" s="7" t="s">
         <v>50</v>
       </c>
@@ -29784,7 +29784,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="975" customHeight="1" spans="1:11">
+    <row r="975" hidden="1" customHeight="1" spans="1:11">
       <c r="A975" s="7" t="s">
         <v>50</v>
       </c>
@@ -29813,7 +29813,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="976" customHeight="1" spans="1:11">
+    <row r="976" hidden="1" customHeight="1" spans="1:11">
       <c r="A976" s="7" t="s">
         <v>50</v>
       </c>
@@ -29842,7 +29842,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="977" customHeight="1" spans="1:12">
+    <row r="977" hidden="1" customHeight="1" spans="1:12">
       <c r="A977" s="7" t="s">
         <v>50</v>
       </c>
@@ -29871,7 +29871,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="978" customHeight="1" spans="1:12">
+    <row r="978" hidden="1" customHeight="1" spans="1:12">
       <c r="A978" s="7" t="s">
         <v>50</v>
       </c>
@@ -29900,7 +29900,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="979" customHeight="1" spans="1:12">
+    <row r="979" hidden="1" customHeight="1" spans="1:12">
       <c r="A979" s="7" t="s">
         <v>50</v>
       </c>
@@ -29929,7 +29929,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="980" customHeight="1" spans="1:12">
+    <row r="980" hidden="1" customHeight="1" spans="1:12">
       <c r="A980" s="7" t="s">
         <v>50</v>
       </c>
@@ -29955,7 +29955,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="981" customHeight="1" spans="1:12">
+    <row r="981" hidden="1" customHeight="1" spans="1:12">
       <c r="A981" s="7" t="s">
         <v>50</v>
       </c>
@@ -29984,7 +29984,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="982" customHeight="1" spans="1:12">
+    <row r="982" hidden="1" customHeight="1" spans="1:12">
       <c r="A982" s="7" t="s">
         <v>50</v>
       </c>
@@ -30013,7 +30013,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="983" customHeight="1" spans="1:12">
+    <row r="983" hidden="1" customHeight="1" spans="1:12">
       <c r="A983" s="7" t="s">
         <v>50</v>
       </c>
@@ -30042,7 +30042,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="984" customHeight="1" spans="1:12">
+    <row r="984" hidden="1" customHeight="1" spans="1:12">
       <c r="A984" s="7" t="s">
         <v>50</v>
       </c>
@@ -30068,7 +30068,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="985" customHeight="1" spans="1:12">
+    <row r="985" hidden="1" customHeight="1" spans="1:12">
       <c r="A985" s="7" t="s">
         <v>50</v>
       </c>
@@ -30097,7 +30097,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="986" customHeight="1" spans="1:12">
+    <row r="986" hidden="1" customHeight="1" spans="1:12">
       <c r="A986" s="7" t="s">
         <v>53</v>
       </c>
@@ -30126,7 +30126,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="987" customHeight="1" spans="1:12">
+    <row r="987" hidden="1" customHeight="1" spans="1:12">
       <c r="A987" s="7" t="s">
         <v>53</v>
       </c>
@@ -30155,7 +30155,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="988" customHeight="1" spans="1:12">
+    <row r="988" hidden="1" customHeight="1" spans="1:12">
       <c r="A988" s="7" t="s">
         <v>53</v>
       </c>
@@ -30184,7 +30184,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="989" customHeight="1" spans="1:12">
+    <row r="989" hidden="1" customHeight="1" spans="1:12">
       <c r="A989" s="7" t="s">
         <v>53</v>
       </c>
@@ -30213,7 +30213,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="990" customHeight="1" spans="1:12">
+    <row r="990" hidden="1" customHeight="1" spans="1:12">
       <c r="A990" s="7" t="s">
         <v>53</v>
       </c>
@@ -30242,7 +30242,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="991" customHeight="1" spans="1:12">
+    <row r="991" hidden="1" customHeight="1" spans="1:12">
       <c r="A991" s="7" t="s">
         <v>53</v>
       </c>
@@ -30271,7 +30271,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="992" customHeight="1" spans="1:12">
+    <row r="992" hidden="1" customHeight="1" spans="1:12">
       <c r="A992" s="7" t="s">
         <v>53</v>
       </c>
@@ -30300,7 +30300,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="993" customHeight="1" spans="1:12">
+    <row r="993" hidden="1" customHeight="1" spans="1:12">
       <c r="A993" s="7" t="s">
         <v>53</v>
       </c>
@@ -30329,7 +30329,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="994" customHeight="1" spans="1:12">
+    <row r="994" hidden="1" customHeight="1" spans="1:12">
       <c r="A994" s="7" t="s">
         <v>53</v>
       </c>
@@ -30358,7 +30358,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="995" customHeight="1" spans="1:12">
+    <row r="995" hidden="1" customHeight="1" spans="1:12">
       <c r="A995" s="7" t="s">
         <v>53</v>
       </c>
@@ -30387,7 +30387,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="996" customHeight="1" spans="1:12">
+    <row r="996" hidden="1" customHeight="1" spans="1:12">
       <c r="A996" s="7" t="s">
         <v>53</v>
       </c>
@@ -30416,7 +30416,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="997" customHeight="1" spans="1:12">
+    <row r="997" hidden="1" customHeight="1" spans="1:12">
       <c r="A997" s="7" t="s">
         <v>53</v>
       </c>
@@ -30445,7 +30445,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="998" customHeight="1" spans="1:12">
+    <row r="998" hidden="1" customHeight="1" spans="1:12">
       <c r="A998" s="7" t="s">
         <v>53</v>
       </c>
@@ -30474,7 +30474,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="999" customHeight="1" spans="1:12">
+    <row r="999" hidden="1" customHeight="1" spans="1:12">
       <c r="A999" s="7" t="s">
         <v>53</v>
       </c>
@@ -30503,7 +30503,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1000" customHeight="1" spans="1:12">
+    <row r="1000" hidden="1" customHeight="1" spans="1:12">
       <c r="A1000" s="7" t="s">
         <v>53</v>
       </c>
@@ -30532,7 +30532,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1001" customHeight="1" spans="1:12">
+    <row r="1001" hidden="1" customHeight="1" spans="1:12">
       <c r="A1001" s="7" t="s">
         <v>53</v>
       </c>
@@ -30561,7 +30561,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1002" customHeight="1" spans="1:12">
+    <row r="1002" hidden="1" customHeight="1" spans="1:12">
       <c r="A1002" s="7" t="s">
         <v>53</v>
       </c>
@@ -30590,7 +30590,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1003" customHeight="1" spans="1:12">
+    <row r="1003" hidden="1" customHeight="1" spans="1:12">
       <c r="A1003" s="7" t="s">
         <v>53</v>
       </c>
@@ -30619,7 +30619,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1004" customHeight="1" spans="1:12">
+    <row r="1004" hidden="1" customHeight="1" spans="1:12">
       <c r="A1004" s="7" t="s">
         <v>53</v>
       </c>
@@ -30648,7 +30648,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1005" customHeight="1" spans="1:12">
+    <row r="1005" hidden="1" customHeight="1" spans="1:12">
       <c r="A1005" s="7" t="s">
         <v>53</v>
       </c>
@@ -30677,7 +30677,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1006" customHeight="1" spans="1:12">
+    <row r="1006" hidden="1" customHeight="1" spans="1:12">
       <c r="A1006" s="7" t="s">
         <v>53</v>
       </c>
@@ -30706,7 +30706,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1007" customHeight="1" spans="1:12">
+    <row r="1007" hidden="1" customHeight="1" spans="1:12">
       <c r="A1007" s="7" t="s">
         <v>53</v>
       </c>
@@ -30735,7 +30735,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1008" customHeight="1" spans="1:12">
+    <row r="1008" hidden="1" customHeight="1" spans="1:12">
       <c r="A1008" s="7" t="s">
         <v>53</v>
       </c>
@@ -30764,7 +30764,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1009" customHeight="1" spans="1:12">
+    <row r="1009" hidden="1" customHeight="1" spans="1:12">
       <c r="A1009" s="7" t="s">
         <v>53</v>
       </c>
@@ -30793,7 +30793,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1010" customHeight="1" spans="1:12">
+    <row r="1010" hidden="1" customHeight="1" spans="1:12">
       <c r="A1010" s="8" t="s">
         <v>12</v>
       </c>
@@ -30825,7 +30825,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1011" customHeight="1" spans="1:12">
+    <row r="1011" hidden="1" customHeight="1" spans="1:12">
       <c r="A1011" s="7" t="s">
         <v>12</v>
       </c>
@@ -30855,7 +30855,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1012" customHeight="1" spans="1:12">
+    <row r="1012" hidden="1" customHeight="1" spans="1:12">
       <c r="A1012" s="7" t="s">
         <v>12</v>
       </c>
@@ -30885,7 +30885,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1013" customHeight="1" spans="1:12">
+    <row r="1013" hidden="1" customHeight="1" spans="1:12">
       <c r="A1013" s="7" t="s">
         <v>12</v>
       </c>
@@ -30915,7 +30915,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1014" customHeight="1" spans="1:12">
+    <row r="1014" hidden="1" customHeight="1" spans="1:12">
       <c r="A1014" s="7" t="s">
         <v>12</v>
       </c>
@@ -30945,7 +30945,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1015" customHeight="1" spans="1:12">
+    <row r="1015" hidden="1" customHeight="1" spans="1:12">
       <c r="A1015" s="7" t="s">
         <v>12</v>
       </c>
@@ -30975,7 +30975,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1016" customHeight="1" spans="1:12">
+    <row r="1016" hidden="1" customHeight="1" spans="1:12">
       <c r="A1016" s="7" t="s">
         <v>12</v>
       </c>
@@ -31005,7 +31005,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1017" customHeight="1" spans="1:12">
+    <row r="1017" hidden="1" customHeight="1" spans="1:12">
       <c r="A1017" s="7" t="s">
         <v>12</v>
       </c>
@@ -31035,7 +31035,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1018" customHeight="1" spans="1:12">
+    <row r="1018" hidden="1" customHeight="1" spans="1:12">
       <c r="A1018" s="7" t="s">
         <v>12</v>
       </c>
@@ -31065,7 +31065,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1019" customHeight="1" spans="1:12">
+    <row r="1019" hidden="1" customHeight="1" spans="1:12">
       <c r="A1019" s="7" t="s">
         <v>12</v>
       </c>
@@ -31095,7 +31095,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1020" customHeight="1" spans="1:12">
+    <row r="1020" hidden="1" customHeight="1" spans="1:12">
       <c r="A1020" s="7" t="s">
         <v>12</v>
       </c>
@@ -31125,7 +31125,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1021" customHeight="1" spans="1:12">
+    <row r="1021" hidden="1" customHeight="1" spans="1:12">
       <c r="A1021" s="7" t="s">
         <v>12</v>
       </c>
@@ -31155,7 +31155,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1022" customHeight="1" spans="1:12">
+    <row r="1022" hidden="1" customHeight="1" spans="1:12">
       <c r="A1022" s="7" t="s">
         <v>12</v>
       </c>
@@ -31185,7 +31185,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1023" customHeight="1" spans="1:12">
+    <row r="1023" hidden="1" customHeight="1" spans="1:12">
       <c r="A1023" s="7" t="s">
         <v>12</v>
       </c>
@@ -31215,7 +31215,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1024" customHeight="1" spans="1:12">
+    <row r="1024" hidden="1" customHeight="1" spans="1:12">
       <c r="A1024" s="7" t="s">
         <v>12</v>
       </c>
@@ -31245,7 +31245,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1025" customHeight="1" spans="1:12">
+    <row r="1025" hidden="1" customHeight="1" spans="1:12">
       <c r="A1025" s="7" t="s">
         <v>12</v>
       </c>
@@ -31275,7 +31275,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1026" customHeight="1" spans="1:12">
+    <row r="1026" hidden="1" customHeight="1" spans="1:12">
       <c r="A1026" s="7" t="s">
         <v>12</v>
       </c>
@@ -31305,7 +31305,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1027" customHeight="1" spans="1:12">
+    <row r="1027" hidden="1" customHeight="1" spans="1:12">
       <c r="A1027" s="7" t="s">
         <v>12</v>
       </c>
@@ -31335,7 +31335,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1028" customHeight="1" spans="1:12">
+    <row r="1028" hidden="1" customHeight="1" spans="1:12">
       <c r="A1028" s="7" t="s">
         <v>12</v>
       </c>
@@ -31365,7 +31365,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1029" customHeight="1" spans="1:12">
+    <row r="1029" hidden="1" customHeight="1" spans="1:12">
       <c r="A1029" s="7" t="s">
         <v>12</v>
       </c>
@@ -31395,7 +31395,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1030" customHeight="1" spans="1:12">
+    <row r="1030" hidden="1" customHeight="1" spans="1:12">
       <c r="A1030" s="7" t="s">
         <v>12</v>
       </c>
@@ -31425,7 +31425,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1031" customHeight="1" spans="1:12">
+    <row r="1031" hidden="1" customHeight="1" spans="1:12">
       <c r="A1031" s="7" t="s">
         <v>12</v>
       </c>
@@ -31455,7 +31455,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1032" customHeight="1" spans="1:12">
+    <row r="1032" hidden="1" customHeight="1" spans="1:12">
       <c r="A1032" s="7" t="s">
         <v>12</v>
       </c>
@@ -31485,7 +31485,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1033" customHeight="1" spans="1:12">
+    <row r="1033" hidden="1" customHeight="1" spans="1:12">
       <c r="A1033" s="7" t="s">
         <v>12</v>
       </c>
@@ -31515,7 +31515,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1034" customHeight="1" spans="1:12">
+    <row r="1034" hidden="1" customHeight="1" spans="1:12">
       <c r="A1034" s="7" t="s">
         <v>50</v>
       </c>
@@ -31545,7 +31545,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1035" customHeight="1" spans="1:12">
+    <row r="1035" hidden="1" customHeight="1" spans="1:12">
       <c r="A1035" s="7" t="s">
         <v>50</v>
       </c>
@@ -31575,7 +31575,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1036" customHeight="1" spans="1:12">
+    <row r="1036" hidden="1" customHeight="1" spans="1:12">
       <c r="A1036" s="7" t="s">
         <v>50</v>
       </c>
@@ -31605,7 +31605,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1037" customHeight="1" spans="1:12">
+    <row r="1037" hidden="1" customHeight="1" spans="1:12">
       <c r="A1037" s="7" t="s">
         <v>50</v>
       </c>
@@ -31635,7 +31635,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1038" customHeight="1" spans="1:12">
+    <row r="1038" hidden="1" customHeight="1" spans="1:12">
       <c r="A1038" s="7" t="s">
         <v>50</v>
       </c>
@@ -31665,7 +31665,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1039" customHeight="1" spans="1:12">
+    <row r="1039" hidden="1" customHeight="1" spans="1:12">
       <c r="A1039" s="7" t="s">
         <v>50</v>
       </c>
@@ -31695,7 +31695,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1040" customHeight="1" spans="1:12">
+    <row r="1040" hidden="1" customHeight="1" spans="1:12">
       <c r="A1040" s="7" t="s">
         <v>50</v>
       </c>
@@ -31725,7 +31725,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1041" customHeight="1" spans="1:12">
+    <row r="1041" hidden="1" customHeight="1" spans="1:12">
       <c r="A1041" s="7" t="s">
         <v>50</v>
       </c>
@@ -31755,7 +31755,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1042" customHeight="1" spans="1:12">
+    <row r="1042" hidden="1" customHeight="1" spans="1:12">
       <c r="A1042" s="7" t="s">
         <v>50</v>
       </c>
@@ -31785,7 +31785,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1043" customHeight="1" spans="1:12">
+    <row r="1043" hidden="1" customHeight="1" spans="1:12">
       <c r="A1043" s="7" t="s">
         <v>50</v>
       </c>
@@ -31815,7 +31815,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1044" customHeight="1" spans="1:12">
+    <row r="1044" hidden="1" customHeight="1" spans="1:12">
       <c r="A1044" s="7" t="s">
         <v>50</v>
       </c>
@@ -31845,7 +31845,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1045" customHeight="1" spans="1:12">
+    <row r="1045" hidden="1" customHeight="1" spans="1:12">
       <c r="A1045" s="7" t="s">
         <v>50</v>
       </c>
@@ -31875,7 +31875,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1046" customHeight="1" spans="1:12">
+    <row r="1046" hidden="1" customHeight="1" spans="1:12">
       <c r="A1046" s="7" t="s">
         <v>50</v>
       </c>
@@ -31905,7 +31905,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1047" customHeight="1" spans="1:12">
+    <row r="1047" hidden="1" customHeight="1" spans="1:12">
       <c r="A1047" s="7" t="s">
         <v>50</v>
       </c>
@@ -31935,7 +31935,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1048" customHeight="1" spans="1:12">
+    <row r="1048" hidden="1" customHeight="1" spans="1:12">
       <c r="A1048" s="7" t="s">
         <v>50</v>
       </c>
@@ -31965,7 +31965,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1049" customHeight="1" spans="1:12">
+    <row r="1049" hidden="1" customHeight="1" spans="1:12">
       <c r="A1049" s="7" t="s">
         <v>50</v>
       </c>
@@ -31995,7 +31995,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1050" customHeight="1" spans="1:12">
+    <row r="1050" hidden="1" customHeight="1" spans="1:12">
       <c r="A1050" s="7" t="s">
         <v>50</v>
       </c>
@@ -32025,7 +32025,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1051" customHeight="1" spans="1:12">
+    <row r="1051" hidden="1" customHeight="1" spans="1:12">
       <c r="A1051" s="7" t="s">
         <v>50</v>
       </c>
@@ -32055,7 +32055,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1052" customHeight="1" spans="1:12">
+    <row r="1052" hidden="1" customHeight="1" spans="1:12">
       <c r="A1052" s="7" t="s">
         <v>50</v>
       </c>
@@ -32085,7 +32085,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1053" customHeight="1" spans="1:12">
+    <row r="1053" hidden="1" customHeight="1" spans="1:12">
       <c r="A1053" s="7" t="s">
         <v>50</v>
       </c>
@@ -32115,7 +32115,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1054" customHeight="1" spans="1:12">
+    <row r="1054" hidden="1" customHeight="1" spans="1:12">
       <c r="A1054" s="7" t="s">
         <v>50</v>
       </c>
@@ -32145,7 +32145,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1055" customHeight="1" spans="1:12">
+    <row r="1055" hidden="1" customHeight="1" spans="1:12">
       <c r="A1055" s="7" t="s">
         <v>50</v>
       </c>
@@ -32175,7 +32175,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1056" customHeight="1" spans="1:12">
+    <row r="1056" hidden="1" customHeight="1" spans="1:12">
       <c r="A1056" s="7" t="s">
         <v>50</v>
       </c>
@@ -32205,7 +32205,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="1057" customHeight="1" spans="1:12">
+    <row r="1057" hidden="1" customHeight="1" spans="1:12">
       <c r="A1057" s="7" t="s">
         <v>50</v>
       </c>
@@ -32933,6 +32933,11 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L1081" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="amazon_uk_yuru"/>
+      </filters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pa-temp-fix-system.com/php/shell/sp/common/excel/PA-amazon广告自动化配置-20260416.xlsx
+++ b/pa-temp-fix-system.com/php/shell/sp/common/excel/PA-amazon广告自动化配置-20260416.xlsx
@@ -33033,9 +33033,9 @@
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L1081" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="3">
-      <filters>
-        <filter val="amazon_uk_hope"/>
-      </filters>
+      <customFilters>
+        <customFilter operator="equal" val="amazon_uk_hope"/>
+      </customFilters>
     </filterColumn>
     <extLst/>
   </autoFilter>
